--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="187">
   <si>
     <t>document</t>
   </si>
@@ -31,7 +31,7 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>customer | Tra cứu theo primary key</t>
+    <t>customer | Tra cứu theo id tự tăng, khóa chính</t>
   </si>
   <si>
     <t>customer | Tra cứu theo mã khách hàng</t>
@@ -43,34 +43,58 @@
     <t>customer | Tra cứu theo số</t>
   </si>
   <si>
-    <t>customer | Tra cứu theo chi nhánh nơi mở/quản lý mã cif này.</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo kiểu</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu theo mã</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo active, inactive, closed...</t>
+    <t>customer | Tìm kiếm theo họ và tên đầy đủ khách hàng.</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo nơi mở</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo loại cif</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo số nhà, tên đường</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo địa chỉ đầy đủ</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo mã chi nhánh quản lý trực tiếp khách hàng.</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo ví dụ: đồng, bạc, vàng, kim cương</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái</t>
   </si>
   <si>
     <t>customer | Tra cứu theo ngày cấp giấy tờ định danh</t>
   </si>
   <si>
-    <t>customer | Tra cứu theo số giấy tờ định danh</t>
+    <t>customer | Tìm kiếm theo địa chỉ thư điện tử khách hàng.</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo số điện thoại bàn/điện thoại cố định.</t>
   </si>
   <si>
     <t>customer | Tra cứu theo ví dụ: đã xác thực - ekyc, chưa xác thực</t>
   </si>
   <si>
-    <t>customer | Tra cứu theo họ tên</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo thời gian (hôm)</t>
-  </si>
-  <si>
-    <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo loại</t>
+    <t>customer | Tra cứu theo ví dụ: "identity card", "passport"</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo thời gian (thời gian)</t>
+  </si>
+  <si>
+    <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không.</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo tọa độ vị trí nhà ở hoặc nơi đăng ký</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo kinh độ</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo số điện thoại di động chính.</t>
   </si>
   <si>
     <t>customer | Tra cứu theo ví dụ: ca tp. hà nội</t>
@@ -79,448 +103,661 @@
     <t>customer | Tra cứu theo giá trị đặc trưng định danh duy nhất khách hàng.</t>
   </si>
   <si>
-    <t>customer | Lọc theo ví dụ: 1-hiệu lực, 0-hết hiệu lực</t>
+    <t>customer | Lọc theo trạng thái bản ghi</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng.</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo đường dẫn hoặc dữ liệu chữ ký mẫu số 2.</t>
+  </si>
+  <si>
+    <t>customer | Tìm kiếm theo giới tính</t>
   </si>
   <si>
     <t>customer | Lọc theo thời gian (ngày tháng năm sinh.)</t>
   </si>
   <si>
-    <t>customer | Lọc theo trạng thái cũ khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo sau khi cập nhật</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu theo đường dẫn ảnh mặt trước giấy tờ định danh</t>
+    <t>customer | Lọc theo trạng thái mới khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu theo cmnd/cccd</t>
   </si>
   <si>
     <t>customer | Tra cứu theo đường dẫn ảnh mặt sau giấy tờ định danh.</t>
   </si>
   <si>
-    <t>customer | Lọc loại theo Thời gian</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên primary key</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên mã khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên số định danh</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên số</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên chi nhánh nơi mở/quản lý mã cif này.</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách khách hàng theo nhóm kiểu</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên mã</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách khách hàng theo nhóm active, inactive, closed...</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên ngày cấp giấy tờ định danh</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên số giấy tờ định danh</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên ví dụ: đã xác thực - ekyc, chưa xác thực</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên họ tên</t>
-  </si>
-  <si>
-    <t>Sao kê lịch sử khách hàng trong khoảng thời gian</t>
-  </si>
-  <si>
-    <t>Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. được phân loại bởi loại</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên ví dụ: ca tp. hà nội</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên giá trị đặc trưng định danh duy nhất khách hàng.</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách khách hàng theo nhóm ví dụ: 1-hiệu lực, 0-hết hiệu lực</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách khách hàng theo nhóm trạng thái cũ khách hàng</t>
-  </si>
-  <si>
-    <t>Liệt kê danh sách khách hàng theo nhóm sau khi cập nhật</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên đường dẫn ảnh mặt trước giấy tờ định danh</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác khách hàng dựa trên đường dẫn ảnh mặt sau giấy tờ định danh.</t>
-  </si>
-  <si>
-    <t>Kết hợp lọc theo loại và khoảng ngày tháng</t>
-  </si>
-  <si>
-    <t>Check primary key 54043
-Tra cứu khách hàng theo primary key 21093
-Xem chi tiết 18101
-Hãy hiển thị dữ liệu bản ghi khách hàng với primary key 92078
-Tìm kiếm khách hàng ứng với số 27812
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có primary key là 11552
-primary key 22324 là của ai?
-khách hàng 66869
-Thông tin về khách hàng số 13849</t>
-  </si>
-  <si>
-    <t>Check mã khách hàng 75709962
-Tra cứu khách hàng theo mã khách hàng 88746681
-Xem chi tiết 22745739
-mã khách hàng 76306273 là của ai?
-Thông tin về khách hàng số 75359566
-Hãy hiển thị dữ liệu bản ghi khách hàng với mã khách hàng 33688568
-Tìm kiếm khách hàng ứng với số 22100700
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có mã khách hàng là 5741939
-khách hàng 92193047</t>
-  </si>
-  <si>
-    <t>khách hàng 77626
-Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 93271
-số định danh 20522 là của ai?
-Tìm kiếm khách hàng ứng với số 97443
-Xem chi tiết 47902
-Tra cứu khách hàng theo số định danh 27571
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 98888
-Check số định danh 33879
-Thông tin về khách hàng số 32183</t>
-  </si>
-  <si>
-    <t>Thông tin về khách hàng số 59371
-Check số 42476
-Xem chi tiết 11379
-Tìm kiếm khách hàng ứng với số 85136
-khách hàng 90167
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số là 12385
-Tra cứu khách hàng theo số 62786
-Hãy hiển thị dữ liệu bản ghi khách hàng với số 12946
-số 64738 là của ai?</t>
-  </si>
-  <si>
-    <t>số định danh 11664 là của ai?
-Check số định danh 93670
-Tìm kiếm khách hàng ứng với số 21285
-Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 11362
-khách hàng 86823
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 76716
-Thông tin về khách hàng số 72821
-Xem chi tiết 48437
-Tra cứu khách hàng theo số định danh 1271</t>
-  </si>
-  <si>
-    <t>Check chi nhánh nơi mở/quản lý mã cif này. 14122900
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có chi nhánh nơi mở/quản lý mã cif này. là 98039122
-Thông tin về khách hàng số 90768741
-khách hàng 3183725
-Xem chi tiết 85331068
-Tra cứu khách hàng theo chi nhánh nơi mở/quản lý mã cif này. 88933156
-Tìm kiếm khách hàng ứng với số 95002949
-chi nhánh nơi mở/quản lý mã cif này. 39837045 là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với chi nhánh nơi mở/quản lý mã cif này. 95252110</t>
-  </si>
-  <si>
-    <t>Cho xem danh sách khách hàng từng
-Lọc các khách hàng đang ở trạng thái cách
-Hãy liệt kê danh sách các khách hàng có kiểu là đang
-Trích xuất báo cáo các khách hàng thuộc loại vậy
-Danh sách chưa
-Tìm tất cả khách hàng loại cũng
-Những khách hàng nào là vài?</t>
-  </si>
-  <si>
-    <t>Tìm kiếm khách hàng ứng với số 28071
-Check mã 41516
-Hãy hiển thị dữ liệu bản ghi khách hàng với mã 15756
-Tra cứu khách hàng theo mã 56060
-Xem chi tiết 29373
-mã 45078 là của ai?
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có mã là 65041
-Thông tin về khách hàng số 92185
-khách hàng 13532</t>
-  </si>
-  <si>
-    <t>Lọc các khách hàng đang ở trạng thái được
-Cho xem danh sách khách hàng giống
-Hãy liệt kê danh sách các khách hàng có active, inactive, closed... là tại
-Những khách hàng nào là và?
-Trích xuất báo cáo các khách hàng thuộc loại đang
-Tìm tất cả khách hàng loại có
-Danh sách sẽ</t>
-  </si>
-  <si>
-    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với ngày cấp giấy tờ định danh 38346
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có ngày cấp giấy tờ định danh là 57402
-Thông tin về khách hàng số 19715
-Tra cứu khách hàng theo ngày cấp giấy tờ định danh 84624
-Tìm kiếm khách hàng ứng với số 14106
-ngày cấp giấy tờ định danh 43049 là của ai?
-Check ngày cấp giấy tờ định danh 38801
-Xem chi tiết 76260
-khách hàng 83945</t>
-  </si>
-  <si>
-    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với số giấy tờ định danh 56772
-Xem chi tiết 16364
-Tra cứu khách hàng theo số giấy tờ định danh 9418
-Check số giấy tờ định danh 8931
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số giấy tờ định danh là 75900
-khách hàng 29252
-Thông tin về khách hàng số 73670
-số giấy tờ định danh 91384 là của ai?
-Tìm kiếm khách hàng ứng với số 55767</t>
-  </si>
-  <si>
-    <t>khách hàng 23314
-Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: đã xác thực - ekyc, chưa xác thực 21688
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có ví dụ: đã xác thực - ekyc, chưa xác thực là 59242
-Tìm kiếm khách hàng ứng với số 6852
-Tra cứu khách hàng theo ví dụ: đã xác thực - ekyc, chưa xác thực 69578
-Xem chi tiết 96953
-ví dụ: đã xác thực - ekyc, chưa xác thực 60936 là của ai?
-Thông tin về khách hàng số 52590
-Check ví dụ: đã xác thực - ekyc, chưa xác thực 5516</t>
-  </si>
-  <si>
-    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với họ tên Bà Thảo Vũ
-Thông tin về khách hàng số Chị Nhật Phạm
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có họ tên là Quý cô Khoa Mai
-Tìm kiếm khách hàng ứng với số Quang Hữu Bùi
-Tra cứu khách hàng theo họ tên Cô Duyên Vũ
-họ tên Quý ông Trọng Dương là của ai?
-Check họ tên Ánh Mai
-Xem chi tiết Hạnh Trần
-khách hàng Hoàng Mai</t>
-  </si>
-  <si>
-    <t>Xem biến động khách hàng giữa 2025-11-04 và hôm nay
-Truy xuất lịch sử khách hàng trong khoảng thời gian từ 2025-08-11 đến hôm nay
-Kiểm tra khách hàng trong ngày 2026-01-15
-Liệt kê các giao dịch phát sinh từ ngày 2025-03-31 tới ngày hôm nay
-Lịch sử khách hàng 2025-12-13 đến hôm nay
-Sao kê khách hàng từ 2025-02-22 - hôm nay
-Những khách hàng nào diễn ra từ 2025-06-08 đến hôm nay?</t>
-  </si>
-  <si>
-    <t>Cộng hết đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các giao dịch 600000
-khách hàng 15150000 có tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. là mấy?
-Thống kê tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của các khách hàng được phân loại theo loại 17100000
-Tính tổng tiền đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. theo loại 24000000
-Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của khách hàng 31000000 là bao nhiêu?
-Hãy tính toán tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. cho nhóm 16600000</t>
-  </si>
-  <si>
-    <t>Thông tin về khách hàng số 1583
-Xem chi tiết 12170
-Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 62546
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 86037
-Tra cứu khách hàng theo số định danh 76930
-Check số định danh 47906
-số định danh 71501 là của ai?
-Tìm kiếm khách hàng ứng với số 72102
-khách hàng 78829</t>
-  </si>
-  <si>
-    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 10670
-khách hàng 12032
-Tìm kiếm khách hàng ứng với số 70092
-số định danh 6968 là của ai?
-Tra cứu khách hàng theo số định danh 57085
-Xem chi tiết 38324
-Check số định danh 54908
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 30484
-Thông tin về khách hàng số 36830</t>
-  </si>
-  <si>
-    <t>Check ví dụ: ca tp. hà nội 33876
-Xem chi tiết 14834
-Tra cứu khách hàng theo ví dụ: ca tp. hà nội 97248
-ví dụ: ca tp. hà nội 77458 là của ai?
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có ví dụ: ca tp. hà nội là 19676
-khách hàng 47752
-Thông tin về khách hàng số 75034
-Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: ca tp. hà nội 14882
-Tìm kiếm khách hàng ứng với số 99655</t>
-  </si>
-  <si>
-    <t>Thông tin về khách hàng số 99186
-Xem chi tiết 48963
-Tra cứu khách hàng theo số định danh 34589
-khách hàng 45036
-số định danh 55780 là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 32515
-Check số định danh 64086
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 58535
-Tìm kiếm khách hàng ứng với số 87075</t>
-  </si>
-  <si>
-    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với giá trị đặc trưng định danh duy nhất khách hàng. 93998
-Xem chi tiết 11833
-Tìm kiếm khách hàng ứng với số 1363
-Thông tin về khách hàng số 15746
-khách hàng 63046
-Check giá trị đặc trưng định danh duy nhất khách hàng. 20091
-giá trị đặc trưng định danh duy nhất khách hàng. 51448 là của ai?
-Tra cứu khách hàng theo giá trị đặc trưng định danh duy nhất khách hàng. 59572
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có giá trị đặc trưng định danh duy nhất khách hàng. là 86119</t>
-  </si>
-  <si>
-    <t>Những khách hàng nào là từng?
-Danh sách trong
-Hãy liệt kê danh sách các khách hàng có ví dụ: 1-hiệu lực, 0-hết hiệu lực là vì
-Trích xuất báo cáo các khách hàng thuộc loại đang
-Cho xem danh sách khách hàng nào
-Lọc các khách hàng đang ở trạng thái đúng
-Tìm tất cả khách hàng loại đến</t>
-  </si>
-  <si>
-    <t>Truy xuất lịch sử khách hàng trong khoảng thời gian từ 2025-05-27 đến hôm nay
-Xem biến động khách hàng giữa 2025-02-08 và hôm nay
-Kiểm tra khách hàng trong ngày 2025-08-16
-Liệt kê các giao dịch phát sinh từ ngày 2025-03-16 tới ngày hôm nay
-Sao kê khách hàng từ 2025-11-29 - hôm nay
-Những khách hàng nào diễn ra từ 2026-01-24 đến hôm nay?
-Lịch sử khách hàng 2025-09-24 đến hôm nay</t>
-  </si>
-  <si>
-    <t>Lọc các khách hàng đang ở trạng thái về
-Cho xem danh sách khách hàng làm
-Những khách hàng nào là là?
-Trích xuất báo cáo các khách hàng thuộc loại không
-Danh sách như
-Tìm tất cả khách hàng loại khiến
-Hãy liệt kê danh sách các khách hàng có trạng thái cũ khách hàng là tại</t>
-  </si>
-  <si>
-    <t>Trích xuất báo cáo các khách hàng thuộc loại với
-Danh sách điều
-Hãy liệt kê danh sách các khách hàng có sau khi cập nhật là vậy
-Tìm tất cả khách hàng loại sẽ
-Lọc các khách hàng đang ở trạng thái của
-Những khách hàng nào là bạn?
-Cho xem danh sách khách hàng gần</t>
-  </si>
-  <si>
-    <t>Tìm kiếm khách hàng ứng với số 4189
-Check đường dẫn ảnh mặt trước giấy tờ định danh 74246
-đường dẫn ảnh mặt trước giấy tờ định danh 23323 là của ai?
-Thông tin về khách hàng số 26310
-Xem chi tiết 3292
-Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt trước giấy tờ định danh 84198
-khách hàng 38498
-Tra cứu khách hàng theo đường dẫn ảnh mặt trước giấy tờ định danh 4574
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có đường dẫn ảnh mặt trước giấy tờ định danh là 19339</t>
-  </si>
-  <si>
-    <t>khách hàng 27622
-đường dẫn ảnh mặt sau giấy tờ định danh. 10691 là của ai?
-Thông tin về khách hàng số 89644
-Tìm kiếm khách hàng ứng với số 23500
-Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt sau giấy tờ định danh. 32401
-Xem chi tiết 69887
-Tra cứu khách hàng theo đường dẫn ảnh mặt sau giấy tờ định danh. 34937
-Vui lòng Tra cứu thông tin chi tiết của khách hàng có đường dẫn ảnh mặt sau giấy tờ định danh. là 27364
-Check đường dẫn ảnh mặt sau giấy tờ định danh. 71792</t>
-  </si>
-  <si>
-    <t>Lọc các khách hàng thì diễn ra từ 2025-05-23 đến hôm nay
-Liệt kê khách hàng của phát sinh ngày 2025-03-23
-Xem khách hàng có loại là điều trong khoảng 2025-10-02 - hôm nay
-Tìm khách hàng nhiều hôm 2025-10-13
-Sao kê khách hàng loại nào từ ngày 2025-07-11 tới hôm nay</t>
-  </si>
-  <si>
-    <t>id, primary key, tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_no, mã khách hàng, tìm kiếm</t>
-  </si>
-  <si>
-    <t>customer_id, số định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>customer_no, số, tìm kiếm</t>
-  </si>
-  <si>
-    <t>system_id, số định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_branch, chi nhánh nơi mở/quản lý mã cif này., tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_type, kiểu, danh sách</t>
-  </si>
-  <si>
-    <t>branch_code, mã, tìm kiếm</t>
-  </si>
-  <si>
-    <t>customer_status, active, inactive, closed..., danh sách</t>
-  </si>
-  <si>
-    <t>date_of_issue, ngày cấp giấy tờ định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>identify_id, số giấy tờ định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>identify_level, ví dụ: đã xác thực - ekyc, chưa xác thực, tìm kiếm</t>
-  </si>
-  <si>
-    <t>identify_name, họ tên, tìm kiếm</t>
-  </si>
-  <si>
-    <t>init_date, thời gian, ngày tháng</t>
-  </si>
-  <si>
-    <t>tổng is_fee_default, thống kê</t>
-  </si>
-  <si>
-    <t>nationality_id, số định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>place_id, số định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>place_of_issue, ví dụ: ca tp. hà nội, tìm kiếm</t>
-  </si>
-  <si>
-    <t>unique_id, số định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>unique_value, giá trị đặc trưng định danh duy nhất khách hàng., tìm kiếm</t>
-  </si>
-  <si>
-    <t>status, ví dụ: 1-hiệu lực, 0-hết hiệu lực, danh sách</t>
-  </si>
-  <si>
-    <t>date_of_birth, thời gian, ngày tháng</t>
-  </si>
-  <si>
-    <t>old_customer_status, trạng thái cũ khách hàng, danh sách</t>
-  </si>
-  <si>
-    <t>new_customer_status, sau khi cập nhật, danh sách</t>
-  </si>
-  <si>
-    <t>unique_image_front, đường dẫn ảnh mặt trước giấy tờ định danh, tìm kiếm</t>
-  </si>
-  <si>
-    <t>unique_image_back, đường dẫn ảnh mặt sau giấy tờ định danh., tìm kiếm</t>
-  </si>
-  <si>
-    <t>cif_type, init_date, lọc đa điều kiện</t>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên id tự tăng, khóa chính (id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên mã khách hàng (cif_no)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số định danh (customer_id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số (customer_no)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong họ và tên đầy đủ khách hàng.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số định danh (system_id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên nơi mở (cif_branch)</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng được phân nhóm bởi loại cif. Ví dụ: loại cif A, B...</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong số nhà, tên đường</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong địa chỉ đầy đủ</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên mã chi nhánh quản lý trực tiếp khách hàng. (branch_code)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong ví dụ: đồng, bạc, vàng, kim cương</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng được phân nhóm bởi trạng thái. Ví dụ: trạng thái A, B...</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên ngày cấp giấy tờ định danh (date_of_issue)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong địa chỉ thư điện tử khách hàng.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong số điện thoại bàn/điện thoại cố định.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số định danh (identify_id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên ví dụ: đã xác thực - ekyc, chưa xác thực (identify_level)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên ví dụ: "identity card", "passport" (identify_name)</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử khách hàng trong một khoảng thời gian cụ thể (Từ ngày... đến ngày...)</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không. của khách hàng. Có thể kết hợp điều kiện lọc (Mặc định chỉ tính giao dịch thành công).</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong tọa độ vị trí nhà ở hoặc nơi đăng ký</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong kinh độ</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong số điện thoại di động chính.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số định danh (nationality_id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số định danh (place_id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên ví dụ: ca tp. hà nội (place_of_issue)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên số định danh (unique_id)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên giá trị đặc trưng định danh duy nhất khách hàng. (unique_value)</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng được phân nhóm bởi trạng thái bản ghi. Ví dụ: trạng thái bản ghi A, B...</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong đường dẫn hoặc dữ liệu chữ ký mẫu số 2.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm các khách hàng có chứa nội dung/từ khóa trong giới tính</t>
+  </si>
+  <si>
+    <t>Liệt kê danh sách khách hàng được phân nhóm bởi trạng thái mới khách hàng. Ví dụ: trạng thái mới khách hàng A, B...</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên cmnd/cccd (unique_image_front)</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác thông tin khách hàng dựa trên đường dẫn ảnh mặt sau giấy tờ định danh. (unique_image_back)</t>
+  </si>
+  <si>
+    <t>Thông tin về khách hàng số 738737
+Check id tự tăng, khóa chính 428221
+id tự tăng, khóa chính 610969 là của ai?
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có id tự tăng, khóa chính là 605236
+Xem chi tiết 600613
+Hãy hiển thị dữ liệu bản ghi khách hàng với id tự tăng, khóa chính 773662
+Tìm kiếm khách hàng ứng với số 985562
+Tra cứu khách hàng theo id tự tăng, khóa chính 513045
+khách hàng 810875</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 485710
+Hãy hiển thị dữ liệu bản ghi khách hàng với mã khách hàng 678862
+mã khách hàng 618026 là của ai?
+Check mã khách hàng 992463
+Thông tin về khách hàng số 350090
+Xem chi tiết 329791
+Vui lòng Xem thông tin chi tiết của khách hàng có mã khách hàng là 724480
+Tìm khách hàng theo mã khách hàng 461296
+khách hàng 449090</t>
+  </si>
+  <si>
+    <t>Vui lòng Xem thông tin chi tiết của khách hàng có số định danh là 175125
+Xem chi tiết 897645
+khách hàng 727196
+Thông tin về khách hàng số 569397
+số định danh 722487 là của ai?
+Check số định danh 298557
+Tra cứu khách hàng theo số định danh 208182
+Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 535591
+Tìm kiếm khách hàng ứng với số 843722</t>
+  </si>
+  <si>
+    <t>Vui lòng Tra cứu thông tin chi tiết của khách hàng có số là 989732
+Tìm kiếm khách hàng ứng với số 813330
+số 251515 là của ai?
+Xem khách hàng theo số 669490
+Xem chi tiết 751730
+Thông tin về khách hàng số 871767
+Hãy hiển thị dữ liệu bản ghi khách hàng với số 195780
+Check số 232764
+khách hàng 625848</t>
+  </si>
+  <si>
+    <t>Xem khách hàng theo họ và tên đầy đủ khách hàng. để
+Hãy hiển thị dữ liệu bản ghi khách hàng với họ và tên đầy đủ khách hàng. như
+Thông tin về khách hàng số của
+Vui lòng Tìm thông tin chi tiết của khách hàng có họ và tên đầy đủ khách hàng. là bên
+Tìm kiếm khách hàng ứng với số như
+khách hàng của
+Check họ và tên đầy đủ khách hàng. khiến
+Xem chi tiết dưới
+họ và tên đầy đủ khách hàng. rất là của ai?</t>
+  </si>
+  <si>
+    <t>Xem chi tiết 689559
+Tìm khách hàng theo số định danh 902220
+Tìm kiếm khách hàng ứng với số 723702
+Check số định danh 789798
+Thông tin về khách hàng số 952852
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 558204
+số định danh 727119 là của ai?
+khách hàng 851871
+Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 467090</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với nơi mở lớn
+Xem chi tiết bên
+Thông tin về khách hàng số bạn
+khách hàng được
+Check nơi mở mà
+nơi mở về là của ai?
+Tìm kiếm khách hàng ứng với số theo
+Tra cứu khách hàng theo nơi mở cho
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có nơi mở là nào</t>
+  </si>
+  <si>
+    <t>Danh sách NHƯ
+Trích xuất báo cáo các khách hàng thuộc loại HOẶC
+khách hàng nạp thẻ
+Tìm tất cả khách hàng loại CỦA
+Lọc các khách hàng đang ở trạng thái BÊN
+Cho xem danh sách khách hàng ĐỂ
+Những khách hàng nào là HOẶC?
+Hãy liệt kê danh sách các khách hàng có loại cif là MỖI
+danh sách khách hàng nạp thẻ</t>
+  </si>
+  <si>
+    <t>Xem chi tiết đi
+Hãy hiển thị dữ liệu bản ghi khách hàng với số nhà, tên đường để
+Check số nhà, tên đường nếu
+Thông tin về khách hàng số của
+số nhà, tên đường đi là của ai?
+khách hàng vẫn
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số nhà, tên đường là đi
+Tìm kiếm khách hàng ứng với số chỉ
+Tìm khách hàng theo số nhà, tên đường hoặc</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với địa chỉ đầy đủ gần
+Tìm kiếm khách hàng ứng với số đó
+Check địa chỉ đầy đủ vài
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có địa chỉ đầy đủ là sẽ
+địa chỉ đầy đủ khi là của ai?
+Thông tin về khách hàng số rất
+Tra cứu khách hàng theo địa chỉ đầy đủ cũng
+khách hàng trong
+Xem chi tiết người</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 932574
+Thông tin về khách hàng số 738398
+khách hàng 312856
+Check mã chi nhánh quản lý trực tiếp khách hàng. 877874
+mã chi nhánh quản lý trực tiếp khách hàng. 775193 là của ai?
+Xem chi tiết 262638
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có mã chi nhánh quản lý trực tiếp khách hàng. là 825292
+Hãy hiển thị dữ liệu bản ghi khách hàng với mã chi nhánh quản lý trực tiếp khách hàng. 349512
+Tìm khách hàng theo mã chi nhánh quản lý trực tiếp khách hàng. 971984</t>
+  </si>
+  <si>
+    <t>Vui lòng Xem thông tin chi tiết của khách hàng có ví dụ: đồng, bạc, vàng, kim cương là tại
+Thông tin về khách hàng số cũng
+ví dụ: đồng, bạc, vàng, kim cương không là của ai?
+khách hàng để
+Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: đồng, bạc, vàng, kim cương được
+Xem chi tiết là
+Check ví dụ: đồng, bạc, vàng, kim cương cách
+Tìm kiếm khách hàng ứng với số đang
+Tìm khách hàng theo ví dụ: đồng, bạc, vàng, kim cương thế</t>
+  </si>
+  <si>
+    <t>Trích xuất báo cáo các khách hàng thuộc loại NHƯNG
+Những khách hàng nào là NÀO?
+danh sách khách hàng hoàn tất
+Tìm tất cả khách hàng loại VÌ
+Danh sách TRONG
+khách hàng hoàn tất
+Hãy liệt kê danh sách các khách hàng có trạng thái là NHƯ
+Cho xem danh sách khách hàng CỦA
+Lọc các khách hàng đang ở trạng thái HƠN</t>
+  </si>
+  <si>
+    <t>Check ngày cấp giấy tờ định danh 2025-08-11
+khách hàng 2026-01-24
+Thông tin về khách hàng số 2025-09-22
+ngày cấp giấy tờ định danh 2025-12-23 là của ai?
+Tra cứu khách hàng theo ngày cấp giấy tờ định danh 2025-12-15
+Hãy hiển thị dữ liệu bản ghi khách hàng với ngày cấp giấy tờ định danh 2025-07-02
+Tìm kiếm khách hàng ứng với số 2025-05-10
+Xem chi tiết 2025-02-25
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có ngày cấp giấy tờ định danh là 2025-12-31</t>
+  </si>
+  <si>
+    <t>địa chỉ thư điện tử khách hàng. trong là của ai?
+Check địa chỉ thư điện tử khách hàng. nào
+Tra cứu khách hàng theo địa chỉ thư điện tử khách hàng. đến
+khách hàng nhưng
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có địa chỉ thư điện tử khách hàng. là nào
+Thông tin về khách hàng số đến
+Hãy hiển thị dữ liệu bản ghi khách hàng với địa chỉ thư điện tử khách hàng. nào
+Xem chi tiết tự
+Tìm kiếm khách hàng ứng với số đúng</t>
+  </si>
+  <si>
+    <t>số điện thoại bàn/điện thoại cố định. vài là của ai?
+Hãy hiển thị dữ liệu bản ghi khách hàng với số điện thoại bàn/điện thoại cố định. các
+Xem chi tiết thay
+Tìm khách hàng theo số điện thoại bàn/điện thoại cố định. vài
+Vui lòng Tìm thông tin chi tiết của khách hàng có số điện thoại bàn/điện thoại cố định. là có
+khách hàng trong
+Thông tin về khách hàng số các
+Tìm kiếm khách hàng ứng với số mà
+Check số điện thoại bàn/điện thoại cố định. như</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 148581
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 371970
+khách hàng 241728
+Xem chi tiết 796927
+Check số định danh 518794
+Tìm kiếm khách hàng ứng với số 137555
+Tìm khách hàng theo số định danh 549922
+số định danh 244684 là của ai?
+Thông tin về khách hàng số 927356</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: đã xác thực - ekyc, chưa xác thực 607915
+Tìm kiếm khách hàng ứng với số 218036
+Tra cứu khách hàng theo ví dụ: đã xác thực - ekyc, chưa xác thực 590636
+Thông tin về khách hàng số 231831
+Xem chi tiết 373515
+khách hàng 112926
+ví dụ: đã xác thực - ekyc, chưa xác thực 926148 là của ai?
+Check ví dụ: đã xác thực - ekyc, chưa xác thực 601115
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có ví dụ: đã xác thực - ekyc, chưa xác thực là 326530</t>
+  </si>
+  <si>
+    <t>khách hàng 330347
+Thông tin về khách hàng số 492547
+Tìm kiếm khách hàng ứng với số 337249
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có ví dụ: "identity card", "passport" là 505151
+Xem chi tiết 348398
+ví dụ: "identity card", "passport" 307071 là của ai?
+Xem khách hàng theo ví dụ: "identity card", "passport" 116433
+Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: "identity card", "passport" 799092
+Check ví dụ: "identity card", "passport" 439464</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào diễn ra từ 2026-01-18 đến hôm nay?
+Sao kê khách hàng từ 2026-01-05 - hôm nay
+Truy xuất lịch sử khách hàng trong khoảng thời gian từ 2026-01-25 đến hôm nay
+Liệt kê các giao dịch phát sinh từ ngày 2026-01-17 tới ngày hôm nay
+Xem biến động khách hàng giữa 2025-12-31 và hôm nay
+Kiểm tra khách hàng trong ngày 2026-01-04
+Lịch sử khách hàng 2026-01-22 đến hôm nay</t>
+  </si>
+  <si>
+    <t>Thống kê tổng  của các khách hàng được phân loại theo  82000000
+khách hàng 2000000 có tổng  là mấy?
+Cộng hết  của các giao dịch 400000
+Hãy tính toán tổng giá trị  cho nhóm 2900000
+Tính tổng tiền  theo  3400000
+Tổng  của khách hàng 96000000 là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Vui lòng Xem thông tin chi tiết của khách hàng có tọa độ vị trí nhà ở hoặc nơi đăng ký là nhiều
+Xem chi tiết điều
+khách hàng này
+Tra cứu khách hàng theo tọa độ vị trí nhà ở hoặc nơi đăng ký đi
+Hãy hiển thị dữ liệu bản ghi khách hàng với tọa độ vị trí nhà ở hoặc nơi đăng ký gần
+tọa độ vị trí nhà ở hoặc nơi đăng ký và là của ai?
+Tìm kiếm khách hàng ứng với số chỉ
+Check tọa độ vị trí nhà ở hoặc nơi đăng ký đó
+Thông tin về khách hàng số bên</t>
+  </si>
+  <si>
+    <t>Check kinh độ bên
+Hãy hiển thị dữ liệu bản ghi khách hàng với kinh độ hơn
+Xem chi tiết trong
+Xem khách hàng theo kinh độ nhưng
+Thông tin về khách hàng số giữa
+Tìm kiếm khách hàng ứng với số của
+kinh độ tự là của ai?
+khách hàng với
+Vui lòng Tìm thông tin chi tiết của khách hàng có kinh độ là cũng</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với số điện thoại di động chính. với
+số điện thoại di động chính. nào là của ai?
+khách hàng cũng
+Xem chi tiết như
+Tra cứu khách hàng theo số điện thoại di động chính. sau
+Thông tin về khách hàng số tự
+Check số điện thoại di động chính. như
+Tìm kiếm khách hàng ứng với số đang
+Vui lòng Tìm thông tin chi tiết của khách hàng có số điện thoại di động chính. là mà</t>
+  </si>
+  <si>
+    <t>Check số định danh 421397
+Tìm khách hàng theo số định danh 941571
+khách hàng 515890
+Thông tin về khách hàng số 583555
+số định danh 500859 là của ai?
+Tìm kiếm khách hàng ứng với số 565892
+Xem chi tiết 636318
+Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 395908
+Vui lòng Xem thông tin chi tiết của khách hàng có số định danh là 321115</t>
+  </si>
+  <si>
+    <t>khách hàng 359142
+Xem chi tiết 498917
+số định danh 314104 là của ai?
+Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 172807
+Check số định danh 781812
+Xem khách hàng theo số định danh 830467
+Tìm kiếm khách hàng ứng với số 652948
+Thông tin về khách hàng số 473450
+Vui lòng Tìm thông tin chi tiết của khách hàng có số định danh là 218132</t>
+  </si>
+  <si>
+    <t>Tra cứu khách hàng theo ví dụ: ca tp. hà nội tại
+Thông tin về khách hàng số tại
+Hãy hiển thị dữ liệu bản ghi khách hàng với ví dụ: ca tp. hà nội nếu
+Check ví dụ: ca tp. hà nội vì
+khách hàng từng
+ví dụ: ca tp. hà nội giữa là của ai?
+Tìm kiếm khách hàng ứng với số đang
+Vui lòng Tìm thông tin chi tiết của khách hàng có ví dụ: ca tp. hà nội là để
+Xem chi tiết đi</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số 291694
+số định danh 885236 là của ai?
+Hãy hiển thị dữ liệu bản ghi khách hàng với số định danh 282645
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có số định danh là 983648
+Thông tin về khách hàng số 646277
+Xem chi tiết 865563
+Check số định danh 903469
+Tìm khách hàng theo số định danh 794866
+khách hàng 955916</t>
+  </si>
+  <si>
+    <t>Xem chi tiết bên
+giá trị đặc trưng định danh duy nhất khách hàng. của là của ai?
+Tìm kiếm khách hàng ứng với số cách
+Vui lòng Tìm thông tin chi tiết của khách hàng có giá trị đặc trưng định danh duy nhất khách hàng. là thay
+Thông tin về khách hàng số trong
+Tìm khách hàng theo giá trị đặc trưng định danh duy nhất khách hàng. số
+Hãy hiển thị dữ liệu bản ghi khách hàng với giá trị đặc trưng định danh duy nhất khách hàng. số
+khách hàng trong
+Check giá trị đặc trưng định danh duy nhất khách hàng. hơn</t>
+  </si>
+  <si>
+    <t>Danh sách VÀ
+Những khách hàng nào là CỦA?
+Tìm tất cả khách hàng loại SỐ
+Trích xuất báo cáo các khách hàng thuộc loại VỚI
+Hãy liệt kê danh sách các khách hàng có trạng thái bản ghi là ĐỂ
+danh sách khách hàng quá giờ
+khách hàng quá giờ
+Lọc các khách hàng đang ở trạng thái CŨNG
+Cho xem danh sách khách hàng VẪN</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số hoặc
+Thông tin về khách hàng số hoặc
+Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng. và
+Check đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng. từ
+Vui lòng Xem thông tin chi tiết của khách hàng có đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng. là một
+khách hàng thế
+đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng. cho là của ai?
+Xem chi tiết tự
+Tìm khách hàng theo đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng. trong</t>
+  </si>
+  <si>
+    <t>Xem chi tiết đang
+Tìm kiếm khách hàng ứng với số đó
+đường dẫn hoặc dữ liệu chữ ký mẫu số 2. bạn là của ai?
+khách hàng đi
+Vui lòng Tìm thông tin chi tiết của khách hàng có đường dẫn hoặc dữ liệu chữ ký mẫu số 2. là dưới
+Tra cứu khách hàng theo đường dẫn hoặc dữ liệu chữ ký mẫu số 2. khi
+Check đường dẫn hoặc dữ liệu chữ ký mẫu số 2. như
+Thông tin về khách hàng số nơi
+Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn hoặc dữ liệu chữ ký mẫu số 2. làm</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với giới tính để
+Tìm kiếm khách hàng ứng với số rất
+Xem chi tiết chưa
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có giới tính là để
+khách hàng trong
+Check giới tính với
+Tìm khách hàng theo giới tính mỗi
+Thông tin về khách hàng số có
+giới tính rất là của ai?</t>
+  </si>
+  <si>
+    <t>Lịch sử khách hàng 2026-01-20 đến hôm nay
+Xem biến động khách hàng giữa 2026-01-15 và hôm nay
+Truy xuất lịch sử khách hàng trong khoảng thời gian từ 2026-01-19 đến hôm nay
+Liệt kê các giao dịch phát sinh từ ngày 2026-01-16 tới ngày hôm nay
+Sao kê khách hàng từ 2026-01-17 - hôm nay
+Những khách hàng nào diễn ra từ 2026-01-08 đến hôm nay?
+Kiểm tra khách hàng trong ngày 2026-01-11</t>
+  </si>
+  <si>
+    <t>danh sách khách hàng treo
+Danh sách THEO
+Hãy liệt kê danh sách các khách hàng có trạng thái là VÌ
+Những khách hàng nào là VÀI?
+Tìm tất cả khách hàng loại TRONG
+Lọc các khách hàng đang ở trạng thái TÔI
+Cho xem danh sách khách hàng GẦN
+Trích xuất báo cáo các khách hàng thuộc loại CỦA
+khách hàng treo</t>
+  </si>
+  <si>
+    <t>Tìm tất cả khách hàng loại CÓ
+khách hàng thành công
+Cho xem danh sách khách hàng SAU
+Hãy liệt kê danh sách các khách hàng có trạng thái mới khách hàng là TỪNG
+Trích xuất báo cáo các khách hàng thuộc loại VỀ
+Lọc các khách hàng đang ở trạng thái ĐI
+danh sách khách hàng thành công
+Danh sách THAY
+Những khách hàng nào là NHƯ?</t>
+  </si>
+  <si>
+    <t>khách hàng nào
+Check cmnd/cccd vì
+Xem chi tiết với
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có cmnd/cccd là người
+Tra cứu khách hàng theo cmnd/cccd dưới
+cmnd/cccd vài là của ai?
+Thông tin về khách hàng số khiến
+Hãy hiển thị dữ liệu bản ghi khách hàng với cmnd/cccd để
+Tìm kiếm khách hàng ứng với số để</t>
+  </si>
+  <si>
+    <t>đường dẫn ảnh mặt sau giấy tờ định danh. nơi là của ai?
+Thông tin về khách hàng số cũng
+Vui lòng Xem thông tin chi tiết của khách hàng có đường dẫn ảnh mặt sau giấy tờ định danh. là sẽ
+Check đường dẫn ảnh mặt sau giấy tờ định danh. bên
+Tìm kiếm khách hàng ứng với số như
+Xem chi tiết cũng
+Tra cứu khách hàng theo đường dẫn ảnh mặt sau giấy tờ định danh. đang
+khách hàng cho
+Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt sau giấy tờ định danh. vài</t>
+  </si>
+  <si>
+    <t>id tự tăng, khóa chính, primary key</t>
+  </si>
+  <si>
+    <t>mã khách hàng, customer information file, số cif, mã định danh khách hàng</t>
+  </si>
+  <si>
+    <t>số định danh, số, id, id định danh khách hàng nội bộ., mã</t>
+  </si>
+  <si>
+    <t>số, có thể khác với cif tùy theo cấu trúc hệ thống, mã số khách hàng, mã số</t>
+  </si>
+  <si>
+    <t>họ và tên đầy đủ khách hàng., tên, họ tên</t>
+  </si>
+  <si>
+    <t>số định danh, số, id, id nguồn, nếu dữ liệu được đẩy từ khác sang, mã</t>
+  </si>
+  <si>
+    <t>nơi mở, chi nhánh nơi mở/quản lý mã cif này., pgd, chi nhánh, phòng giao dịch</t>
+  </si>
+  <si>
+    <t>loại cif, ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên..., hình thức, kiểu, loại</t>
+  </si>
+  <si>
+    <t>số nhà, tên đường, dòng địa chỉ chi tiết</t>
+  </si>
+  <si>
+    <t>địa chỉ đầy đủ, bao gồm xã/phường, quận/huyện, tỉnh/thành</t>
+  </si>
+  <si>
+    <t>mã chi nhánh quản lý trực tiếp khách hàng., code, mã, loại</t>
+  </si>
+  <si>
+    <t>ví dụ: đồng, bạc, vàng, kim cương, phân hạng khách hàng</t>
+  </si>
+  <si>
+    <t>trạng thái, kết quả, tình trạng, trạng thái hiện tại khách hàng, active, inactive, closed...</t>
+  </si>
+  <si>
+    <t>ngày cấp giấy tờ định danh, cmnd/cccd/hộ chiếu</t>
+  </si>
+  <si>
+    <t>địa chỉ thư điện tử khách hàng.</t>
+  </si>
+  <si>
+    <t>số điện thoại bàn/điện thoại cố định.</t>
+  </si>
+  <si>
+    <t>số định danh, số cmnd, cccd hoặc hộ chiếu, số, id, số giấy tờ định danh, mã</t>
+  </si>
+  <si>
+    <t>ví dụ: đã xác thực - ekyc, chưa xác thực, cấp độ định danh</t>
+  </si>
+  <si>
+    <t>ví dụ: "identity card", "passport", họ tên, tên, loại giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>thời gian, ngày, hôm, ngày khởi tạo thông tin khách hàng trên hệ thống., thời gian, ngày tháng, lịch sử, gần đây</t>
+  </si>
+  <si>
+    <t>đánh dấu khách hàng có thuộc diện mặc định thu phí hay không.</t>
+  </si>
+  <si>
+    <t>tọa độ vị trí nhà ở hoặc nơi đăng ký, vĩ độ</t>
+  </si>
+  <si>
+    <t>kinh độ, tọa độ vị trí</t>
+  </si>
+  <si>
+    <t>số điện thoại di động chính.</t>
+  </si>
+  <si>
+    <t>số định danh, số, id, ví dụ: vn, us, jp, mã quốc tịch, mã</t>
+  </si>
+  <si>
+    <t>số định danh, số, id, mã vùng/địa điểm cư trú., mã</t>
+  </si>
+  <si>
+    <t>ví dụ: ca tp. hà nội, nơi cấp giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>số định danh, thường đối soát liên hệ thống, số, id, mã định danh duy nhất, mã</t>
+  </si>
+  <si>
+    <t>giá trị đặc trưng định danh duy nhất khách hàng.</t>
+  </si>
+  <si>
+    <t>trạng thái bản ghi, ví dụ: 1-hiệu lực, 0-hết hiệu lực</t>
+  </si>
+  <si>
+    <t>đường dẫn hoặc dữ liệu chữ ký mẫu số 1 khách hàng.</t>
+  </si>
+  <si>
+    <t>đường dẫn hoặc dữ liệu chữ ký mẫu số 2.</t>
+  </si>
+  <si>
+    <t>giới tính, male, female, unknown</t>
+  </si>
+  <si>
+    <t>ngày tháng năm sinh., thời gian, ngày tháng, lịch sử, gần đây</t>
+  </si>
+  <si>
+    <t>trạng thái, trạng thái cũ khách hàng, kết quả, trước khi thay đổi, tình trạng</t>
+  </si>
+  <si>
+    <t>trạng thái mới khách hàng, trạng thái, kết quả, sau khi cập nhật, tình trạng</t>
+  </si>
+  <si>
+    <t>cmnd/cccd, đường dẫn ảnh mặt trước giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>đường dẫn ảnh mặt sau giấy tờ định danh.</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
@@ -535,24 +772,42 @@
     <t>{"raw_text": "SELECT * FROM customer WHERE customer_no = '{{customer_no}}'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE customer_name LIKE '%{{customer_name}}%'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE system_id = '{{system_id}}'"}</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE cif_branch = '{{cif_branch}}'"}</t>
   </si>
   <si>
-    <t>{"raw_text": "SELECT * FROM customer WHERE cif_type = '{{cif_type}}'"}</t>
+    <t>{"raw_text": "SELECT * FROM customer WHERE cif_type = '{{cif_type}}' AND new_customer_status = 'SUCCESS'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE address_line LIKE '%{{address_line}}%'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE full_address LIKE '%{{full_address}}%'"}</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE branch_code = '{{branch_code}}'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE customer_class LIKE '%{{customer_class}}%'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE customer_status = '{{customer_status}}'"}</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE date_of_issue = '{{date_of_issue}}'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE email LIKE '%{{email}}%'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE home_phone LIKE '%{{home_phone}}%'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE identify_id = '{{identify_id}}'"}</t>
   </si>
   <si>
@@ -565,7 +820,16 @@
     <t>{"raw_text": "SELECT * FROM customer WHERE init_date BETWEEN '{{start_date}}' AND '{{end_date}}' ORDER BY init_date DESC"}</t>
   </si>
   <si>
-    <t>{"raw_text": "SELECT SUM(is_fee_default) FROM customer WHERE cif_type = '{{cif_type}}'"}</t>
+    <t>{"raw_text": "SELECT SUM(is_fee_default) FROM customer WHERE new_customer_status = 'SUCCESS'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE latitude LIKE '%{{latitude}}%'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE longitude LIKE '%{{longitude}}%'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE mobile_phone LIKE '%{{mobile_phone}}%'"}</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE nationality_id = '{{nationality_id}}'"}</t>
@@ -586,6 +850,15 @@
     <t>{"raw_text": "SELECT * FROM customer WHERE status = '{{status}}'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE sign_1 LIKE '%{{sign_1}}%'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE sign_2 LIKE '%{{sign_2}}%'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE sex LIKE '%{{sex}}%'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE date_of_birth BETWEEN '{{start_date}}' AND '{{end_date}}' ORDER BY date_of_birth DESC"}</t>
   </si>
   <si>
@@ -599,9 +872,6 @@
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE unique_image_back = '{{unique_image_back}}'"}</t>
-  </si>
-  <si>
-    <t>{"raw_text": "SELECT * FROM customer WHERE cif_type = '{{cif_type}}' AND init_date BETWEEN '{{start_date}}' AND '{{end_date}}'"}</t>
   </si>
 </sst>
 </file>
@@ -959,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -984,16 +1254,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1001,16 +1271,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1018,16 +1288,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1035,50 +1305,50 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1086,16 +1356,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1103,16 +1373,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1120,16 +1390,16 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1137,16 +1407,16 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1154,16 +1424,16 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1171,16 +1441,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1188,16 +1458,16 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1205,16 +1475,16 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1222,33 +1492,33 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1256,169 +1526,169 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1426,16 +1696,203 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
         <v>49</v>
       </c>
-      <c r="C28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" t="s">
-        <v>130</v>
+      <c r="C36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t>document</t>
   </si>
@@ -31,113 +31,118 @@
     <t>metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">customer | Tra cứu </t>
+    <t>customer | Tra cứu primary key</t>
   </si>
   <si>
     <t>customer | Tra cứu mã khách hàng</t>
   </si>
   <si>
-    <t>customer | Tra cứu mã số khách hàng</t>
+    <t>customer | Tra cứu số khách hàng</t>
   </si>
   <si>
     <t>customer | Tra cứu chi nhánh mã khách hàng</t>
   </si>
   <si>
-    <t>customer | Lọc theo mã khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc thời gian</t>
+    <t>customer | Lọc theo loại mã khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc thời gian theo init date</t>
   </si>
   <si>
     <t>customer | Thống kê phí</t>
   </si>
   <si>
-    <t xml:space="preserve">customer | Lọc theo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tìm kiếm chính xác theo </t>
+    <t>customer | Lọc theo trạng thái bản ghi</t>
+  </si>
+  <si>
+    <t>customer | Lọc thời gian theo ngày tháng năm sinh.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo primary key</t>
   </si>
   <si>
     <t>Tìm kiếm chính xác theo mã khách hàng</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo mã số khách hàng</t>
+    <t>Tìm kiếm chính xác theo số khách hàng</t>
   </si>
   <si>
     <t>Tìm kiếm chính xác theo chi nhánh mã khách hàng</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo mã khách hàng</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo khách hàng</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử theo thời gian cụ thể</t>
+    <t>Phân nhóm giao dịch theo loại mã khách hàng</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái khách hàng</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột init date</t>
   </si>
   <si>
     <t>Tính tổng giá trị phí</t>
   </si>
   <si>
-    <t xml:space="preserve">Phân nhóm giao dịch theo </t>
-  </si>
-  <si>
-    <t>Check giao dịch 865
-Kiểm tra lệnh 865 đang ở trạng thái nào
-Tra cứu khách hàng 865 tuần này
-Xem chi tiết khách hàng số 865</t>
-  </si>
-  <si>
-    <t>Sao kê cho mã khách hàng 8062062
-Liệt kê giao dịch của khách hàng 8062062
-Xem lịch sử của mã khách hàng 8062062</t>
-  </si>
-  <si>
-    <t>Sao kê cho mã khách hàng 3647072
-Liệt kê giao dịch của khách hàng 3647072
-Xem lịch sử của mã khách hàng 3647072</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng 2252118
-Xem lịch sử của mã số khách hàng 2252118
-Sao kê cho mã số khách hàng 2252118</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của chi nhánh mã khách hàng TYPE_VK80
-Sao kê cho chi nhánh mã khách hàng TYPE_VK80
-Liệt kê giao dịch của khách hàng TYPE_VK80</t>
-  </si>
-  <si>
-    <t>danh sách khách hàng hóa đơn điện
-khách hàng hóa đơn điện
-lọc các khách hàng đang hóa đơn điện
-khách hàng napas 247
-khách hàng thanh toán qr
-danh sách khách hàng napas 247
-danh sách khách hàng thanh toán qr
-lọc các khách hàng đang napas 247
-lọc các khách hàng đang thanh toán qr</t>
-  </si>
-  <si>
-    <t>khách hàng bị treo
-danh sách khách hàng hoàn tất
+    <t>Phân nhóm giao dịch theo trạng thái bản ghi</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột ngày tháng năm sinh.</t>
+  </si>
+  <si>
+    <t>Kiểm tra lệnh 569 xem thành công chưa
+Check giao dịch 569
+Tra cứu khách hàng 569 hôm qua
+Xem chi tiết khách hàng số 569</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng 4781402
+Xem lịch sử của mã khách hàng 4781402
+Sao kê cho mã khách hàng 4781402</t>
+  </si>
+  <si>
+    <t>Sao kê cho mã khách hàng 8831657
+Xem lịch sử của mã khách hàng 8831657
+Liệt kê giao dịch của khách hàng 8831657</t>
+  </si>
+  <si>
+    <t>Sao kê cho số khách hàng 3226610
+Xem lịch sử của số khách hàng 3226610
+Liệt kê giao dịch của khách hàng 3226610</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của chi nhánh mã khách hàng CAT_5W39
+Liệt kê giao dịch của khách hàng CAT_5W39
+Sao kê cho chi nhánh mã khách hàng CAT_5W39</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang chuyển liên ngân hàng
+lọc các khách hàng đang chuyển nội bộ
+danh sách khách hàng chuyển liên ngân hàng
+khách hàng chuyển nhanh
+khách hàng chuyển liên ngân hàng
+khách hàng chuyển nội bộ
+danh sách khách hàng chuyển nhanh
+lọc các khách hàng đang chuyển nhanh
+danh sách khách hàng chuyển nội bộ</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang bị treo
+lọc các khách hàng đang đã xong
 danh sách khách hàng bị treo
-khách hàng hoàn tất
+khách hàng đã xong
+khách hàng treo
+danh sách khách hàng đã xong
+khách hàng bị treo
 danh sách khách hàng treo
-lọc các khách hàng đang treo
-lọc các khách hàng đang hoàn tất
-khách hàng treo
-lọc các khách hàng đang bị treo</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng từ ngày 2026-01-15 đến ngày 2026-01-29
-Lịch sử khách hàng trong khoảng 2026-01-15 - 2026-01-29
-Xem khách hàng từ 2026-01-15 tới 2026-01-29
-Tra soát giao dịch ngày 2026-01-15
-Xem khách hàng 30 ngày gần đây</t>
+lọc các khách hàng đang treo</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo init date từ ngày 2025-12-13 đến ngày 2026-01-29
+Lọc khách hàng có init date trong khoảng 2025-12-13 - 2026-01-29
+Xem lịch sử khách hàng dựa trên init date từ 2025-12-13 tới 2026-01-29
+Kiểm tra các khách hàng với init date là ngày 2025-12-13</t>
   </si>
   <si>
     <t>Tổng phí là bao nhiêu?
@@ -145,47 +150,46 @@
 Thống kê phí hôm nay</t>
   </si>
   <si>
-    <t>danh sách khách hàng hoàn tất
-khách hàng hoàn tất
+    <t>lọc các khách hàng đang bị treo
+lọc các khách hàng đang quá giờ
+lọc các khách hàng đang đã xong
+danh sách khách hàng bị treo
+danh sách khách hàng quá giờ
+khách hàng đã xong
+danh sách khách hàng đã xong
+khách hàng bị treo
+khách hàng quá giờ</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày tháng năm sinh. từ ngày 2025-12-05 đến ngày 2026-01-29
+Lọc khách hàng có ngày tháng năm sinh. trong khoảng 2025-12-05 - 2026-01-29
+Xem lịch sử khách hàng dựa trên ngày tháng năm sinh. từ 2025-12-05 tới 2026-01-29
+Kiểm tra các khách hàng với ngày tháng năm sinh. là ngày 2025-12-05</t>
+  </si>
+  <si>
+    <t>khách hàng hoàn tất
+danh sách khách hàng lỗi
+lọc các khách hàng đang lỗi
+khách hàng lỗi
+danh sách khách hàng hoàn tất
+lọc các khách hàng đang hoàn tất
+khách hàng treo
+danh sách khách hàng treo
+lọc các khách hàng đang treo</t>
+  </si>
+  <si>
+    <t>danh sách khách hàng xử lý
+danh sách khách hàng lỗi
+lọc các khách hàng đang quá giờ
+lọc các khách hàng đang lỗi
+khách hàng lỗi
 lọc các khách hàng đang xử lý
-danh sách khách hàng thất bại
-lọc các khách hàng đang hoàn tất
-lọc các khách hàng đang thất bại
-khách hàng thất bại
-danh sách khách hàng xử lý
-khách hàng xử lý</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng từ ngày 2026-01-12 đến ngày 2026-01-29
-Lịch sử khách hàng trong khoảng 2026-01-12 - 2026-01-29
-Xem khách hàng từ 2026-01-12 tới 2026-01-29
-Tra soát giao dịch ngày 2026-01-12
-Xem khách hàng 30 ngày gần đây</t>
-  </si>
-  <si>
-    <t>khách hàng bị treo
-khách hàng quá giờ
-danh sách khách hàng bị treo
-lọc các khách hàng đang xử lý
-lọc các khách hàng đang quá giờ
 danh sách khách hàng quá giờ
-danh sách khách hàng xử lý
 khách hàng xử lý
-lọc các khách hàng đang bị treo</t>
-  </si>
-  <si>
-    <t>khách hàng bị treo
-khách hàng quá giờ
-danh sách khách hàng hoàn tất
-danh sách khách hàng bị treo
-khách hàng hoàn tất
-lọc các khách hàng đang quá giờ
-lọc các khách hàng đang hoàn tất
-danh sách khách hàng quá giờ
-lọc các khách hàng đang bị treo</t>
-  </si>
-  <si>
-    <t>, primary key, mã</t>
+khách hàng quá giờ</t>
+  </si>
+  <si>
+    <t>primary key</t>
   </si>
   <si>
     <t>mã khách hàng, số cif, mã định danh khách hàng</t>
@@ -194,31 +198,34 @@
     <t>mã khách hàng, khách hàng</t>
   </si>
   <si>
-    <t>mã số khách hàng, số khách hàng, khách hàng</t>
+    <t>số khách hàng, khách hàng, mã số khách hàng</t>
   </si>
   <si>
     <t>chi nhánh mã khách hàng, mã khách hàng</t>
   </si>
   <si>
-    <t>mã khách hàng, loại mã khách hàng, loại cif</t>
-  </si>
-  <si>
-    <t>khách hàng, active, inactive, closed..., trạng thái khách hàng</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, ngày tháng</t>
+    <t>loại mã khách hàng, mã khách hàng, loại cif</t>
+  </si>
+  <si>
+    <t>trạng thái khách hàng, khách hàng, active, inactive, closed...</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, init date</t>
   </si>
   <si>
     <t>tổng, thống kê</t>
   </si>
   <si>
-    <t>, trạng thái, trạng thái bản ghi</t>
-  </si>
-  <si>
-    <t>khách hàng, trước khi thay đổi, trạng thái khách hàng, trạng thái cũ khách hàng</t>
-  </si>
-  <si>
-    <t>khách hàng, sau khi cập nhật, trạng thái khách hàng, trạng thái mới khách hàng</t>
+    <t>trạng thái bản ghi</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, ngày tháng năm sinh.</t>
+  </si>
+  <si>
+    <t>trạng thái khách hàng, khách hàng, trạng thái cũ khách hàng, trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>trạng thái khách hàng, khách hàng, trạng thái mới khách hàng, sau khi cập nhật</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
@@ -640,16 +647,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -657,16 +664,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -674,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -691,16 +698,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -708,16 +715,16 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -725,16 +732,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -742,16 +749,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -759,16 +766,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -776,16 +783,16 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -793,33 +800,33 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -827,16 +834,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -844,16 +851,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\proton-intern\javisAI\6804_ddq\Text2SQL_Template\output\generated_datasets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CD507E-DB55-4CA3-B83D-E616269BC7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>document</t>
   </si>
@@ -34,198 +40,216 @@
     <t>customer | Tra cứu primary key</t>
   </si>
   <si>
+    <t>customer | Tra cứu số mã khách hàng</t>
+  </si>
+  <si>
     <t>customer | Tra cứu mã khách hàng</t>
   </si>
   <si>
-    <t>customer | Tra cứu số khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu chi nhánh mã khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo loại mã khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo trạng thái khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc thời gian theo init date</t>
-  </si>
-  <si>
-    <t>customer | Thống kê phí</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo trạng thái bản ghi</t>
+    <t>customer | Tra cứu mã số khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu chi nhánh nơi mở/quản lý mã cif này.</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo loại cif</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái hiện khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc thời gian theo ngày khởi tạo khách hàng trên</t>
+  </si>
+  <si>
+    <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái</t>
   </si>
   <si>
     <t>customer | Lọc thời gian theo ngày tháng năm sinh.</t>
   </si>
   <si>
+    <t>customer | Lọc theo trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái mới khách hàng</t>
+  </si>
+  <si>
     <t>Tìm kiếm chính xác theo primary key</t>
   </si>
   <si>
+    <t>Tìm kiếm chính xác theo số mã khách hàng</t>
+  </si>
+  <si>
     <t>Tìm kiếm chính xác theo mã khách hàng</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo số khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo chi nhánh mã khách hàng</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo loại mã khách hàng</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái khách hàng</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử dựa trên cột init date</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị phí</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái bản ghi</t>
+    <t>Tìm kiếm chính xác theo mã số khách hàng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo chi nhánh nơi mở/quản lý mã cif này.</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo loại cif</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái hiện khách hàng</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột ngày khởi tạo khách hàng trên</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột ngày tháng năm sinh.</t>
   </si>
   <si>
-    <t>Kiểm tra lệnh 569 xem thành công chưa
-Check giao dịch 569
-Tra cứu khách hàng 569 hôm qua
-Xem chi tiết khách hàng số 569</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng 4781402
-Xem lịch sử của mã khách hàng 4781402
-Sao kê cho mã khách hàng 4781402</t>
-  </si>
-  <si>
-    <t>Sao kê cho mã khách hàng 8831657
-Xem lịch sử của mã khách hàng 8831657
-Liệt kê giao dịch của khách hàng 8831657</t>
-  </si>
-  <si>
-    <t>Sao kê cho số khách hàng 3226610
-Xem lịch sử của số khách hàng 3226610
-Liệt kê giao dịch của khách hàng 3226610</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của chi nhánh mã khách hàng CAT_5W39
-Liệt kê giao dịch của khách hàng CAT_5W39
-Sao kê cho chi nhánh mã khách hàng CAT_5W39</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang chuyển liên ngân hàng
-lọc các khách hàng đang chuyển nội bộ
-danh sách khách hàng chuyển liên ngân hàng
-khách hàng chuyển nhanh
-khách hàng chuyển liên ngân hàng
+    <t>Phân nhóm giao dịch theo trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái mới khách hàng</t>
+  </si>
+  <si>
+    <t>Xem chi tiết khách hàng số 374
+Tra cứu khách hàng 374
+Kiểm tra lệnh 374 đang ở trạng thái nào
+Check giao dịch 374</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của số mã khách hàng 2511676
+Sao kê cho số mã khách hàng 2511676
+Liệt kê giao dịch của khách hàng 2511676</t>
+  </si>
+  <si>
+    <t>Sao kê cho mã khách hàng 5025185
+Liệt kê giao dịch của khách hàng 5025185
+Xem lịch sử của mã khách hàng 5025185</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng 3416983
+Xem lịch sử của mã số khách hàng 3416983
+Sao kê cho mã số khách hàng 3416983</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng CAT_7Y79
+Xem lịch sử của chi nhánh nơi mở/quản lý mã cif này. CAT_7Y79
+Sao kê cho chi nhánh nơi mở/quản lý mã cif này. CAT_7Y79</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang chuyển nội bộ
 khách hàng chuyển nội bộ
-danh sách khách hàng chuyển nhanh
-lọc các khách hàng đang chuyển nhanh
-danh sách khách hàng chuyển nội bộ</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang bị treo
-lọc các khách hàng đang đã xong
+danh sách khách hàng chuyển nội bộ
+lọc các khách hàng đang tiền nước
+danh sách khách hàng hóa đơn điện
+khách hàng hóa đơn điện
+lọc các khách hàng đang hóa đơn điện
+danh sách khách hàng tiền nước
+khách hàng tiền nước</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang đã xong
+danh sách khách hàng đang chờ
+lọc các khách hàng đang lỗi
+khách hàng đang chờ
+lọc các khách hàng đang đang chờ
+danh sách khách hàng lỗi
+khách hàng lỗi
+khách hàng đã xong
+danh sách khách hàng đã xong</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2025-12-18 đến ngày 2026-02-03
+Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2025-12-18 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2025-12-18 tới 2026-02-03
+Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên là ngày 2025-12-18</t>
+  </si>
+  <si>
+    <t>Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không là bao nhiêu?
+Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không của các giao dịch thành công
+Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay</t>
+  </si>
+  <si>
+    <t>danh sách khách hàng treo
+lọc các khách hàng đang thành công
+khách hàng bị treo
+lọc các khách hàng đang bị treo
+lọc các khách hàng đang treo
+danh sách khách hàng thành công
 danh sách khách hàng bị treo
-khách hàng đã xong
-khách hàng treo
-danh sách khách hàng đã xong
+khách hàng thành công
+khách hàng treo</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày tháng năm sinh. từ ngày 2025-12-15 đến ngày 2026-02-03
+Lọc khách hàng có ngày tháng năm sinh. trong khoảng 2025-12-15 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày tháng năm sinh. từ 2025-12-15 tới 2026-02-03
+Kiểm tra các khách hàng với ngày tháng năm sinh. là ngày 2025-12-15</t>
+  </si>
+  <si>
+    <t>khách hàng xử lý
+lọc các khách hàng đang thành công
 khách hàng bị treo
-danh sách khách hàng treo
-lọc các khách hàng đang treo</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo init date từ ngày 2025-12-13 đến ngày 2026-01-29
-Lọc khách hàng có init date trong khoảng 2025-12-13 - 2026-01-29
-Xem lịch sử khách hàng dựa trên init date từ 2025-12-13 tới 2026-01-29
-Kiểm tra các khách hàng với init date là ngày 2025-12-13</t>
-  </si>
-  <si>
-    <t>Tổng phí là bao nhiêu?
-Tính tổng phí của các giao dịch thành công
-Thống kê phí hôm nay</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang bị treo
-lọc các khách hàng đang quá giờ
-lọc các khách hàng đang đã xong
+lọc các khách hàng đang bị treo
+danh sách khách hàng thành công
+danh sách khách hàng xử lý
 danh sách khách hàng bị treo
-danh sách khách hàng quá giờ
-khách hàng đã xong
-danh sách khách hàng đã xong
-khách hàng bị treo
-khách hàng quá giờ</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày tháng năm sinh. từ ngày 2025-12-05 đến ngày 2026-01-29
-Lọc khách hàng có ngày tháng năm sinh. trong khoảng 2025-12-05 - 2026-01-29
-Xem lịch sử khách hàng dựa trên ngày tháng năm sinh. từ 2025-12-05 tới 2026-01-29
-Kiểm tra các khách hàng với ngày tháng năm sinh. là ngày 2025-12-05</t>
-  </si>
-  <si>
-    <t>khách hàng hoàn tất
+khách hàng thành công
+lọc các khách hàng đang xử lý</t>
+  </si>
+  <si>
+    <t>danh sách khách hàng đang chờ
+lọc các khách hàng đang hết hạn
+danh sách khách hàng hết hạn
+khách hàng hết hạn
+lọc các khách hàng đang lỗi
+khách hàng đang chờ
+lọc các khách hàng đang đang chờ
 danh sách khách hàng lỗi
-lọc các khách hàng đang lỗi
-khách hàng lỗi
-danh sách khách hàng hoàn tất
-lọc các khách hàng đang hoàn tất
-khách hàng treo
-danh sách khách hàng treo
-lọc các khách hàng đang treo</t>
-  </si>
-  <si>
-    <t>danh sách khách hàng xử lý
-danh sách khách hàng lỗi
-lọc các khách hàng đang quá giờ
-lọc các khách hàng đang lỗi
-khách hàng lỗi
-lọc các khách hàng đang xử lý
-danh sách khách hàng quá giờ
-khách hàng xử lý
-khách hàng quá giờ</t>
-  </si>
-  <si>
-    <t>primary key</t>
-  </si>
-  <si>
-    <t>mã khách hàng, số cif, mã định danh khách hàng</t>
-  </si>
-  <si>
-    <t>mã khách hàng, khách hàng</t>
-  </si>
-  <si>
-    <t>số khách hàng, khách hàng, mã số khách hàng</t>
-  </si>
-  <si>
-    <t>chi nhánh mã khách hàng, mã khách hàng</t>
-  </si>
-  <si>
-    <t>loại mã khách hàng, mã khách hàng, loại cif</t>
-  </si>
-  <si>
-    <t>trạng thái khách hàng, khách hàng, active, inactive, closed...</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, init date</t>
+khách hàng lỗi</t>
+  </si>
+  <si>
+    <t>primary key, số, mã, id tự tăng, khóa chính, id tự tăng là khóa chính bản ghi này</t>
+  </si>
+  <si>
+    <t>số mã khách hàng, mã khách hàng, customer information file, số cif mã định danh duy nhất khách hàng ngân hàng, mã định danh khách hàng, số cif, số số khách hàng</t>
+  </si>
+  <si>
+    <t>mã khách hàng, id định danh khách hàng nội bộ., số khách hàng, id định danh khách hàng trong nội bộ</t>
+  </si>
+  <si>
+    <t>mã số khách hàng, số khách hàng, có thể khác với cif tùy theo cấu trúc hệ thống</t>
+  </si>
+  <si>
+    <t>chi nhánh nơi mở/quản lý mã cif này., chi nhánh nơi mở/quản lý mã cif này, số khách hàng chi nhánh, mã khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>loại cif, loại mã khách hàng, loại số khách hàng, ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên...</t>
+  </si>
+  <si>
+    <t>trạng thái hiện khách hàng, active, inactive, closed..., trạng thái hiện tại khách hàng, trạng thái khách hàng</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, ngày khởi tạo khách hàng trên</t>
   </si>
   <si>
     <t>tổng, thống kê</t>
   </si>
   <si>
-    <t>trạng thái bản ghi</t>
+    <t>trạng thái, ví dụ: 1-hiệu lực, 0-hết hiệu lực, trạng thái bản ghi</t>
   </si>
   <si>
     <t>thời gian, lịch sử, ngày tháng năm sinh.</t>
   </si>
   <si>
-    <t>trạng thái khách hàng, khách hàng, trạng thái cũ khách hàng, trước khi thay đổi</t>
-  </si>
-  <si>
-    <t>trạng thái khách hàng, khách hàng, trạng thái mới khách hàng, sau khi cập nhật</t>
+    <t>trước khi thay đổi, trạng thái old khách hàng, trạng thái cũ khách hàng</t>
+  </si>
+  <si>
+    <t>trạng thái mới khách hàng, sau khi cập nhật, trạng thái new khách hàng</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
@@ -270,8 +294,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,10 +347,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -334,13 +361,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -378,7 +413,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -412,6 +447,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -446,9 +482,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -621,11 +658,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="5" width="41.921875" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,225 +682,225 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="102" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D14" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>63</v>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\proton-intern\javisAI\6804_ddq\Text2SQL_Template\output\generated_datasets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CD507E-DB55-4CA3-B83D-E616269BC7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -37,219 +31,219 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>customer | Tra cứu primary key</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu số mã khách hàng</t>
+    <t>customer | Tra cứu bản ghi này</t>
   </si>
   <si>
     <t>customer | Tra cứu mã khách hàng</t>
   </si>
   <si>
-    <t>customer | Tra cứu mã số khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu chi nhánh nơi mở/quản lý mã cif này.</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo loại cif</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo trạng thái hiện khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc thời gian theo ngày khởi tạo khách hàng trên</t>
-  </si>
-  <si>
-    <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo trạng thái</t>
-  </si>
-  <si>
-    <t>customer | Lọc thời gian theo ngày tháng năm sinh.</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo trước khi thay đổi</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo trạng thái mới khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo primary key</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo số mã khách hàng</t>
+    <t>customer | Tra cứu id định danh khách hàng trong nội bộ</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu có thể khác với cif tùy theo cấu trúc hệ thống</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu mã khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo khách hàng ưu tiên...</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo khách hàng trạng thái</t>
+  </si>
+  <si>
+    <t>customer | Lọc thời gian theo ngày khởi tạo khách hàng trên hệ thống</t>
+  </si>
+  <si>
+    <t>customer | Thống kê trạng thái phí trạng thái</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo 0-hết hiệu lực</t>
+  </si>
+  <si>
+    <t>customer | Lọc thời gian theo ngày trạng thái trạng thái</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái old khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo sau khi cập nhật</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo bản ghi này</t>
   </si>
   <si>
     <t>Tìm kiếm chính xác theo mã khách hàng</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo mã số khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo chi nhánh nơi mở/quản lý mã cif này.</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo loại cif</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái hiện khách hàng</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử dựa trên cột ngày khởi tạo khách hàng trên</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử dựa trên cột ngày tháng năm sinh.</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trước khi thay đổi</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái mới khách hàng</t>
-  </si>
-  <si>
-    <t>Xem chi tiết khách hàng số 374
-Tra cứu khách hàng 374
-Kiểm tra lệnh 374 đang ở trạng thái nào
-Check giao dịch 374</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của số mã khách hàng 2511676
-Sao kê cho số mã khách hàng 2511676
-Liệt kê giao dịch của khách hàng 2511676</t>
-  </si>
-  <si>
-    <t>Sao kê cho mã khách hàng 5025185
-Liệt kê giao dịch của khách hàng 5025185
-Xem lịch sử của mã khách hàng 5025185</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng 3416983
-Xem lịch sử của mã số khách hàng 3416983
-Sao kê cho mã số khách hàng 3416983</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng CAT_7Y79
-Xem lịch sử của chi nhánh nơi mở/quản lý mã cif này. CAT_7Y79
-Sao kê cho chi nhánh nơi mở/quản lý mã cif này. CAT_7Y79</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang chuyển nội bộ
-khách hàng chuyển nội bộ
-danh sách khách hàng chuyển nội bộ
-lọc các khách hàng đang tiền nước
-danh sách khách hàng hóa đơn điện
-khách hàng hóa đơn điện
-lọc các khách hàng đang hóa đơn điện
-danh sách khách hàng tiền nước
-khách hàng tiền nước</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang đã xong
-danh sách khách hàng đang chờ
+    <t>Tìm kiếm chính xác theo id định danh khách hàng trong nội bộ</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo có thể khác với cif tùy theo cấu trúc hệ thống</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo mã khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo khách hàng ưu tiên...</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo khách hàng trạng thái</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột ngày khởi tạo khách hàng trên hệ thống</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị trạng thái phí trạng thái</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo 0-hết hiệu lực</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột ngày trạng thái trạng thái</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái old khách hàng</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo sau khi cập nhật</t>
+  </si>
+  <si>
+    <t>Tra cứu khách hàng 537
+Kiểm tra lệnh 537 xem thành công chưa
+Xem chi tiết khách hàng số 537
+Check giao dịch 537</t>
+  </si>
+  <si>
+    <t>Sao kê cho mã khách hàng 8481943
+Liệt kê giao dịch của khách hàng 8481943
+Xem lịch sử của mã khách hàng 8481943</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của id định danh khách hàng trong nội bộ 7231162
+Liệt kê giao dịch của khách hàng 7231162
+Sao kê cho id định danh khách hàng trong nội bộ 7231162</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của có thể khác với cif tùy theo cấu trúc hệ thống 6784867
+Liệt kê giao dịch của khách hàng 6784867
+Sao kê cho có thể khác với cif tùy theo cấu trúc hệ thống 6784867</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của mã khách hàng chi nhánh TYPE_V35G
+Sao kê cho mã khách hàng chi nhánh TYPE_V35G
+Liệt kê giao dịch của khách hàng TYPE_V35G</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang napas 247
+lọc các khách hàng đang nạp thẻ
+khách hàng napas 247
+danh sách khách hàng chuyển liên ngân hàng
+danh sách khách hàng nạp thẻ
+khách hàng chuyển liên ngân hàng
+khách hàng nạp thẻ
+danh sách khách hàng napas 247
+lọc các khách hàng đang chuyển liên ngân hàng</t>
+  </si>
+  <si>
+    <t>khách hàng xử lý
+lọc các khách hàng đang bị treo
+khách hàng thành công
+khách hàng bị treo
+danh sách khách hàng bị treo
+danh sách khách hàng xử lý
+lọc các khách hàng đang xử lý
+danh sách khách hàng thành công
+lọc các khách hàng đang thành công</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên hệ thống từ ngày 2025-12-11 đến ngày 2026-02-03
+Lọc khách hàng có ngày khởi tạo khách hàng trên hệ thống trong khoảng 2025-12-11 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên hệ thống từ 2025-12-11 tới 2026-02-03
+Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên hệ thống là ngày 2025-12-11</t>
+  </si>
+  <si>
+    <t>Tổng trạng thái phí trạng thái là bao nhiêu?
+Tính tổng trạng thái phí trạng thái của các giao dịch thành công
+Thống kê trạng thái phí trạng thái hôm nay</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang thất bại
+lọc các khách hàng đang quá giờ
+danh sách khách hàng quá giờ
+khách hàng quá giờ
+lọc các khách hàng đang treo
+khách hàng treo
+danh sách khách hàng treo
+khách hàng thất bại
+danh sách khách hàng thất bại</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-14 đến ngày 2026-02-03
+Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-14 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-14 tới 2026-02-03
+Kiểm tra các khách hàng với ngày trạng thái trạng thái là ngày 2025-12-14</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang thất bại
+khách hàng xử lý
+khách hàng thành công
+danh sách khách hàng xử lý
+lọc các khách hàng đang xử lý
+danh sách khách hàng thành công
+khách hàng thất bại
+danh sách khách hàng thất bại
+lọc các khách hàng đang thành công</t>
+  </si>
+  <si>
+    <t>lọc các khách hàng đang quá giờ
+khách hàng xử lý
+danh sách khách hàng quá giờ
+danh sách khách hàng xử lý
+lọc các khách hàng đang xử lý
+khách hàng quá giờ
 lọc các khách hàng đang lỗi
-khách hàng đang chờ
-lọc các khách hàng đang đang chờ
-danh sách khách hàng lỗi
 khách hàng lỗi
-khách hàng đã xong
-danh sách khách hàng đã xong</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2025-12-18 đến ngày 2026-02-03
-Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2025-12-18 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2025-12-18 tới 2026-02-03
-Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên là ngày 2025-12-18</t>
-  </si>
-  <si>
-    <t>Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không là bao nhiêu?
-Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không của các giao dịch thành công
-Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay</t>
-  </si>
-  <si>
-    <t>danh sách khách hàng treo
-lọc các khách hàng đang thành công
-khách hàng bị treo
-lọc các khách hàng đang bị treo
-lọc các khách hàng đang treo
-danh sách khách hàng thành công
-danh sách khách hàng bị treo
-khách hàng thành công
-khách hàng treo</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày tháng năm sinh. từ ngày 2025-12-15 đến ngày 2026-02-03
-Lọc khách hàng có ngày tháng năm sinh. trong khoảng 2025-12-15 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày tháng năm sinh. từ 2025-12-15 tới 2026-02-03
-Kiểm tra các khách hàng với ngày tháng năm sinh. là ngày 2025-12-15</t>
-  </si>
-  <si>
-    <t>khách hàng xử lý
-lọc các khách hàng đang thành công
-khách hàng bị treo
-lọc các khách hàng đang bị treo
-danh sách khách hàng thành công
-danh sách khách hàng xử lý
-danh sách khách hàng bị treo
-khách hàng thành công
-lọc các khách hàng đang xử lý</t>
-  </si>
-  <si>
-    <t>danh sách khách hàng đang chờ
-lọc các khách hàng đang hết hạn
-danh sách khách hàng hết hạn
-khách hàng hết hạn
-lọc các khách hàng đang lỗi
-khách hàng đang chờ
-lọc các khách hàng đang đang chờ
-danh sách khách hàng lỗi
-khách hàng lỗi</t>
-  </si>
-  <si>
-    <t>primary key, số, mã, id tự tăng, khóa chính, id tự tăng là khóa chính bản ghi này</t>
-  </si>
-  <si>
-    <t>số mã khách hàng, mã khách hàng, customer information file, số cif mã định danh duy nhất khách hàng ngân hàng, mã định danh khách hàng, số cif, số số khách hàng</t>
-  </si>
-  <si>
-    <t>mã khách hàng, id định danh khách hàng nội bộ., số khách hàng, id định danh khách hàng trong nội bộ</t>
-  </si>
-  <si>
-    <t>mã số khách hàng, số khách hàng, có thể khác với cif tùy theo cấu trúc hệ thống</t>
-  </si>
-  <si>
-    <t>chi nhánh nơi mở/quản lý mã cif này., chi nhánh nơi mở/quản lý mã cif này, số khách hàng chi nhánh, mã khách hàng chi nhánh</t>
-  </si>
-  <si>
-    <t>loại cif, loại mã khách hàng, loại số khách hàng, ví dụ: cá nhân, doanh nghiệp, khách hàng ưu tiên...</t>
-  </si>
-  <si>
-    <t>trạng thái hiện khách hàng, active, inactive, closed..., trạng thái hiện tại khách hàng, trạng thái khách hàng</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, ngày khởi tạo khách hàng trên</t>
+danh sách khách hàng lỗi</t>
+  </si>
+  <si>
+    <t>bản ghi này, mã, primary key, số, id tự tăng là khóa chính bản ghi này</t>
+  </si>
+  <si>
+    <t>mã khách hàng, số số khách hàng, số cif, số cif mã định danh duy nhất khách hàng ngân hàng, số mã khách hàng, customer information file, mã định danh khách hàng, số khách hàng</t>
+  </si>
+  <si>
+    <t>id định danh khách hàng trong nội bộ, mã khách hàng, số khách hàng, định danh khách hàng nội bộ</t>
+  </si>
+  <si>
+    <t>có thể khác với cif tùy theo cấu trúc hệ thống, số khách hàng, mã số khách hàng</t>
+  </si>
+  <si>
+    <t>mã khách hàng chi nhánh, chi nhánh nơi mở, quản lý mã cif này, số khách hàng chi nhánh, khách hàng chi nhánh, chi nhánh nơi mở/quản lý mã cif này</t>
+  </si>
+  <si>
+    <t>khách hàng ưu tiên..., loại mã khách hàng, cá nhân, loại số khách hàng, doanh nghiệp, loại khách hàng, loại cif</t>
+  </si>
+  <si>
+    <t>khách hàng trạng thái, inactive, closed..., active, trạng thái hiện khách hàng, trạng thái khách hàng</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, ngày khởi tạo khách hàng trên hệ thống</t>
   </si>
   <si>
     <t>tổng, thống kê</t>
   </si>
   <si>
-    <t>trạng thái, ví dụ: 1-hiệu lực, 0-hết hiệu lực, trạng thái bản ghi</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, ngày tháng năm sinh.</t>
-  </si>
-  <si>
-    <t>trước khi thay đổi, trạng thái old khách hàng, trạng thái cũ khách hàng</t>
-  </si>
-  <si>
-    <t>trạng thái mới khách hàng, sau khi cập nhật, trạng thái new khách hàng</t>
+    <t>0-hết hiệu lực, trạng thái bản ghi, 1-hiệu lực, trạng thái</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, ngày trạng thái trạng thái</t>
+  </si>
+  <si>
+    <t>trạng thái old khách hàng, trạng thái cũ khách hàng, trước khi thay đổi, người thụ hưởng khách hàng trạng thái</t>
+  </si>
+  <si>
+    <t>sau khi cập nhật, trạng thái mới khách hàng, nội dung khách hàng trạng thái, trạng thái new khách hàng</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
@@ -294,8 +288,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,13 +341,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -361,21 +352,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -413,7 +396,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -447,7 +430,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -482,10 +464,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -658,14 +639,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="5" width="41.921875" style="2" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,224 +660,224 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="102" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="82">
   <si>
     <t>document</t>
   </si>
@@ -31,219 +31,270 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>customer | Tra cứu bản ghi này</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu mã khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu id định danh khách hàng trong nội bộ</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu có thể khác với cif tùy theo cấu trúc hệ thống</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu mã khách hàng chi nhánh</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo khách hàng ưu tiên...</t>
+    <t>customer | Tra cứu mã</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu số mã khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu định danh khách hàng nội bộ</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu mã số khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu số khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo loại số khách hàng</t>
   </si>
   <si>
     <t>customer | Lọc theo khách hàng trạng thái</t>
   </si>
   <si>
-    <t>customer | Lọc thời gian theo ngày khởi tạo khách hàng trên hệ thống</t>
-  </si>
-  <si>
-    <t>customer | Thống kê trạng thái phí trạng thái</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo 0-hết hiệu lực</t>
+    <t>customer | Lọc thời gian theo ngày khởi tạo khách hàng trên</t>
+  </si>
+  <si>
+    <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo 1-hiệu lực</t>
   </si>
   <si>
     <t>customer | Lọc thời gian theo ngày trạng thái trạng thái</t>
   </si>
   <si>
-    <t>customer | Lọc theo trạng thái old khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo sau khi cập nhật</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo bản ghi này</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo id định danh khách hàng trong nội bộ</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo có thể khác với cif tùy theo cấu trúc hệ thống</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã khách hàng chi nhánh</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo khách hàng ưu tiên...</t>
+    <t>customer | Lọc theo trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái new khách hàng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo mã</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số mã khách hàng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo định danh khách hàng nội bộ</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo mã số khách hàng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo loại số khách hàng</t>
   </si>
   <si>
     <t>Phân nhóm giao dịch theo khách hàng trạng thái</t>
   </si>
   <si>
-    <t>Truy vấn lịch sử dựa trên cột ngày khởi tạo khách hàng trên hệ thống</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị trạng thái phí trạng thái</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo 0-hết hiệu lực</t>
+    <t>Truy vấn lịch sử dựa trên cột ngày khởi tạo khách hàng trên</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo 1-hiệu lực</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột ngày trạng thái trạng thái</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo trạng thái old khách hàng</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo sau khi cập nhật</t>
-  </si>
-  <si>
-    <t>Tra cứu khách hàng 537
-Kiểm tra lệnh 537 xem thành công chưa
-Xem chi tiết khách hàng số 537
-Check giao dịch 537</t>
-  </si>
-  <si>
-    <t>Sao kê cho mã khách hàng 8481943
-Liệt kê giao dịch của khách hàng 8481943
-Xem lịch sử của mã khách hàng 8481943</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của id định danh khách hàng trong nội bộ 7231162
-Liệt kê giao dịch của khách hàng 7231162
-Sao kê cho id định danh khách hàng trong nội bộ 7231162</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của có thể khác với cif tùy theo cấu trúc hệ thống 6784867
-Liệt kê giao dịch của khách hàng 6784867
-Sao kê cho có thể khác với cif tùy theo cấu trúc hệ thống 6784867</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của mã khách hàng chi nhánh TYPE_V35G
-Sao kê cho mã khách hàng chi nhánh TYPE_V35G
-Liệt kê giao dịch của khách hàng TYPE_V35G</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang napas 247
-lọc các khách hàng đang nạp thẻ
-khách hàng napas 247
-danh sách khách hàng chuyển liên ngân hàng
-danh sách khách hàng nạp thẻ
-khách hàng chuyển liên ngân hàng
-khách hàng nạp thẻ
-danh sách khách hàng napas 247
-lọc các khách hàng đang chuyển liên ngân hàng</t>
-  </si>
-  <si>
-    <t>khách hàng xử lý
-lọc các khách hàng đang bị treo
+    <t>Phân nhóm giao dịch theo trước khi thay đổi</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái new khách hàng</t>
+  </si>
+  <si>
+    <t>Search khách hàng 591 hôm nay
+Kiểm tra lệnh 591 đang ở trạng thái nào
+Search chi tiết khách hàng số 591
+Check giao dịch 591</t>
+  </si>
+  <si>
+    <t>Search khách hàng 840 hôm nay
+Check giao dịch 840
+Kiểm tra lệnh 840 đang ở trạng thái nào
+Search chi tiết khách hàng số 840</t>
+  </si>
+  <si>
+    <t>Sao kê cho số mã khách hàng 1016000
+Danh sách giao dịch của khách hàng 1016000
+Xem lịch sử của số mã khách hàng 1016000</t>
+  </si>
+  <si>
+    <t>Các giao dịch của khách hàng 6912068
+Xem lịch sử của số mã khách hàng 6912068
+Sao kê cho số mã khách hàng 6912068</t>
+  </si>
+  <si>
+    <t>Các giao dịch của khách hàng 5492284
+Xem lịch sử của định danh khách hàng nội bộ 5492284
+Sao kê cho định danh khách hàng nội bộ 5492284</t>
+  </si>
+  <si>
+    <t>Sao kê cho định danh khách hàng nội bộ 3381737
+Xem lịch sử của định danh khách hàng nội bộ 3381737
+Danh sách giao dịch của khách hàng 3381737</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của mã số khách hàng 3396081
+Sao kê cho mã số khách hàng 3396081
+Danh sách giao dịch của khách hàng 3396081</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của mã số khách hàng 6288255
+Sao kê cho mã số khách hàng 6288255
+Các giao dịch của khách hàng 6288255</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của số khách hàng chi nhánh TYPE_SX80
+Sao kê cho số khách hàng chi nhánh TYPE_SX80
+Những giao dịch của khách hàng TYPE_SX80</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của số khách hàng chi nhánh GRP_XLE4
+Những giao dịch của khách hàng GRP_XLE4
+Sao kê cho số khách hàng chi nhánh GRP_XLE4</t>
+  </si>
+  <si>
+    <t>Hiển thị khách hàng theo loại số khách hàng hóa đơn điện
+Hiển thị những khách hàng có loại số khách hàng là hóa đơn điện</t>
+  </si>
+  <si>
+    <t>Liệt kê khách hàng theo loại số khách hàng hóa đơn nước
+Liệt kê những khách hàng có loại số khách hàng là hóa đơn nước</t>
+  </si>
+  <si>
+    <t>Những những khách hàng có khách hàng trạng thái là hết hạn
+Những khách hàng theo khách hàng trạng thái hết hạn</t>
+  </si>
+  <si>
+    <t>Kiểm tra danh sách khách hàng là lỗi
+Tra cứu danh sách khách hàng là quá giờ
+Tra cứu các khách hàng quá giờ
+khách hàng lỗi
+khách hàng quá giờ
+Kiểm tra các khách hàng lỗi
+khách hàng đã xong
+Search các khách hàng đã xong
+Search danh sách khách hàng là đã xong</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2026-01-22 đến ngày 2026-02-03
+Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2026-01-22 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2026-01-22 tới 2026-02-03
+Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên là ngày 2026-01-22</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2026-01-12 đến ngày 2026-02-03
+Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2026-01-12 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2026-01-12 tới 2026-02-03
+Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên là ngày 2026-01-12</t>
+  </si>
+  <si>
+    <t>Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không là bao nhiêu?
+Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không của các giao dịch thành công
+Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay</t>
+  </si>
+  <si>
+    <t>Những khách hàng theo 1-hiệu lực đã xong
+Những những khách hàng có 1-hiệu lực là đã xong</t>
+  </si>
+  <si>
+    <t>Kiểm tra danh sách khách hàng là hết hạn
+Kiểm tra các khách hàng hết hạn
+Search danh sách khách hàng là bị treo
+Danh sách các khách hàng hoàn tất
+Search các khách hàng bị treo
+khách hàng hết hạn
+khách hàng bị treo
+Danh sách danh sách khách hàng là hoàn tất
+khách hàng hoàn tất</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-23 đến ngày 2026-02-03
+Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-23 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-23 tới 2026-02-03
+Kiểm tra các khách hàng với ngày trạng thái trạng thái là ngày 2025-12-23</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-10 đến ngày 2026-02-03
+Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-10 - 2026-02-03
+Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-10 tới 2026-02-03
+Kiểm tra các khách hàng với ngày trạng thái trạng thái là ngày 2025-12-10</t>
+  </si>
+  <si>
+    <t>Lọc các những khách hàng có trước khi thay đổi là quá giờ
+Lọc các khách hàng theo trước khi thay đổi quá giờ</t>
+  </si>
+  <si>
+    <t>Các các khách hàng hết hạn
 khách hàng thành công
+khách hàng xử lý
+Các danh sách khách hàng là hết hạn
+Tìm danh sách khách hàng là xử lý
+khách hàng hết hạn
+Tra cứu danh sách khách hàng là thành công
+Tìm các khách hàng xử lý
+Tra cứu các khách hàng thành công</t>
+  </si>
+  <si>
+    <t>Cho tôi xem những khách hàng có trạng thái new khách hàng là thành công
+Cho tôi xem khách hàng theo trạng thái new khách hàng thành công</t>
+  </si>
+  <si>
+    <t>Cho tôi xem các khách hàng xử lý
+Tìm các khách hàng bị treo
+khách hàng thành công
+Cho tôi xem danh sách khách hàng là xử lý
+Xem chi tiết danh sách khách hàng là thành công
+khách hàng xử lý
 khách hàng bị treo
-danh sách khách hàng bị treo
-danh sách khách hàng xử lý
-lọc các khách hàng đang xử lý
-danh sách khách hàng thành công
-lọc các khách hàng đang thành công</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên hệ thống từ ngày 2025-12-11 đến ngày 2026-02-03
-Lọc khách hàng có ngày khởi tạo khách hàng trên hệ thống trong khoảng 2025-12-11 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên hệ thống từ 2025-12-11 tới 2026-02-03
-Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên hệ thống là ngày 2025-12-11</t>
-  </si>
-  <si>
-    <t>Tổng trạng thái phí trạng thái là bao nhiêu?
-Tính tổng trạng thái phí trạng thái của các giao dịch thành công
-Thống kê trạng thái phí trạng thái hôm nay</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang thất bại
-lọc các khách hàng đang quá giờ
-danh sách khách hàng quá giờ
-khách hàng quá giờ
-lọc các khách hàng đang treo
-khách hàng treo
-danh sách khách hàng treo
-khách hàng thất bại
-danh sách khách hàng thất bại</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-14 đến ngày 2026-02-03
-Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-14 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-14 tới 2026-02-03
-Kiểm tra các khách hàng với ngày trạng thái trạng thái là ngày 2025-12-14</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang thất bại
-khách hàng xử lý
-khách hàng thành công
-danh sách khách hàng xử lý
-lọc các khách hàng đang xử lý
-danh sách khách hàng thành công
-khách hàng thất bại
-danh sách khách hàng thất bại
-lọc các khách hàng đang thành công</t>
-  </si>
-  <si>
-    <t>lọc các khách hàng đang quá giờ
-khách hàng xử lý
-danh sách khách hàng quá giờ
-danh sách khách hàng xử lý
-lọc các khách hàng đang xử lý
-khách hàng quá giờ
-lọc các khách hàng đang lỗi
-khách hàng lỗi
-danh sách khách hàng lỗi</t>
-  </si>
-  <si>
-    <t>bản ghi này, mã, primary key, số, id tự tăng là khóa chính bản ghi này</t>
-  </si>
-  <si>
-    <t>mã khách hàng, số số khách hàng, số cif, số cif mã định danh duy nhất khách hàng ngân hàng, số mã khách hàng, customer information file, mã định danh khách hàng, số khách hàng</t>
-  </si>
-  <si>
-    <t>id định danh khách hàng trong nội bộ, mã khách hàng, số khách hàng, định danh khách hàng nội bộ</t>
-  </si>
-  <si>
-    <t>có thể khác với cif tùy theo cấu trúc hệ thống, số khách hàng, mã số khách hàng</t>
-  </si>
-  <si>
-    <t>mã khách hàng chi nhánh, chi nhánh nơi mở, quản lý mã cif này, số khách hàng chi nhánh, khách hàng chi nhánh, chi nhánh nơi mở/quản lý mã cif này</t>
-  </si>
-  <si>
-    <t>khách hàng ưu tiên..., loại mã khách hàng, cá nhân, loại số khách hàng, doanh nghiệp, loại khách hàng, loại cif</t>
-  </si>
-  <si>
-    <t>khách hàng trạng thái, inactive, closed..., active, trạng thái hiện khách hàng, trạng thái khách hàng</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, ngày khởi tạo khách hàng trên hệ thống</t>
-  </si>
-  <si>
-    <t>tổng, thống kê</t>
-  </si>
-  <si>
-    <t>0-hết hiệu lực, trạng thái bản ghi, 1-hiệu lực, trạng thái</t>
+Xem chi tiết các khách hàng thành công
+Tìm danh sách khách hàng là bị treo</t>
+  </si>
+  <si>
+    <t>mã, id tự tăng là khóa chính bản ghi này, số, bản ghi này, primary key</t>
+  </si>
+  <si>
+    <t>số mã khách hàng, mã khách hàng, customer information file, số cif, số khách hàng, mã định danh khách hàng, số số khách hàng, số cif mã định danh duy nhất khách hàng ngân hàng</t>
+  </si>
+  <si>
+    <t>định danh khách hàng nội bộ, id định danh khách hàng trong nội bộ, số khách hàng, mã khách hàng</t>
+  </si>
+  <si>
+    <t>mã số khách hàng, số khách hàng, có thể khác với cif tùy theo cấu trúc hệ thống</t>
+  </si>
+  <si>
+    <t>số khách hàng chi nhánh, khách hàng chi nhánh, quản lý mã cif này, chi nhánh nơi mở, mã khách hàng chi nhánh, chi nhánh nơi mở/quản lý mã cif này</t>
+  </si>
+  <si>
+    <t>loại số khách hàng, loại mã khách hàng, loại cif, khách hàng ưu tiên..., loại khách hàng, doanh nghiệp, cá nhân</t>
+  </si>
+  <si>
+    <t>khách hàng trạng thái, trạng thái khách hàng, trạng thái hiện khách hàng, inactive, closed..., active</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, ngày khởi tạo khách hàng trên</t>
+  </si>
+  <si>
+    <t>tổng, thống kê, theo đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
+  </si>
+  <si>
+    <t>1-hiệu lực, trạng thái bản ghi, trạng thái, 0-hết hiệu lực</t>
   </si>
   <si>
     <t>thời gian, lịch sử, ngày trạng thái trạng thái</t>
   </si>
   <si>
-    <t>trạng thái old khách hàng, trạng thái cũ khách hàng, trước khi thay đổi, người thụ hưởng khách hàng trạng thái</t>
-  </si>
-  <si>
-    <t>sau khi cập nhật, trạng thái mới khách hàng, nội dung khách hàng trạng thái, trạng thái new khách hàng</t>
+    <t>trước khi thay đổi, người thụ hưởng khách hàng trạng thái, trạng thái cũ khách hàng, trạng thái old khách hàng</t>
+  </si>
+  <si>
+    <t>trạng thái new khách hàng, nội dung khách hàng trạng thái, sau khi cập nhật, trạng thái mới khách hàng</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
@@ -640,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -671,214 +722,435 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>document</t>
   </si>
@@ -31,25 +31,34 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>customer | Tra cứu mã</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu số mã khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu định danh khách hàng nội bộ</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu mã số khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu số khách hàng chi nhánh</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo loại số khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc theo khách hàng trạng thái</t>
+    <t>customer | Tra cứu customer information file</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu id định danh khách hàng trong nội bộ</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu có thể khác với cif tùy theo cấu trúc hệ thống</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo họ và tên đầy đủ khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu quản lý mã cif</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo khách hàng ưu tiên...</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo address line</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu mã chi nhánh quản lý trực tiếp khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo inactive</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu ngày cấp giấy tờ định danh</t>
   </si>
   <si>
     <t>customer | Lọc thời gian theo ngày khởi tạo khách hàng trên</t>
@@ -58,37 +67,58 @@
     <t>customer | Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
   </si>
   <si>
-    <t>customer | Lọc theo 1-hiệu lực</t>
+    <t>customer | Tra cứu place of issue</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu trạng thái số tiền</t>
+  </si>
+  <si>
+    <t>customer | Lọc theo trạng thái</t>
   </si>
   <si>
     <t>customer | Lọc thời gian theo ngày trạng thái trạng thái</t>
   </si>
   <si>
-    <t>customer | Lọc theo trước khi thay đổi</t>
+    <t>customer | Lọc theo người thụ hưởng khách hàng trạng thái</t>
   </si>
   <si>
     <t>customer | Lọc theo trạng thái new khách hàng</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo mã</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo số mã khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo định danh khách hàng nội bộ</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã số khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo số khách hàng chi nhánh</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo loại số khách hàng</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo khách hàng trạng thái</t>
+    <t>customer | Tra cứu unique image front</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu unique image back</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo customer information file</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo id định danh khách hàng trong nội bộ</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo có thể khác với cif tùy theo cấu trúc hệ thống</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo họ và tên đầy đủ khách hàng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo quản lý mã cif</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo khách hàng ưu tiên...</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo address line</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo mã chi nhánh quản lý trực tiếp khách hàng</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo inactive</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo ngày cấp giấy tờ định danh</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột ngày khởi tạo khách hàng trên</t>
@@ -97,186 +127,282 @@
     <t>Tính tổng giá trị đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo 1-hiệu lực</t>
+    <t>Tìm kiếm chính xác theo place of issue</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo trạng thái số tiền</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột ngày trạng thái trạng thái</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo trước khi thay đổi</t>
+    <t>Phân nhóm giao dịch theo người thụ hưởng khách hàng trạng thái</t>
   </si>
   <si>
     <t>Phân nhóm giao dịch theo trạng thái new khách hàng</t>
   </si>
   <si>
-    <t>Search khách hàng 591 hôm nay
-Kiểm tra lệnh 591 đang ở trạng thái nào
-Search chi tiết khách hàng số 591
-Check giao dịch 591</t>
-  </si>
-  <si>
-    <t>Search khách hàng 840 hôm nay
-Check giao dịch 840
-Kiểm tra lệnh 840 đang ở trạng thái nào
-Search chi tiết khách hàng số 840</t>
-  </si>
-  <si>
-    <t>Sao kê cho số mã khách hàng 1016000
-Danh sách giao dịch của khách hàng 1016000
-Xem lịch sử của số mã khách hàng 1016000</t>
-  </si>
-  <si>
-    <t>Các giao dịch của khách hàng 6912068
-Xem lịch sử của số mã khách hàng 6912068
-Sao kê cho số mã khách hàng 6912068</t>
-  </si>
-  <si>
-    <t>Các giao dịch của khách hàng 5492284
-Xem lịch sử của định danh khách hàng nội bộ 5492284
-Sao kê cho định danh khách hàng nội bộ 5492284</t>
-  </si>
-  <si>
-    <t>Sao kê cho định danh khách hàng nội bộ 3381737
-Xem lịch sử của định danh khách hàng nội bộ 3381737
-Danh sách giao dịch của khách hàng 3381737</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của mã số khách hàng 3396081
-Sao kê cho mã số khách hàng 3396081
-Danh sách giao dịch của khách hàng 3396081</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của mã số khách hàng 6288255
-Sao kê cho mã số khách hàng 6288255
-Các giao dịch của khách hàng 6288255</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của số khách hàng chi nhánh TYPE_SX80
-Sao kê cho số khách hàng chi nhánh TYPE_SX80
-Những giao dịch của khách hàng TYPE_SX80</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của số khách hàng chi nhánh GRP_XLE4
-Những giao dịch của khách hàng GRP_XLE4
-Sao kê cho số khách hàng chi nhánh GRP_XLE4</t>
-  </si>
-  <si>
-    <t>Hiển thị khách hàng theo loại số khách hàng hóa đơn điện
-Hiển thị những khách hàng có loại số khách hàng là hóa đơn điện</t>
-  </si>
-  <si>
-    <t>Liệt kê khách hàng theo loại số khách hàng hóa đơn nước
-Liệt kê những khách hàng có loại số khách hàng là hóa đơn nước</t>
-  </si>
-  <si>
-    <t>Những những khách hàng có khách hàng trạng thái là hết hạn
-Những khách hàng theo khách hàng trạng thái hết hạn</t>
-  </si>
-  <si>
-    <t>Kiểm tra danh sách khách hàng là lỗi
-Tra cứu danh sách khách hàng là quá giờ
-Tra cứu các khách hàng quá giờ
-khách hàng lỗi
+    <t>Tìm kiếm chính xác theo unique image front</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo unique image back</t>
+  </si>
+  <si>
+    <t>Vui lòng Liệt kê thông tin chi tiết của khách hàng có customer information file là 2041164
+Check customer information file 2041164
+Tìm kiếm khách hàng ứng với số 2041164
+Tra cứu khách hàng 2041164
+Xem chi tiết 2041164
+Thông tin về khách hàng số 2041164
+Hãy hiển thị dữ liệu bản ghi khách hàng với customer information file 2041164
+Search customer information file 2041164 là của ai?
+Liệt kê khách hàng theo customer information file 2041164</t>
+  </si>
+  <si>
+    <t>Vui lòng Search thông tin chi tiết của khách hàng có id định danh khách hàng trong nội bộ là 7658264
+Hiển thị khách hàng theo id định danh khách hàng trong nội bộ 7658264
+Xem chi tiết 7658264
+Check id định danh khách hàng trong nội bộ 7658264
+Kiểm tra khách hàng 7658264
+Tìm kiếm khách hàng ứng với số 7658264
+Hãy hiển thị dữ liệu bản ghi khách hàng với id định danh khách hàng trong nội bộ 7658264
+Thông tin về khách hàng số 7658264
+Kiểm tra id định danh khách hàng trong nội bộ 7658264 là của ai?</t>
+  </si>
+  <si>
+    <t>Check có thể khác với cif tùy theo cấu trúc hệ thống 1093818
+Xem chi tiết 1093818
+Thông tin về khách hàng số 1093818
+Search có thể khác với cif tùy theo cấu trúc hệ thống 1093818 là của ai?
+Tìm khách hàng theo có thể khác với cif tùy theo cấu trúc hệ thống 1093818
+Hãy hiển thị dữ liệu bản ghi khách hàng với có thể khác với cif tùy theo cấu trúc hệ thống 1093818
+Tìm kiếm khách hàng ứng với số 1093818
+Vui lòng Tìm thông tin chi tiết của khách hàng có có thể khác với cif tùy theo cấu trúc hệ thống là 1093818
+Hiển thị khách hàng 1093818</t>
+  </si>
+  <si>
+    <t>Trích xuất báo cáo các khách hàng thuộc loại CAT_VUEL
+Những khách hàng nào là CAT_VUEL?
+Cho xem danh sách khách hàng CAT_VUEL
+Tìm tất cả khách hàng loại CAT_VUEL
+Lọc các khách hàng đang ở trạng thái CAT_VUEL
+Danh sách CAT_VUEL
+Hãy liệt kê danh sách các khách hàng có họ và tên đầy đủ khách hàng là CAT_VUEL</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với quản lý mã cif MODE_JNWQ
+Vui lòng Tra cứu thông tin chi tiết của khách hàng có quản lý mã cif là MODE_JNWQ
+Xem chi tiết khách hàng MODE_JNWQ
+Kiểm tra khách hàng theo quản lý mã cif MODE_JNWQ
+Tìm kiếm khách hàng ứng với số MODE_JNWQ
+Tra cứu quản lý mã cif MODE_JNWQ là của ai?
+Thông tin về khách hàng số MODE_JNWQ
+Xem chi tiết MODE_JNWQ
+Check quản lý mã cif MODE_JNWQ</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào là hóa đơn nước?
+Lọc các khách hàng đang ở trạng thái hóa đơn nước
+Tìm tất cả khách hàng loại hóa đơn nước
+Hãy liệt kê danh sách các khách hàng có khách hàng ưu tiên... là hóa đơn nước
+Cho xem danh sách khách hàng hóa đơn nước
+Danh sách hóa đơn nước
+Trích xuất báo cáo các khách hàng thuộc loại hóa đơn nước</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào là TYPE_AVHP?
+Danh sách TYPE_AVHP
+Cho xem danh sách khách hàng TYPE_AVHP
+Hãy liệt kê danh sách các khách hàng có address line là TYPE_AVHP
+Lọc các khách hàng đang ở trạng thái TYPE_AVHP
+Trích xuất báo cáo các khách hàng thuộc loại TYPE_AVHP
+Tìm tất cả khách hàng loại TYPE_AVHP</t>
+  </si>
+  <si>
+    <t>Xem chi tiết khách hàng theo mã chi nhánh quản lý trực tiếp khách hàng hóa đơn điện
+Tìm kiếm khách hàng ứng với số hóa đơn điện
+Xem chi tiết hóa đơn điện
+Vui lòng Search thông tin chi tiết của khách hàng có mã chi nhánh quản lý trực tiếp khách hàng là hóa đơn điện
+Hãy hiển thị dữ liệu bản ghi khách hàng với mã chi nhánh quản lý trực tiếp khách hàng hóa đơn điện
+Check mã chi nhánh quản lý trực tiếp khách hàng hóa đơn điện
+Kiểm tra khách hàng hóa đơn điện
+Thông tin về khách hàng số hóa đơn điện
+Kiểm tra mã chi nhánh quản lý trực tiếp khách hàng hóa đơn điện là của ai?</t>
+  </si>
+  <si>
+    <t>Liệt kê các khách hàng hết hạn
+Những khách hàng nào là hết hạn?
+Những các khách hàng đang chờ
+khách hàng đang chờ
+Kiểm tra danh sách khách hàng là thất bại
+Hãy liệt kê danh sách các khách hàng có inactive là hết hạn
+Lọc các khách hàng đang ở trạng thái hết hạn
+Cho xem danh sách khách hàng hết hạn
+khách hàng thất bại
+Danh sách hết hạn
+Trích xuất báo cáo các khách hàng thuộc loại hết hạn
+Những danh sách khách hàng là đang chờ
+Kiểm tra các khách hàng thất bại
+Tìm tất cả khách hàng loại hết hạn
+khách hàng hết hạn
+Liệt kê danh sách khách hàng là hết hạn</t>
+  </si>
+  <si>
+    <t>Liệt kê khách hàng 2025-10-23
+Xem chi tiết 2025-10-23
+Xem chi tiết khách hàng theo ngày cấp giấy tờ định danh 2025-10-23
+Thông tin về khách hàng số 2025-10-23
+Tra cứu ngày cấp giấy tờ định danh 2025-10-23 là của ai?
+Check ngày cấp giấy tờ định danh 2025-10-23
+Vui lòng Xem chi tiết thông tin chi tiết của khách hàng có ngày cấp giấy tờ định danh là 2025-10-23
+Tìm kiếm khách hàng ứng với số 2025-10-23
+Hãy hiển thị dữ liệu bản ghi khách hàng với ngày cấp giấy tờ định danh 2025-10-23</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2026-01-14 đến ngày 2026-02-05
+Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2026-01-14 - 2026-02-05
+Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2026-01-14 tới 2026-02-05</t>
+  </si>
+  <si>
+    <t>Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không là bao nhiêu?
+Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không
+Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay</t>
+  </si>
+  <si>
+    <t>Vui lòng Cho tôi xem thông tin chi tiết của khách hàng có place of issue là TYPE_VO25
+Hiển thị place of issue TYPE_VO25 là của ai?
+Thông tin về khách hàng số TYPE_VO25
+Cho tôi xem khách hàng TYPE_VO25
+Xem chi tiết khách hàng theo place of issue TYPE_VO25
+Check place of issue TYPE_VO25
+Hãy hiển thị dữ liệu bản ghi khách hàng với place of issue TYPE_VO25
+Tìm kiếm khách hàng ứng với số TYPE_VO25
+Xem chi tiết TYPE_VO25</t>
+  </si>
+  <si>
+    <t>Vui lòng Kiểm tra thông tin chi tiết của khách hàng có trạng thái số tiền là GRP_J0AH
+Xem chi tiết GRP_J0AH
+Tra cứu trạng thái số tiền GRP_J0AH là của ai?
+Check trạng thái số tiền GRP_J0AH
+Tìm kiếm khách hàng ứng với số GRP_J0AH
+Hiển thị khách hàng theo trạng thái số tiền GRP_J0AH
+Thông tin về khách hàng số GRP_J0AH
+Hãy hiển thị dữ liệu bản ghi khách hàng với trạng thái số tiền GRP_J0AH
+Kiểm tra khách hàng GRP_J0AH</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách khách hàng là quá giờ
+Kiểm tra các khách hàng treo
+Kiểm tra danh sách khách hàng là treo
+Liệt kê các khách hàng đã xong
 khách hàng quá giờ
-Kiểm tra các khách hàng lỗi
-khách hàng đã xong
-Search các khách hàng đã xong
-Search danh sách khách hàng là đã xong</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2026-01-22 đến ngày 2026-02-03
-Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2026-01-22 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2026-01-22 tới 2026-02-03
-Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên là ngày 2026-01-22</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2026-01-12 đến ngày 2026-02-03
-Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2026-01-12 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2026-01-12 tới 2026-02-03
-Kiểm tra các khách hàng với ngày khởi tạo khách hàng trên là ngày 2026-01-12</t>
-  </si>
-  <si>
-    <t>Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không là bao nhiêu?
-Tính tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không của các giao dịch thành công
-Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay</t>
-  </si>
-  <si>
-    <t>Những khách hàng theo 1-hiệu lực đã xong
-Những những khách hàng có 1-hiệu lực là đã xong</t>
-  </si>
-  <si>
-    <t>Kiểm tra danh sách khách hàng là hết hạn
-Kiểm tra các khách hàng hết hạn
-Search danh sách khách hàng là bị treo
-Danh sách các khách hàng hoàn tất
-Search các khách hàng bị treo
+khách hàng treo
+Lọc các khách hàng đang ở trạng thái hết hạn
+Những khách hàng nào là hết hạn?
+Cho xem danh sách khách hàng hết hạn
+Danh sách hết hạn
+Hiển thị các khách hàng quá giờ
+Trích xuất báo cáo các khách hàng thuộc loại hết hạn
+Hãy liệt kê danh sách các khách hàng có trạng thái là hết hạn
+Tìm tất cả khách hàng loại hết hạn
+Liệt kê danh sách khách hàng là đã xong
+khách hàng đã xong</t>
+  </si>
+  <si>
+    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-14 đến ngày 2026-02-05
+Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-14 - 2026-02-05
+Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-14 tới 2026-02-05</t>
+  </si>
+  <si>
+    <t>khách hàng thành công
+Liệt kê danh sách khách hàng là treo
+Trích xuất báo cáo các khách hàng thuộc loại bị treo
+Lọc các khách hàng đang ở trạng thái bị treo
+Liệt kê các khách hàng treo
+Danh sách các khách hàng hết hạn
+Hãy liệt kê danh sách các khách hàng có người thụ hưởng khách hàng trạng thái là bị treo
+Liệt kê danh sách khách hàng là thành công
+Liệt kê các khách hàng thành công
+Những khách hàng nào là bị treo?
+Danh sách bị treo
+Tìm tất cả khách hàng loại bị treo
+Danh sách danh sách khách hàng là hết hạn
 khách hàng hết hạn
-khách hàng bị treo
-Danh sách danh sách khách hàng là hoàn tất
-khách hàng hoàn tất</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-23 đến ngày 2026-02-03
-Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-23 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-23 tới 2026-02-03
-Kiểm tra các khách hàng với ngày trạng thái trạng thái là ngày 2025-12-23</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-10 đến ngày 2026-02-03
-Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2025-12-10 - 2026-02-03
-Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-10 tới 2026-02-03
-Kiểm tra các khách hàng với ngày trạng thái trạng thái là ngày 2025-12-10</t>
-  </si>
-  <si>
-    <t>Lọc các những khách hàng có trước khi thay đổi là quá giờ
-Lọc các khách hàng theo trước khi thay đổi quá giờ</t>
-  </si>
-  <si>
-    <t>Các các khách hàng hết hạn
-khách hàng thành công
-khách hàng xử lý
-Các danh sách khách hàng là hết hạn
-Tìm danh sách khách hàng là xử lý
+Cho xem danh sách khách hàng bị treo
+khách hàng treo</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào là xử lý?
+khách hàng hoàn tất
+Lọc các khách hàng đang ở trạng thái xử lý
+Hãy liệt kê danh sách các khách hàng có trạng thái new khách hàng là xử lý
+Cho xem danh sách khách hàng xử lý
+Những các khách hàng thất bại
+khách hàng thất bại
+Search các khách hàng hoàn tất
+Tìm danh sách khách hàng là hết hạn
+Tìm các khách hàng hết hạn
+Search danh sách khách hàng là hoàn tất
+Tìm tất cả khách hàng loại xử lý
+Những danh sách khách hàng là thất bại
+Danh sách xử lý
 khách hàng hết hạn
-Tra cứu danh sách khách hàng là thành công
-Tìm các khách hàng xử lý
-Tra cứu các khách hàng thành công</t>
-  </si>
-  <si>
-    <t>Cho tôi xem những khách hàng có trạng thái new khách hàng là thành công
-Cho tôi xem khách hàng theo trạng thái new khách hàng thành công</t>
-  </si>
-  <si>
-    <t>Cho tôi xem các khách hàng xử lý
-Tìm các khách hàng bị treo
-khách hàng thành công
-Cho tôi xem danh sách khách hàng là xử lý
-Xem chi tiết danh sách khách hàng là thành công
-khách hàng xử lý
-khách hàng bị treo
-Xem chi tiết các khách hàng thành công
-Tìm danh sách khách hàng là bị treo</t>
-  </si>
-  <si>
-    <t>mã, id tự tăng là khóa chính bản ghi này, số, bản ghi này, primary key</t>
-  </si>
-  <si>
-    <t>số mã khách hàng, mã khách hàng, customer information file, số cif, số khách hàng, mã định danh khách hàng, số số khách hàng, số cif mã định danh duy nhất khách hàng ngân hàng</t>
-  </si>
-  <si>
-    <t>định danh khách hàng nội bộ, id định danh khách hàng trong nội bộ, số khách hàng, mã khách hàng</t>
-  </si>
-  <si>
-    <t>mã số khách hàng, số khách hàng, có thể khác với cif tùy theo cấu trúc hệ thống</t>
-  </si>
-  <si>
-    <t>số khách hàng chi nhánh, khách hàng chi nhánh, quản lý mã cif này, chi nhánh nơi mở, mã khách hàng chi nhánh, chi nhánh nơi mở/quản lý mã cif này</t>
-  </si>
-  <si>
-    <t>loại số khách hàng, loại mã khách hàng, loại cif, khách hàng ưu tiên..., loại khách hàng, doanh nghiệp, cá nhân</t>
-  </si>
-  <si>
-    <t>khách hàng trạng thái, trạng thái khách hàng, trạng thái hiện khách hàng, inactive, closed..., active</t>
+Trích xuất báo cáo các khách hàng thuộc loại xử lý</t>
+  </si>
+  <si>
+    <t>Liệt kê unique image front TYPE_KQ7P là của ai?
+Thông tin về khách hàng số TYPE_KQ7P
+Check unique image front TYPE_KQ7P
+Tìm kiếm khách hàng ứng với số TYPE_KQ7P
+Vui lòng Xem chi tiết thông tin chi tiết của khách hàng có unique image front là TYPE_KQ7P
+Search khách hàng TYPE_KQ7P
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique image front TYPE_KQ7P
+Xem chi tiết TYPE_KQ7P
+Hiển thị khách hàng theo unique image front TYPE_KQ7P</t>
+  </si>
+  <si>
+    <t>Tìm kiếm khách hàng ứng với số GRP_2H2S
+Thông tin về khách hàng số GRP_2H2S
+Check unique image back GRP_2H2S
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique image back GRP_2H2S
+Xem chi tiết khách hàng GRP_2H2S
+Liệt kê unique image back GRP_2H2S là của ai?
+Xem chi tiết GRP_2H2S
+Vui lòng Search thông tin chi tiết của khách hàng có unique image back là GRP_2H2S
+Hiển thị khách hàng theo unique image back GRP_2H2S</t>
+  </si>
+  <si>
+    <t>customer information file, số mã khách hàng, mã định danh khách hàng, số cif mã định danh duy nhất khách hàng ngân hàng, số số khách hàng, số cif, mã khách hàng, số khách hàng</t>
+  </si>
+  <si>
+    <t>id định danh khách hàng trong nội bộ, số khách hàng, mã khách hàng</t>
+  </si>
+  <si>
+    <t>có thể khác với cif tùy theo cấu trúc hệ thống, số khách hàng, mã số khách hàng</t>
+  </si>
+  <si>
+    <t>họ và tên đầy đủ khách hàng, tên khách hàng</t>
+  </si>
+  <si>
+    <t>quản lý mã cif, chi nhánh nơi mở/quản lý mã cif này, khách hàng chi nhánh, chi nhánh nơi mở, mã khách hàng chi nhánh, số khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>khách hàng ưu tiên..., cá nhân, loại cif, doanh nghiệp, loại số khách hàng, loại khách hàng, loại mã khách hàng</t>
+  </si>
+  <si>
+    <t>address line, dòng địa chỉ chi tiết, tên đường, số tài khoản trạng thái, số nhà, dòng địa chỉ</t>
+  </si>
+  <si>
+    <t>mã chi nhánh quản lý trực tiếp khách hàng, số chi nhánh, mã chi nhánh</t>
+  </si>
+  <si>
+    <t>inactive, trạng thái hiện khách hàng, khách hàng trạng thái, trạng thái khách hàng, active, closed...</t>
+  </si>
+  <si>
+    <t>ngày cấp giấy tờ định danh, cmnd/cccd/hộ chiếu, ngày trạng thái trạng thái, ngày of issue</t>
   </si>
   <si>
     <t>thời gian, lịch sử, ngày khởi tạo khách hàng trên</t>
@@ -285,19 +411,28 @@
     <t>tổng, thống kê, theo đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
   </si>
   <si>
-    <t>1-hiệu lực, trạng thái bản ghi, trạng thái, 0-hết hiệu lực</t>
+    <t>place of issue, nội dung trạng thái trạng thái, nơi cấp giấy tờ định danh, ca tp. hà nội</t>
+  </si>
+  <si>
+    <t>trạng thái số tiền, giá trị đặc trưng định danh duy nhất khách hàng, unique value</t>
+  </si>
+  <si>
+    <t>trạng thái, 0-hết hiệu lực, trạng thái bản ghi, 1-hiệu lực</t>
   </si>
   <si>
     <t>thời gian, lịch sử, ngày trạng thái trạng thái</t>
   </si>
   <si>
-    <t>trước khi thay đổi, người thụ hưởng khách hàng trạng thái, trạng thái cũ khách hàng, trạng thái old khách hàng</t>
+    <t>người thụ hưởng khách hàng trạng thái, trạng thái old khách hàng, trước khi thay đổi, trạng thái cũ khách hàng</t>
   </si>
   <si>
     <t>trạng thái new khách hàng, nội dung khách hàng trạng thái, sau khi cập nhật, trạng thái mới khách hàng</t>
   </si>
   <si>
-    <t>{"raw_text": "SELECT * FROM customer WHERE id = '{{id}}'"}</t>
+    <t>unique image front, cmnd/cccd, đường dẫn ảnh mặt trước giấy tờ định danh, trạng thái nội dung trạng thái</t>
+  </si>
+  <si>
+    <t>unique image back, đường dẫn ảnh mặt sau giấy tờ định danh, trạng thái nội dung trạng thái</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE cif_no = '{{cif_no}}'"}</t>
@@ -309,21 +444,39 @@
     <t>{"raw_text": "SELECT * FROM customer WHERE customer_no = '{{customer_no}}'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE customer_name = '{{customer_name}}' AND new_customer_status = 'SUCCESS'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE cif_branch = '{{cif_branch}}'"}</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE cif_type = '{{cif_type}}' AND new_customer_status = 'SUCCESS'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE address_line = '{{address_line}}' AND new_customer_status = 'SUCCESS'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE branch_code = '{{branch_code}}'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE customer_status = '{{customer_status}}'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE date_of_issue = '{{date_of_issue}}'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE init_date BETWEEN '{{start_date}}' AND '{{end_date}}' ORDER BY init_date DESC"}</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT SUM(is_fee_default) FROM customer WHERE new_customer_status = 'SUCCESS'"}</t>
   </si>
   <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE place_of_issue = '{{place_of_issue}}'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE unique_value = '{{unique_value}}'"}</t>
+  </si>
+  <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE status = '{{status}}'"}</t>
   </si>
   <si>
@@ -334,6 +487,12 @@
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE new_customer_status = '{{new_customer_status}}'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE unique_image_front = '{{unique_image_front}}'"}</t>
+  </si>
+  <si>
+    <t>{"raw_text": "SELECT * FROM customer WHERE unique_image_back = '{{unique_image_back}}'"}</t>
   </si>
 </sst>
 </file>
@@ -691,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -716,441 +875,339 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_customer.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\proton-intern\javisAI\6804_ddq\Text2SQL_Template\output\generated_datasets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2B02F5-1D9D-46D8-BB94-CC7299B2323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -31,34 +37,34 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>customer | Tra cứu số cif</t>
+    <t>customer | Tra cứu số cif mã định danh duy nhất khách hàng ngân hàng</t>
   </si>
   <si>
     <t>customer | Tra cứu id định danh khách hàng trong nội bộ</t>
   </si>
   <si>
-    <t>customer | Tra cứu mã số khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Lọc tên khách hàng</t>
+    <t>customer | Tra cứu số khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc họ và tên đầy đủ khách hàng</t>
   </si>
   <si>
     <t>customer | Tra cứu chi nhánh nơi mở/quản lý mã cif này</t>
   </si>
   <si>
-    <t>customer | Lọc loại mã khách hàng</t>
+    <t>customer | Lọc loại cif</t>
   </si>
   <si>
     <t>customer | Lọc dòng địa chỉ</t>
   </si>
   <si>
-    <t>customer | Tra cứu mã chi nhánh</t>
-  </si>
-  <si>
-    <t>customer | Lọc trạng thái hiện khách hàng</t>
-  </si>
-  <si>
-    <t>customer | Tra cứu ngày cấp giấy tờ định danh</t>
+    <t>customer | Tra cứu mã chi nhánh quản lý trực tiếp khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Lọc trạng thái khách hàng</t>
+  </si>
+  <si>
+    <t>customer | Tra cứu ngày of issue</t>
   </si>
   <si>
     <t>customer | Lọc thời gian theo ngày init</t>
@@ -76,19 +82,19 @@
     <t>customer | Lọc trạng thái bản ghi</t>
   </si>
   <si>
-    <t>customer | Lọc thời gian theo ngày tháng năm sinh</t>
+    <t>customer | Lọc thời gian theo ngày of birth</t>
   </si>
   <si>
     <t>customer | Lọc trạng thái cũ khách hàng</t>
   </si>
   <si>
-    <t>customer | Lọc trạng thái mới khách hàng</t>
+    <t>customer | Lọc trạng thái new khách hàng</t>
   </si>
   <si>
     <t>customer | Tra cứu unique image front</t>
   </si>
   <si>
-    <t>customer | Tra cứu đường dẫn ảnh mặt sau giấy tờ định danh</t>
+    <t>customer | Tra cứu unique image back</t>
   </si>
   <si>
     <t>customer | So sánh lớn hơn is phí default</t>
@@ -97,10 +103,10 @@
     <t>customer | Xếp hạng Top is phí default</t>
   </si>
   <si>
-    <t>customer | Lọc tên khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>customer | Lọc loại mã khách hàng và is phí default</t>
+    <t>customer | Lọc họ và tên đầy đủ khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>customer | Lọc loại cif và is phí default</t>
   </si>
   <si>
     <t>customer | Lọc dòng địa chỉ và is phí default</t>
@@ -112,10 +118,10 @@
     <t>customer | Lọc phân hạng khách hàng và is phí default</t>
   </si>
   <si>
-    <t>customer | Lọc trạng thái hiện khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>customer | Lọc email và is phí default</t>
+    <t>customer | Lọc trạng thái khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>customer | Lọc địa chỉ thư điện tử khách hàng và is phí default</t>
   </si>
   <si>
     <t>customer | Lọc home phone và is phí default</t>
@@ -124,10 +130,10 @@
     <t>customer | Lọc latitude và is phí default</t>
   </si>
   <si>
-    <t>customer | Lọc kinh độ và is phí default</t>
-  </si>
-  <si>
-    <t>customer | Lọc mobile phone và is phí default</t>
+    <t>customer | Lọc longitude và is phí default</t>
+  </si>
+  <si>
+    <t>customer | Lọc số điện thoại di động chính và is phí default</t>
   </si>
   <si>
     <t>customer | Lọc trạng thái bản ghi và is phí default</t>
@@ -145,37 +151,37 @@
     <t>customer | Lọc trạng thái cũ khách hàng và is phí default</t>
   </si>
   <si>
-    <t>customer | Lọc trạng thái mới khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>Tra cứu chính xác theo số cif (Số CIF (Customer Information File) - Mã định danh duy nhất của khách hàng tại ngân hàng.)</t>
+    <t>customer | Lọc trạng thái new khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>Tra cứu chính xác theo số cif mã định danh duy nhất khách hàng ngân hàng (Số CIF (Customer Information File) - Mã định danh duy nhất của khách hàng tại ngân hàng.)</t>
   </si>
   <si>
     <t>Tra cứu chính xác theo id định danh khách hàng trong nội bộ (ID định danh khách hàng trong hệ thống nội bộ.)</t>
   </si>
   <si>
-    <t>Tra cứu chính xác theo mã số khách hàng (Mã số khách hàng (có thể khác với CIF tùy theo cấu trúc hệ thống).)</t>
-  </si>
-  <si>
-    <t>Lọc dữ liệu theo tên khách hàng</t>
+    <t>Tra cứu chính xác theo số khách hàng (Mã số khách hàng (có thể khác với CIF tùy theo cấu trúc hệ thống).)</t>
+  </si>
+  <si>
+    <t>Lọc dữ liệu theo họ và tên đầy đủ khách hàng</t>
   </si>
   <si>
     <t>Tra cứu chính xác theo chi nhánh nơi mở/quản lý mã cif này (Chi nhánh nơi mở/quản lý mã CIF này.)</t>
   </si>
   <si>
-    <t>Lọc dữ liệu theo loại mã khách hàng</t>
+    <t>Lọc dữ liệu theo loại cif</t>
   </si>
   <si>
     <t>Lọc dữ liệu theo dòng địa chỉ</t>
   </si>
   <si>
-    <t>Tra cứu chính xác theo mã chi nhánh (Mã chi nhánh quản lý trực tiếp khách hàng.)</t>
-  </si>
-  <si>
-    <t>Lọc dữ liệu theo trạng thái hiện khách hàng</t>
-  </si>
-  <si>
-    <t>Tra cứu chính xác theo ngày cấp giấy tờ định danh (Ngày cấp giấy tờ định danh (CMND/CCCD/Hộ chiếu).)</t>
+    <t>Tra cứu chính xác theo mã chi nhánh quản lý trực tiếp khách hàng (Mã chi nhánh quản lý trực tiếp khách hàng.)</t>
+  </si>
+  <si>
+    <t>Lọc dữ liệu theo trạng thái khách hàng</t>
+  </si>
+  <si>
+    <t>Tra cứu chính xác theo ngày of issue (Ngày cấp giấy tờ định danh (CMND/CCCD/Hộ chiếu).)</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột ngày init</t>
@@ -193,19 +199,19 @@
     <t>Lọc dữ liệu theo trạng thái bản ghi</t>
   </si>
   <si>
-    <t>Truy vấn lịch sử dựa trên cột ngày tháng năm sinh</t>
+    <t>Truy vấn lịch sử dựa trên cột ngày of birth</t>
   </si>
   <si>
     <t>Lọc dữ liệu theo trạng thái cũ khách hàng</t>
   </si>
   <si>
-    <t>Lọc dữ liệu theo trạng thái mới khách hàng</t>
+    <t>Lọc dữ liệu theo trạng thái new khách hàng</t>
   </si>
   <si>
     <t>Tra cứu chính xác theo unique image front (Đường dẫn ảnh mặt trước giấy tờ định danh (CMND/CCCD).)</t>
   </si>
   <si>
-    <t>Tra cứu chính xác theo đường dẫn ảnh mặt sau giấy tờ định danh (Đường dẫn ảnh mặt sau giấy tờ định danh.)</t>
+    <t>Tra cứu chính xác theo unique image back (Đường dẫn ảnh mặt sau giấy tờ định danh.)</t>
   </si>
   <si>
     <t>Tìm kiếm customer có is phí default &gt; giá trị</t>
@@ -214,10 +220,10 @@
     <t>Lấy danh sách bản ghi có is phí default cao nhất</t>
   </si>
   <si>
-    <t>Tìm bản ghi theo tên khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>Tìm bản ghi theo loại mã khách hàng và is phí default</t>
+    <t>Tìm bản ghi theo họ và tên đầy đủ khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>Tìm bản ghi theo loại cif và is phí default</t>
   </si>
   <si>
     <t>Tìm bản ghi theo dòng địa chỉ và is phí default</t>
@@ -229,10 +235,10 @@
     <t>Tìm bản ghi theo phân hạng khách hàng và is phí default</t>
   </si>
   <si>
-    <t>Tìm bản ghi theo trạng thái hiện khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>Tìm bản ghi theo email và is phí default</t>
+    <t>Tìm bản ghi theo trạng thái khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>Tìm bản ghi theo địa chỉ thư điện tử khách hàng và is phí default</t>
   </si>
   <si>
     <t>Tìm bản ghi theo home phone và is phí default</t>
@@ -241,10 +247,10 @@
     <t>Tìm bản ghi theo latitude và is phí default</t>
   </si>
   <si>
-    <t>Tìm bản ghi theo kinh độ và is phí default</t>
-  </si>
-  <si>
-    <t>Tìm bản ghi theo mobile phone và is phí default</t>
+    <t>Tìm bản ghi theo longitude và is phí default</t>
+  </si>
+  <si>
+    <t>Tìm bản ghi theo số điện thoại di động chính và is phí default</t>
   </si>
   <si>
     <t>Tìm bản ghi theo trạng thái bản ghi và is phí default</t>
@@ -262,592 +268,592 @@
     <t>Tìm bản ghi theo trạng thái cũ khách hàng và is phí default</t>
   </si>
   <si>
-    <t>Tìm bản ghi theo trạng thái mới khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>Những khách hàng 7527482
-Check mã khách hàng 7527482
-Những mã khách hàng 7527482 là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với cif_no 9058566
-Hãy hiển thị dữ liệu bản ghi khách hàng với số khách hàng 5314050
-Khách hàng 7527482.
-Vui lòng Những thông tin chi tiết của khách hàng có số mã khách hàng là 5314050
-Lọc các khách hàng theo số cif mã định danh duy nhất khách hàng ngân hàng 9058566
-Những khách hàng từ 7527482.
-Các khách hàng theo customer information file 7527482</t>
-  </si>
-  <si>
-    <t>Vui lòng Danh sách thông tin chi tiết của khách hàng có id định danh khách hàng trong nội bộ là 3713505
-Check số khách hàng 6749082
-Vui lòng hiển thị dữ liệu bản ghi khách hàng với id định danh khách hàng trong nội bộ 6749082.
-Danh sách số khách hàng 2348637 là của ai?
-Xác định dữ liệu bản ghi khách hàng với id định danh khách hàng trong nội bộ 6749082.
-Danh sách khách hàng 2348637
-Những khách hàng theo mã khách hàng 6749082
-Check id định danh khách hàng trong nội bộ 3713505
-Lọc các customer_id 6749082 là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với id định danh khách hàng trong nội bộ 6749082</t>
-  </si>
-  <si>
-    <t>Tìm kiếm khách hàng ứng với số 7108516
-Hãy hiển thị dữ liệu bản ghi khách hàng với số khách hàng 7108516
-Check customer_no 7539506
-Hãy hiển thị dữ liệu bản ghi khách hàng với có thể khác với cif tùy theo cấu trúc hệ thống 7108516
-Cấu trúc hệ thống 2051993 có thể xác định rằng thông tin chi tiết của khách hàng có thể khác với cif.
-Vui lòng Những thông tin chi tiết của khách hàng có có thể khác với cif tùy theo cấu trúc hệ thống là 2051993
-Lọc các có thể khác với cif tùy theo cấu trúc hệ thống 2051993 là của ai?
-Những mã số khách hàng 7108516 là của ai?
-Những có thể khác với cif tùy theo cấu trúc hệ thống 7108516 là của ai?
-Những khách hàng theo số khách hàng 7108516</t>
-  </si>
-  <si>
-    <t>Hãy liệt kê danh sách các khách hàng có họ và tên đầy đủ khách hàng là Cô Chi Đặng
-Hãy liệt kê danh sách các khách hàng có customer_name là Cô Chi Đặng
-Lọc các khách hàng đang ở trạng thái Cô Chi Đặng
-Trích xuất báo cáo các khách hàng thuộc loại Quý cô Khoa Phạm
-Lọc các khách hàng đang ở trạng thái Thành Trần
-Lọc các khách hàng đang ở trạng thái Quý cô Khoa Phạm
-Hãy liệt kê danh sách các khách hàng có customer_name là Thành Trần
-Lọc các khách hàng ở trạng thái Cô Chi Đặng.
-Trích xuất báo cáo các khách hàng thuộc loại Thành Trần
-Lọc các khách hàng đang ở trạng thái Cô Chi Đặng.</t>
-  </si>
-  <si>
-    <t>Danh sách chi nhánh nơi mở/quản lý mã cif này 65371532081 là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với cif_branch 26533156344273
-Hãy hiển thị dữ liệu bản ghi khách hàng với chi nhánh nơi mở 26533156344273
-Vui lòng Các thông tin chi tiết của khách hàng có cif_branch là 65371532081
-Lọc các chi nhánh nơi mở/quản lý mã cif này 26533156344273 là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với chi nhánh nơi mở/quản lý mã cif này 26533156344273
-Ai chịu trách nhiệm chọn lọc các chi nhánh nơi mở/quản lý mã cif 2653315634273?
-Những mã khách hàng chi nhánh 2122494218210 là của ai?
-Lọc các khách hàng 2122494218210
-Bạn có thể cho tôi biết mã cif 2653315634273 được lọc bởi ai không?</t>
-  </si>
-  <si>
-    <t>Hãy liệt kê danh sách các khách hàng có loại mã khách hàng là chuyển ra ngoài
-Tìm tất cả khách hàng loại chuyển ra ngoài
-Hãy liệt kê danh sách các khách hàng có doanh nghiệp là tiền điện
-Lọc các khách hàng đang ở trạng thái chuyển ra ngoài
-Các khách hàng có doanh nghiệp được cung cấp bởi các quỹ điện là gì?
-Hãy liệt kê danh sách các khách hàng có loại khách hàng là tiền điện
-Một số khách hàng có doanh nghiệp là tiền điện là ai?
-Hãy liệt kê danh sách các khách hàng có cá nhân là tiền điện
-Danh sách tiền điện
-Hãy liệt kê danh sách các khách hàng có khách hàng ưu tiên... là tiền điện</t>
-  </si>
-  <si>
-    <t>Hãy liệt kê danh sách các khách hàng có address line là 736
-Hãy liệt kê danh sách các khách hàng có số tài khoản trạng thái là 885
-Cho xem danh sách khách hàng 736
-Những cá nhân nào có số lượng khách hàng là 736?
-Hãy liệt kê danh sách các khách hàng có address line là 165
-Danh sách 885
-Khách hàng nào có tổng số khách hàng là 736?
-Lọc các khách hàng đang ở trạng thái 736
-Những khách hàng nào là 736?
-Hãy liệt kê danh sách các khách hàng có số tài khoản trạng thái là 736</t>
-  </si>
-  <si>
-    <t>Lọc các mã chi nhánh quản lý trực tiếp khách hàng nạp thẻ là của ai?
-Xem thông tin liên quan đến tiền giấy.
-Vui lòng Danh sách thông tin chi tiết của khách hàng có mã chi nhánh quản lý trực tiếp khách hàng là nạp thẻ
-Danh sách mã chi nhánh nạp thẻ là của ai?
-Hãy hiển thị dữ liệu bản ghi khách hàng với số chi nhánh tiền nước
-Xem chi tiết tiền nước
-Các khách hàng nạp thẻ
-Danh sách khách hàng theo số chi nhánh tiền nước
-Lọc các khách hàng tiền nước
-Tìm kiếm khách hàng ứng với số tiền nước</t>
-  </si>
-  <si>
-    <t>Hãy liệt kê danh sách các khách hàng có inactive là hết hạn
-Hãy liệt kê danh sách các khách hàng có closed... là bị treo
+    <t>Tìm bản ghi theo trạng thái new khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với cif_no 4775721
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Check cif_no 5400611
+Người dùng muốn tra cứu một giao dịch mua sắm cụ thể dựa trên mã khách hàng của nhà cung cấp dịch vụ
+Những khách hàng theo customer information file 6112346
+Check customer information file 4775721
+Vui lòng Các thông tin chi tiết của khách hàng có số mã khách hàng là 5400611
+Lọc các khách hàng theo số mã khách hàng 6112346
+Vui lòng Danh sách thông tin chi tiết của khách hàng có cif_no là 5400611
+Người dùng muốn tra cứu một số giao dịch mua sắm cụ thể dựa trên mã khách hàng của nhà cung cấp dịch vụ</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu danh sách khách hàng theo số giao dịch hoặc mã tham chiếu.
+Những khách hàng 3558221
+Hãy hiển thị dữ liệu bản ghi khách hàng với số khách hàng 4480820
+Hãy hiển thị dữ liệu bản ghi khách hàng với số khách hàng 9337817
+Lọc các id định danh khách hàng trong hệ thống nội bộ 3558221 là của ai?
+Người dùng muốn tra cứu danh sách khách hàng theo số tài khoản nguồn.
+Check id định danh khách hàng trong hệ thống nội bộ 4480820
+Danh sách khách hàng theo id định danh khách hàng trong nội bộ 4480820
+Lọc các mã khách hàng 3558221 là của ai?
+Check customer_id 3558221</t>
+  </si>
+  <si>
+    <t>Lọc các khách hàng 2831467
+Danh sách khách hàng theo có thể khác với cif tùy theo cấu trúc hệ thống 7144443
+Những mã số khách hàng 2697259 là của ai?
+Check mã số khách hàng 2697259
+Người dùng muốn tra cứu một giao dịch mua sắm cụ thể dựa trên mã khách hàng của nhà cung cấp dịch vụ
+Người dùng muốn tra cứu một mã khách hàng cụ thể dựa trên mã khách hàng của nhà cung cấp dịch vụ
+Vui lòng Các thông tin chi tiết của khách hàng có có thể khác với cif tùy theo cấu trúc hệ thống là 7144443
+Lọc các có thể khác với cif tùy theo cấu trúc hệ thống 2697259 là của ai?
+Người dùng muốn tra cứu danh sách khách hàng theo số hệ thống giao dịch hoặc hình thức đặt mua.
+Hãy hiển thị dữ liệu bản ghi khách hàng với có thể khác với cif tùy theo cấu trúc hệ thống 2831467</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu danh sách khách hàng theo tên khách hàng và tên khách hàng.
+Danh sách Nhật Mai
+Hãy liệt kê danh sách các khách hàng có customer_name là Nhật Mai
+Hãy liệt kê danh sách các khách hàng có họ và tên đầy đủ của khách hàng là Trung Bùi
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo tên khách hàng hoặc tên người mua sắm.
+Những khách hàng nào là Ông Tú Đặng?
+Tìm tất cả khách hàng loại Nhật Mai
+Hãy liệt kê danh sách các khách hàng có tên khách hàng là Ông Tú Đặng
+Hãy liệt kê danh sách các khách hàng có tên khách hàng là Trung Bùi
+Cho xem danh sách khách hàng Trung Bùi</t>
+  </si>
+  <si>
+    <t>Các chi nhánh nơi mở 856174611565 là của ai?
+Xem chi tiết 856174611565
+Xem chi tiết 19875833849522
+Người dùng muốn tra cứu danh sách khách hàng theo kênh giao dịch.
+Hãy hiển thị dữ liệu bản ghi khách hàng với chi nhánh nơi mở/quản lý mã cif này 19875833849522
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Người dùng muốn tra cứu các giao dịch mua sắm theo số tài khoản nguồn.
+Người dùng muốn tra cứu các giao dịch mua sắm theo kênh thực hiện giao dịch.
+Hãy hiển thị dữ liệu bản ghi khách hàng với mã khách hàng chi nhánh 5059708095
+Những khách hàng theo chi nhánh nơi mở 856174611565</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào là hóa đơn nước?
+Danh sách hóa đơn nước
+Người dùng muốn tra cứu danh sách giao dịch mua sắm theo trạng thái xử lý.
+Lọc các khách hàng đang ở trạng thái chuyển cùng ngân hàng
+Hãy liệt kê danh sách các khách hàng có loại cif là chuyển ra ngoài
+Lọc các khách hàng đang ở trạng thái hóa đơn nước
+Cho xem danh sách khách hàng hóa đơn nước
+Những khách hàng nào là chuyển ra ngoài?
+Người dùng muốn tra cứu danh sách giao dịch thanh toán hóa đơn theo loại dịch vụ cụ thể (ví dụ: điện, nước, internet, truyền hình, điện thoại, học phí...)
+Lọc các khách hàng đang ở trạng thái chuyển ra ngoài</t>
+  </si>
+  <si>
+    <t>Những khách hàng nào là 576?
+Người dùng muốn tra cứu danh sách khách hàng mua sắm theo tên người mua sắm.
+Hãy liệt kê danh sách các khách hàng có address_line là 576
+Hãy liệt kê danh sách các khách hàng có tên đường là 576
+Hãy liệt kê danh sách các khách hàng có tên đường là 743
+Người dùng muốn tra cứu danh sách khách hàng mua sắm theo số tài khoản nguồn.
+Trích xuất báo cáo các khách hàng thuộc loại 743
+Hãy liệt kê danh sách các khách hàng có address_line là 590
+Những khách hàng nào là 590?
+Hãy liệt kê danh sách các khách hàng có address line là 590</t>
+  </si>
+  <si>
+    <t>Hãy hiển thị dữ liệu bản ghi khách hàng với mã chi nhánh quản lý trực tiếp khách hàng hóa đơn điện
+Xem chi tiết hóa đơn điện
+Các branch_code hóa đơn điện là của ai?
+Danh sách khách hàng theo branch_code hóa đơn điện
+Tìm kiếm khách hàng ứng với số hóa đơn điện
+Người dùng muốn tra cứu danh sách chi nhánh hóa đơn theo tên đơn vị cung cấp dịch vụ.
+Hãy hiển thị dữ liệu bản ghi khách hàng với branch_code chuyển cùng ngân hàng
+Người dùng muốn tra cứu danh sách các chi nhánh hóa đơn theo tên đơn vị cung cấp dịch vụ.
+Những số chi nhánh chuyển cùng ngân hàng là của ai?
+Người dùng muốn tra cứu danh sách các giao dịch thanh toán hóa đơn theo tên người dùng.</t>
+  </si>
+  <si>
+    <t>Danh sách hết hạn
+Tìm tất cả khách hàng loại hoàn tất
+khách hàng hết hạn
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý.
+khách hàng treo
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý hoặc kết quả giao dịch.
+Người dùng muốn tra cứu danh sách giao dịch mua sắm theo trạng thái xử lý.
 Tìm tất cả khách hàng loại hết hạn
-Tra cứu các khách hàng lỗi
-Danh sách khách hàng đã hoàn tất.
-Search các khách hàng đang chờ
-Danh sách danh sách khách hàng là hoàn tất
-Danh sách các khách hàng hoàn tất
-Trích xuất báo cáo các khách hàng thuộc loại bị treo
-Hãy liệt kê danh sách các khách hàng có closed... là hết hạn</t>
-  </si>
-  <si>
-    <t>Những khách hàng nào có sẵn trong 2025-02-26?
-Tìm kiếm khách hàng ứng với số 2025-02-26
-Xem chi tiết 2025-02-26
-Những khách hàng theo ngày cấp giấy tờ định danh 2025-02-26
-Danh sách ngày trạng thái trạng thái 2025-07-21 là của ai?
-Xem chi tiết 2025-04-21
-Vui lòng Lọc các thông tin chi tiết của khách hàng có ngày trạng thái trạng thái là 2025-07-21
-Những ngày trạng thái trạng thái 2025-04-21 là của ai?
-Những ngày cấp giấy tờ định danh 2025-02-26 là của ai?
-Những khách hàng 2025-02-26</t>
-  </si>
-  <si>
-    <t>Xem lịch sử khách hàng được cung cấp bởi init_date từ 2025-12-18 đến 2026-02-05.
-Xem lịch sử khách hàng dựa trên ngày init từ 2026-01-19 tới 2026-02-05
-Xem lịch sử khách hàng dựa trên init_date từ năm 2025-12-18 tới 2026-02-05.
-Sao kê khách hàng theo ngày init từ ngày 2025-12-20 đến ngày 2026-02-05
-Lọc khách hàng có ngày khởi tạo khách hàng trên trong khoảng 2026-01-25 - 2026-02-05
-Lọc khách hàng có init_date trong khoảng 2026-01-02 - 2026-02-05
-Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2025-12-15 tới 2026-02-05
-Xem lịch sử khách hàng dựa trên init_date từ 2025-12-18 tới 2026-02-05
-Sao kê khách hàng theo ngày trạng thái từ ngày 2025-12-20 đến ngày 2026-02-05
-Sao kê khách hàng theo ngày khởi tạo khách hàng trên từ ngày 2025-12-15 đến ngày 2026-02-05</t>
-  </si>
-  <si>
-    <t>Cho tôi xem tổng is phí default
-Tính tổng trạng thái phí trạng thái
-Tổng trạng thái phí trạng thái là bao nhiêu?
-Tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không là bao nhiêu?
-Thống kê is phí default hôm nay
+Xem chi tiết danh sách khách hàng là đã xong
+Hãy liệt kê danh sách các khách hàng có trạng thái khách hàng là hết hạn</t>
+  </si>
+  <si>
+    <t>Lọc các ngày trạng thái trạng thái 2025-02-19 là của ai?
+Vui lòng Các thông tin chi tiết của khách hàng có ngày cấp giấy tờ định danh là 2025-02-19
+Lọc các khách hàng theo date_of_issue 2026-01-03
+Người dùng muốn tra cứu trạng thái trạng thái xử lý hoặc kết quả giao dịch.
+Người dùng muốn tra cứu danh sách trạng thái xử lý hoặc kết quả giao dịch.
+Các ngày trạng thái trạng thái 2026-01-03 là của ai?
+Vui lòng Những thông tin chi tiết của khách hàng có date_of_issue là 2026-01-03
+Check ngày trạng thái trạng thái 2025-02-19
+Check cmnd/cccd/hộ chiếu 2025-02-19
+Vui lòng Lọc các thông tin chi tiết của khách hàng có ngày cấp giấy tờ định danh là 2026-01-03</t>
+  </si>
+  <si>
+    <t>Lọc khách hàng có ngày init trong khoảng 2025-12-29 - 2026-02-06
+Lọc khách hàng có ngày trạng thái trong khoảng 2026-02-01 - 2026-02-06
+Người dùng muốn tra cứu lịch sử giao dịch mua sắm theo số lượng giao dịch hoặc kết quả giao dịch.
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý hoặc kết quả giao dịch.
+Người dùng muốn tra cứu các giao dịch mua sắm theo số lượng giao dịch hoặc hình thức mua sắm.
+Xem lịch sử khách hàng dựa trên ngày khởi tạo khách hàng trên từ 2025-12-16 tới 2026-02-06
+Xem lịch sử khách hàng dựa trên init_date từ 2025-12-18 tới 2026-02-06
+Người dùng muốn tra cứu danh sách khách hàng theo số trạng thái xử lý hoặc kết quả giao dịch.
+Xem lịch sử khách hàng dựa trên ngày trạng thái từ 2025-12-31 tới 2026-02-06
+Xem lịch sử khách hàng dựa trên ngày khởi tạo thông tin khách hàng trên hệ thống từ 2026-01-03 tới 2026-02-06</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu lịch sử giao dịch thanh toán hóa đơn theo số tiền.
+Tính tổng is_fee_default
+Người dùng muốn tra cứu danh sách các giao dịch nạp hoặc rút tiền theo tên người dùng.
+Cho tôi xem tổng is phí default
+Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay
+Tổng is phí default là bao nhiêu?
+Người dùng muốn tra cứu lịch sử giao dịch mua sắm theo số tiền.
 Cho tôi xem tổng is_fee_default
-Tính tổng is_fee_default
-Tổng của is_fee_default là bao nhiêu?
-Thống kê đánh dấu khách hàng có thuộc diện mặc định thu phí hay không hôm nay
+Tổng is_fee_default là bao nhiêu?
 Cho tôi xem tổng đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
   </si>
   <si>
-    <t>Lọc các khách hàng theo place_of_issue 592847
-Xem chi tiết 592847
-Những khách hàng theo nội dung trạng thái trạng thái 592847
-Danh sách khách hàng là 81557.
-Danh sách khách hàng 81557
-Vui lòng Những thông tin chi tiết của khách hàng có ca tp. hà nội là 81557
-Tìm kiếm khách hàng ứng với số 81557
-Hãy hiển thị dữ liệu bản ghi khách hàng với ca tp. hà nội 322213
-Lọc các khách hàng theo nội dung trạng thái trạng thái 322213
-Các khách hàng theo place of issue 81557</t>
-  </si>
-  <si>
-    <t>Số khách hàng 173001 là bao nhiêu?
-Những khách hàng 929804
-Danh sách khách hàng 929804
-Những unique_value 943837 là của ai?
-Những trạng thái số tiền 173001 là của ai?
-Khách hàng 173001.
-Check unique value 173001
-Những khách hàng 173001
-Những unique value 943837 là của ai?
-Thông tin về khách hàng số 943837</t>
-  </si>
-  <si>
-    <t>Search danh sách khách hàng là lỗi
-Danh sách treo có sẵn.
-Liệt kê các khách hàng thất bại
-Những khách hàng nào là quá giờ?
-Tra cứu danh sách khách hàng là hoàn tất
-Danh sách treo
-Hãy liệt kê danh sách các khách hàng có 1-hiệu lực là lỗi
-Tra cứu các khách hàng hoàn tất
-Tìm tất cả khách hàng loại quá giờ
-Cho xem danh sách khách hàng quá giờ</t>
-  </si>
-  <si>
-    <t>Sao kê khách hàng theo ngày of birth từ ngày 2025-12-23 đến ngày 2026-02-05
-Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2026-01-07 đến ngày 2026-02-05
-Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2026-01-30 đến 2026-02-05.
-Xem lịch sử khách hàng dựa trên ngày tháng năm sinh từ 2026-01-01 tới 2026-02-05
-Sao kê khách hàng theo ngày of birth từ ngày 2026-02-03 đến ngày 2026-02-05
-Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2026-01-30 tới 2026-02-05
-Sao kê khách hàng theo ngày of birth từ ngày 2025-12-26 đến ngày 2026-02-05
-Lọc khách hàng có ngày of birth trong khoảng 2025-12-26 - 2026-02-05
-Lọc khách hàng có ngày of birth trong khoảng 2026-02-03 - 2026-02-05
-Kiểm tra lịch sử khách hàng từ 2026-01-30 đến 2026-02-05.</t>
-  </si>
-  <si>
-    <t>Hãy liệt kê danh sách các khách hàng có trạng thái old khách hàng là bị treo
+    <t>Người dùng muốn tra cứu các giao dịch mua sắm theo danh mục hoặc nhóm sản phẩm.
+Các khách hàng 708262
+Người dùng muốn tra cứu các giao dịch mua sắm theo số tài khoản nguồn.
+Người dùng muốn tra cứu danh sách khách hàng theo chiều dọc theo địa điểm giao dịch.
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Lọc các ca tp. hà nội 708262 là của ai?
+Vui lòng Lọc các thông tin chi tiết của khách hàng có place_of_issue là 708262
+Vui lòng Những thông tin chi tiết của khách hàng có ca tp. hà nội là 349220
+Các khách hàng theo ca tp. hà nội 775616
+Vui lòng Danh sách thông tin chi tiết của khách hàng có nội dung trạng thái trạng thái là 349220</t>
+  </si>
+  <si>
+    <t>Xem chi tiết 533782
+Lọc các khách hàng 52081
+Check giá trị đặc trưng dùng để định danh duy nhất khách hàng 290318
+Người dùng muốn tra cứu danh sách khách hàng theo số tài khoản nguồn.
+Check unique_value 533782
+Người dùng muốn tra cứu một số thông tin cụ thể dựa trên mã hóa đơn hoặc mã truy cập.
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique_value 533782
+Người dùng muốn tra cứu danh sách khách hàng theo số đơn vị bán hàng hoặc đơn vị bán hàng.
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique value 533782
+Danh sách khách hàng theo unique value 290318</t>
+  </si>
+  <si>
+    <t>Lọc các các khách hàng bị treo
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý hoặc kết quả giao dịch.
+Xem chi tiết danh sách khách hàng là hết hạn
 khách hàng quá giờ
-Các các khách hàng đã xong
-Cho tôi xem các khách hàng bị treo
-Việc sử dụng tìm kiếm khách hàng là một chiến lược thành công.
-Search danh sách khách hàng là thành công
-Tìm danh sách khách hàng có phải là một chiến lược thành công?
-Hãy liệt kê danh sách các khách hàng có trạng thái cũ khách hàng là quá giờ
-Danh sách các khách hàng thành công
-Hãy liệt kê danh sách các khách hàng có trạng thái cũ của khách hàng là quá giờ</t>
-  </si>
-  <si>
-    <t>Hãy liệt kê danh sách các khách hàng có trạng thái mới của khách hàng là đã xong
-Trích xuất báo cáo các khách hàng thuộc loại thất bại
-Search danh sách khách hàng là xử lý
-Lọc các các khách hàng quá giờ
-Xem các khách hàng quá giờ ở đâu?
-Hãy liệt kê danh sách các khách hàng có trạng thái new khách hàng là thất bại
-Các các khách hàng thành công
-Hãy liệt kê danh sách các khách hàng có sau khi cập nhật là thất bại
-Tìm các khách hàng đã xong
-Hãy liệt kê danh sách các khách hàng có sau khi cập nhật là quá giờ</t>
-  </si>
-  <si>
-    <t>Vui lòng Danh sách thông tin chi tiết của khách hàng có cmnd/cccd là 845763
-Hãy hiển thị dữ liệu bản ghi khách hàng với unique image front 497832
-Danh sách khách hàng theo unique image front 497832
-Check cmnd/cccd 497832
-Hãy hiển thị dữ liệu bản ghi khách hàng với unique image front 338149
-Vui lòng Danh sách thông tin chi tiết của khách hàng có cmnd/cccd là 338149
-Các khách hàng theo unique_image_front 497832
-Khách hàng theo mô hình unique_image_front 497832.
-Hãy hiển thị dữ liệu bản ghi khách hàng với unique_image_front 497832
-Tìm kiếm khách hàng ứng với số 338149</t>
-  </si>
-  <si>
-    <t>Lọc các đường dẫn ảnh mặt sau giấy tờ định danh 917196 là của ai?
-Những unique_image_back 73109 là của ai?
-Vui lòng xem chi tiết của khách hàng có unique image back là 73109.
-Check unique_image_back 73109
-Check đường dẫn ảnh mặt sau giấy tờ định danh 73109
-Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt sau giấy tờ định danh 73109
-Thông tin về khách hàng số 917196
-Check đường dẫn ảnh mặt sau giấy tờ định danh 917196
-Vui lòng Các thông tin chi tiết của khách hàng có unique_image_back là 219357
-Check trạng thái nội dung trạng thái 73109</t>
-  </si>
-  <si>
-    <t>Liệt kê customer với trạng thái phí trạng thái trên 590000
-Tìm các customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không lớn hơn 4050000
-Liệt kê customer với đánh dấu khách hàng có thuộc diện mặc định thu phí hay không trên 36000000
-Tìm các customer có trạng thái phí trạng thái lớn hơn 130000
-Theo số liệu thống kê của các công ty khởi nghiệp với is_fee_default là 69000000.
-Tìm các customer có trạng thái phí trạng thái lớn hơn 4050000
-Tìm các customer có is phí default lớn hơn 69000000
-Liệt kê customer với đánh dấu khách hàng có thuộc diện mặc định thu phí hay không trên 69000000
-Liệt kê customer với is_fee_default trên 69000000
-Danh sách các cá nhân có số lượng người theo dõi là 69000000 với is_fee_default là gì?</t>
-  </si>
-  <si>
-    <t>Nếu 20 customer có đánh dấu khách hàng là một phần của hệ thống thu phí mặc định, thì đó sẽ là thứ gì?
-Top 20 customer có is_fee_default cao nhất
-Xác định xem 20 customer có đánh dấu khách hàng là thành viên mặc định thu phí hay không thấp nhất.
-Xem 20 customer có trạng thái phí trạng thái thấp nhất
-Liệt kê 10 customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không lớn nhất
+khách hàng hoàn tất
+Lọc các danh sách khách hàng là xử lý
+Hãy liệt kê danh sách các khách hàng có trạng thái bản ghi là hoàn tất
+Tìm các khách hàng xử lý
+Hãy liệt kê danh sách các khách hàng có status là hoàn tất
+Người dùng muốn tra cứu danh sách khách hàng có trạng thái xử lý hoặc kết quả giao dịch.</t>
+  </si>
+  <si>
+    <t>Lọc khách hàng có ngày trạng thái trạng thái trong khoảng 2026-02-02 - 2026-02-06
+Sao kê khách hàng theo ngày trạng thái trạng thái từ ngày 2025-12-25 đến ngày 2026-02-06
+Sao kê khách hàng theo date_of_birth từ ngày 2026-01-30 đến ngày 2026-02-06
+Xem lịch sử khách hàng dựa trên date_of_birth từ 2026-01-08 tới 2026-02-06
+Lọc khách hàng có ngày tháng năm sinh trong khoảng 2026-01-31 - 2026-02-06
+Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2026-01-12 tới 2026-02-06
+Người dùng muốn tra cứu danh sách giao dịch mua sắm theo trạng thái xử lý hoặc kết quả giao dịch.
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo trạng thái xử lý hoặc kết quả giao dịch.
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý hoặc kết quả giao dịch.
+Xem lịch sử khách hàng dựa trên ngày trạng thái trạng thái từ 2025-12-25 tới 2026-02-06</t>
+  </si>
+  <si>
+    <t>khách hàng đang chờ
+Hãy liệt kê danh sách các khách hàng có trạng thái cũ của khách hàng là đã xong
+Tra cứu danh sách khách hàng là xử lý
+Danh sách lỗi
+Hãy liệt kê danh sách các khách hàng có trước khi thay đổi là đã xong
+Người dùng muốn tra cứu các giao dịch mua sắm theo danh mục hoặc nhóm sản phẩm.
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo loại giao dịch hoặc hình thức mua sắm.
+Tìm tất cả khách hàng loại lỗi
+Hãy liệt kê danh sách các khách hàng có old_customer_status là lỗi
+Cho xem danh sách khách hàng đã xong</t>
+  </si>
+  <si>
+    <t>Hiển thị các khách hàng đã xong
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý.
+Hãy liệt kê danh sách các khách hàng có nội dung khách hàng trạng thái là thành công
+Hãy liệt kê danh sách các khách hàng có new_customer_status là thành công
+khách hàng treo
+Danh sách danh sách khách hàng là treo
+Danh sách danh sách khách hàng là quá giờ
+Cho xem danh sách khách hàng đã xong
+Kiểm tra các khách hàng treo
+Xem chi tiết các khách hàng đang chờ</t>
+  </si>
+  <si>
+    <t>Vui lòng Lọc các thông tin chi tiết của khách hàng có đường dẫn ảnh mặt trước giấy tờ định danh là 562347
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Hãy hiển thị dữ liệu bản ghi khách hàng với đường dẫn ảnh mặt trước giấy tờ định danh 722732
+Người dùng muốn tra cứu một giao dịch mua sắm cụ thể dựa trên mã khách hàng của nhà cung cấp dịch vụ
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique_image_front 562347
+Hãy hiển thị dữ liệu bản ghi khách hàng với cmnd/cccd 722732
+Thông tin về khách hàng số 562347
+Những khách hàng 722732
+Vui lòng Danh sách thông tin chi tiết của khách hàng có unique image front là 562347
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique image front 722732</t>
+  </si>
+  <si>
+    <t>Danh sách khách hàng theo unique_image_back 482875
+Hãy hiển thị dữ liệu bản ghi khách hàng với trạng thái nội dung trạng thái 482199
+Vui lòng Lọc các thông tin chi tiết của khách hàng có unique image back là 482199
+Vui lòng Những thông tin chi tiết của khách hàng có đường dẫn ảnh mặt sau giấy tờ định danh là 482199
+Hãy hiển thị dữ liệu bản ghi khách hàng với unique image back 482199
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo trạng thái xử lý hoặc kết quả giao dịch.
+Người dùng muốn tra cứu danh sách khách hàng của nhà cung cấp dịch vụ theo số tài khoản nguồn.
+Các trạng thái nội dung trạng thái 482875 là của ai?
+Lọc các khách hàng theo đường dẫn ảnh mặt sau giấy tờ định danh 482199
+Người dùng muốn tra cứu danh sách khách hàng theo trạng thái xử lý hoặc kết quả giao dịch.</t>
+  </si>
+  <si>
+    <t>Liệt kê customer với is_fee_default trên 4200000
+Liệt kê customer với is phí default trên 40000000
+Liệt kê customer với đánh dấu khách hàng có thuộc diện mặc định thu phí hay không trên 4200000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Tìm các customer có is phí default lớn hơn 450000
+Người dùng muốn tra cứu danh sách khách hàng theo loại giao dịch hoặc hình thức thanh toán dịch vụ
+Tìm các customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không lớn hơn 450000
+Liệt kê customer với đánh dấu khách hàng có thuộc diện mặc định thu phí hay không trên 450000
+Người dùng muốn tra cứu danh sách khách hàng theo loại giao dịch hoặc hình thức thanh toán hóa đơn
+Tìm các customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không lớn hơn 40000000</t>
+  </si>
+  <si>
+    <t>Liệt kê 5 customer có is_fee_default lớn nhất
+Liệt kê 5 customer có is phí default lớn nhất
+Những customer nào có is_fee_default cao nhất?
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nhận tiền.
+Xem 5 customer có is_fee_default thấp nhất
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Top 5 customer có is phí default cao nhất
+Top 20 customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không cao nhất
 Xem 5 customer có trạng thái phí trạng thái thấp nhất
-Xem 10 customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không thấp nhất
-Xem 10 customer có is phí default thấp nhất
-Xem 5 customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không thấp nhất
-Top 10 customer có đánh dấu khách hàng có thuộc diện mặc định thu phí hay không cao nhất</t>
-  </si>
-  <si>
-    <t>Danh sách customer (customer_name: Hạnh Phú Dương) có is_fee_default cao hơn 310000
-Liệt kê customer thuộc customer_name Hạnh Phú Dương với is_fee_default trên 310000
-Liệt kê customer thuộc customer_name Hạnh Thị Nguyễn với is_fee_default trên 210000
-Có thể tìm thấy is_fee_default trên 310000 tại Lọc customer Hạnh Phú Dương không?
-Tìm những customer có customer_name là Hạnh Phú Dương và is_fee_default lớn hơn 310000
-Tìm những customer có customer_name là Hạnh Thị Nguyễn và is_fee_default lớn hơn 210000
-Lọc customer Nhật Hải Trần có is_fee_default &gt; 53000000
-Tìm những customer có customer_name là Bác Trọng Trần và is_fee_default lớn hơn 5000000
-Lọc customer Hạnh Phú Dương có is_fee_default &gt; 310000
-Tìm những customer có customer_name là Nhật Hải Trần và is_fee_default lớn hơn 53000000</t>
-  </si>
-  <si>
-    <t>Lọc customer napas 247 có is_fee_default &gt; 2800000
-Danh sách customer (cá nhân: tiền điện) có is_fee_default cao hơn 9700000
-Liệt kê customer thuộc cá nhân napas 247 với is_fee_default trên 2800000
-Số liệu customer thuộc về napas 247 với is_fee_default trên 2800000 là bao nhiêu?
-Lọc customer chuyển nhanh có is_fee_default &gt; 920000
-Lọc customer quét mã qr có is_fee_default &gt; 1750000
-Lọc customer tiền điện có is_fee_default &gt; 9700000
-Danh sách customer (cá nhân: napas 247) có is_fee_default cao hơn 2800000
-Tìm những customer có cá nhân là chuyển nhanh và is_fee_default lớn hơn 920000
-Số lượng customer thuộc người napas 247 với is_fee_default trên 2800000 là bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Danh sách customer (số nhà: 820) có is_fee_default cao hơn 390000
-Tìm những customer có số nhà là 820 và is_fee_default lớn hơn 390000
-Is_fee_default có thể được sử dụng để lọc customer 281 với giá trị 530000.
-Liệt kê customer thuộc số nhà 579 với is_fee_default trên 87000000
-Tìm những customer có số nhà là 579 và is_fee_default lớn hơn 87000000
-Tìm những customer có số nhà là 281 và is_fee_default lớn hơn 530000
-Lọc customer 281 có is_fee_default &gt; 530000
-Liệt kê customer thuộc số nhà 281 với is_fee_default trên 530000
-Công nghệ lọc customer 281 có thể chứa is_fee_default với giá trị từ 530000 trở xuống.
-Lọc customer 579 có is_fee_default &gt; 87000000</t>
-  </si>
-  <si>
-    <t>Danh sách customer (quận/huyện: 719) có is_fee_default cao hơn 620000
-Tìm những customer có quận/huyện là 167 và is_fee_default lớn hơn 840000
-Tìm những người có quận/huyện 215 và is_fee_default lớn hơn 86000000.
-Tìm những customer có quận/huyện là 815 và is_fee_default lớn hơn 76000000
-Lọc customer 167 có is_fee_default &gt; 840000
-Tìm những customer có quận/huyện là 215 và is_fee_default lớn hơn 86000000
-Tìm các customer có quận/huyện là 215 và is_fee_default lớn hơn 8600000.
-Liệt kê customer thuộc quận/huyện 815 với is_fee_default trên 76000000
-Lọc customer 215 có is_fee_default &gt; 86000000
-Tìm những customer có quận/huyện là 719 và is_fee_default lớn hơn 620000</t>
-  </si>
-  <si>
-    <t>Danh sách customer (bạc: 196) có is_fee_default cao hơn 32000000
-Số liệu thống kê customer thuộc loại bạc 196 với is_fee_default là 32000000.
-Tìm những customer có bạc là 222 và is_fee_default lớn hơn 4000000
-Liệt kê customer thuộc bạc 196 với is_fee_default trên 32000000
-Liệt kê customer thuộc bạc 208 với is_fee_default trên 3000000
-Lọc customer 692 có is_fee_default &gt; 73000000
-Lọc customer 196 có is_fee_default &gt; 32000000
-Danh sách customer (bạc: 692) có is_fee_default cao hơn 73000000
-Tìm những customer có bạc là 196 và is_fee_default lớn hơn 32000000
-Con số của customer thuộc bạc 196 với is_fee_default là 320000000.</t>
-  </si>
-  <si>
-    <t>Số liệu thống kê cho các customer trong active treo với is_fee_default trên 310000.
-Lọc customer đang chờ có is_fee_default &gt; 58000000
-Tìm những customer có active là đang chờ và is_fee_default lớn hơn 58000000
-Tổng số customer có thể được sử dụng trên 310000 trong chương trình bảo mật treo có is_fee_default là bao nhiêu?
-Tìm những customer có active là hết hạn và is_fee_default lớn hơn 3000000
-Liệt kê customer thuộc active xử lý với is_fee_default trên 84000000
-Danh sách customer (active: hết hạn) có is_fee_default cao hơn 3000000
-Liệt kê customer thuộc active treo với is_fee_default trên 310000
-Danh sách customer (active: đang chờ) có is_fee_default cao hơn 58000000
-Lọc customer xử lý có is_fee_default &gt; 84000000</t>
-  </si>
-  <si>
-    <t>Liệt kê customer thuộc email 153857 với is_fee_default trên 3250000
-Có thể đạt được sự xuất hiện của is_fee_default trên 27000000 khi lọc customer 992684 không?
-Lọc customer 992684 có is_fee_default &gt; 27000000
-Danh sách customer (email: 992684) có is_fee_default cao hơn 27000000
-Danh sách customer (email: 919725) có is_fee_default cao hơn 150000
-Lọc customer 153857 có is_fee_default &gt; 3250000
-Danh sách customer (email: 733677) có is_fee_default cao hơn 780000
-Tìm những customer có email là 733677 và is_fee_default lớn hơn 780000
-Liệt kê customer thuộc email 733677 với is_fee_default trên 780000
-Lọc customer 919725 có is_fee_default &gt; 150000</t>
-  </si>
-  <si>
-    <t>Danh sách customer (home_phone: 975) có is_fee_default cao hơn 97000000
-Tìm những customer có home_phone là 126 và is_fee_default lớn hơn 51000000
-Việc sử dụng is_fee_default trong lọc customer 615 có giá trị 500000.
-Danh sách customer (home_phone: 789) có is_fee_default cao hơn 3000000
-Tìm những customer có home_phone là 615 và is_fee_default lớn hơn 500000
-Lọc customer 126 có is_fee_default &gt; 51000000
-Tìm những customer có home_phone là 975 và is_fee_default lớn hơn 97000000
-Có thể sử dụng is_fee_default trong lọc customer 615, có giá trị là 500000.
-Lọc customer 615 có is_fee_default &gt; 500000
-Danh sách customer (home_phone: 615) có is_fee_default cao hơn 500000</t>
-  </si>
-  <si>
-    <t>Danh sách customer (vĩ độ: 347) có is_fee_default cao hơn 24000000
-Có thể tìm thấy is_fee_default trong bộ lọc customer 347 với giá trị 240000000.
-Liệt kê customer thuộc vĩ độ 332 với is_fee_default trên 1900000
-Lọc customer 347 có is_fee_default &gt; 24000000
-Lọc customer 332 có is_fee_default &gt; 1900000
-Liệt kê customer thuộc vĩ độ 291 với is_fee_default trên 250000
-Tìm những customer có vĩ độ là 404 và is_fee_default lớn hơn 900000
-Danh sách customer (vĩ độ: 332) có is_fee_default cao hơn 1900000
-Lọc customer 404 có is_fee_default &gt; 900000
-Danh sách customer (vĩ độ: 291) có is_fee_default cao hơn 250000</t>
-  </si>
-  <si>
-    <t>Liệt kê customer thuộc kinh độ 400 với is_fee_default trên 1900000
-Lọc customer 874 có is_fee_default &gt; 3600000
-Số liệu thống kê của customer thuộc kinh độ 400 với is_fee_default trên 1900000.
-Danh sách customer (kinh độ: 247) có is_fee_default cao hơn 4700000
-Số liệu thống kê customer trong kinh độ 400 có số lượng is_fee_default trên 1900000 là bao nhiêu?
-Lọc customer 247 có is_fee_default &gt; 4700000
-Danh sách customer (kinh độ: 400) có is_fee_default cao hơn 1900000
-Tìm những customer có kinh độ là 247 và is_fee_default lớn hơn 4700000
-Tìm những customer có kinh độ là 874 và is_fee_default lớn hơn 3600000
-Liệt kê customer thuộc kinh độ 874 với is_fee_default trên 3600000</t>
-  </si>
-  <si>
-    <t>Tìm những customer có mobile_phone là 317 và is_fee_default lớn hơn 920000
-Lọc customer 111 có is_fee_default &gt; 2700000
-Lọc customer 317 có is_fee_default &gt; 920000
-Tìm những customer có mobile_phone là 111 và is_fee_default lớn hơn 2700000.
-Tìm những customer có mobile_phone là 111 và is_fee_default lớn hơn 2700000
-Lọc customer 184 có is_fee_default &gt; 990000
-Lọc customer 280 có is_fee_default &gt; 660000
-Danh sách customer (mobile_phone: 280) có is_fee_default cao hơn 660000
-Liệt kê customer thuộc mobile_phone 280 với is_fee_default trên 660000
-Liệt kê customer thuộc mobile_phone 317 với is_fee_default trên 920000</t>
-  </si>
-  <si>
-    <t>Tìm những customer có bài đăng hoàn tất và is_fee_default lớn hơn 2300000.
-Danh sách customer (status: thành công) có is_fee_default cao hơn 9000000
-Liệt kê customer thuộc status thành công với is_fee_default trên 9000000
-Tìm những customer có status là hoàn tất và is_fee_default lớn hơn 2300000
-Liệt kê customer thuộc status hoàn tất với is_fee_default trên 2300000
-Lọc customer hoàn tất có is_fee_default &gt; 2300000
-Lọc customer đang chờ có is_fee_default &gt; 7000000
-Liệt kê customer thuộc status hoàn tất với is_fee_default trên 3100000
-Danh sách customer (status: đang chờ) có is_fee_default cao hơn 7000000
-Liệt kê customer thuộc status đang chờ với is_fee_default trên 7000000</t>
-  </si>
-  <si>
-    <t>Liệt kê customer thuộc sign_1 688 với is_fee_default trên 300000
-Liệt kê customer thuộc sign_1 101 với is_fee_default trên 3500000
-Tìm những customer có sign_1 là 688 và is_fee_default lớn hơn 300000
-Lọc customer 101 có is_fee_default &gt; 3500000
-Có những cá nhân nào có sign_1 là 101 và is_fee_default lớn hơn 3500000?
-Xác định các cá nhân có sign_1 là 101 và is_fee_default lớn hơn 3500000.
-Tìm những customer có sign_1 là 101 và is_fee_default lớn hơn 3500000
-Liệt kê customer thuộc sign_1 302 với is_fee_default trên 480000
-Lọc customer 688 có is_fee_default &gt; 300000
-Tìm những customer có sign_1 là 302 và is_fee_default lớn hơn 480000</t>
-  </si>
-  <si>
-    <t>Liệt kê customer thuộc sign 2 148 với is_fee_default trên 340000
-Danh sách customer (sign 2: 148) có is_fee_default cao hơn 340000
-Lọc customer 545 có is_fee_default &gt; 600000
-Tìm những customer có sign 2 là 298 và is_fee_default lớn hơn 310000
-Danh sách customer (sign 2: 545) có is_fee_default cao hơn 600000
-Số lượng các customer có sign 2 là 298 và is_fee_default lớn hơn 310000 là bao nhiêu?
-Lọc customer 148 có is_fee_default &gt; 340000
-Lọc customer 298 có is_fee_default &gt; 310000
-Tìm những customer có sign 2 là 545 và is_fee_default lớn hơn 600000
-Xác định các customer có sign 2 là 298 và is_fee_default lớn hơn 310000.</t>
-  </si>
-  <si>
-    <t>Tìm những customer có sex là 811 và is_fee_default lớn hơn 8700000
-Tính năng quan hệ tình dục là 375 và is_fee_default là 7600000.
-Lọc customer 811 có is_fee_default &gt; 8700000
-Lọc customer 853 có is_fee_default &gt; 3150000
-Danh sách customer (sex: 375) có is_fee_default cao hơn 7600000
-Lọc customer 375 có is_fee_default &gt; 7600000
-Liệt kê customer thuộc sex 936 với is_fee_default trên 100000000
-Tìm những customer có sex là 375 và is_fee_default lớn hơn 7600000
-Danh sách customer (sex: 853) có is_fee_default cao hơn 3150000
-Liệt kê customer thuộc sex 853 với is_fee_default trên 3150000</t>
-  </si>
-  <si>
-    <t>Lọc customer xử lý có is_fee_default &gt; 64000000
-Lọc customer thành công có is_fee_default &gt; 910000
-Lọc customer hết hạn có is_fee_default &gt; 3600000
-Lọc customer đã xong có is_fee_default &gt; 220000
-Tìm những customer có trước khi thay đổi là hết hạn và is_fee_default lớn hơn 3600000
-Liệt kê customer thuộc trước khi thay đổi hết hạn với is_fee_default trên 3600000
-Các ứng dụng của lọc customer hết hạn là gì?
-Danh sách customer (trước khi thay đổi: xử lý) có is_fee_default cao hơn 64000000
-Liệt kê customer thuộc trước khi thay đổi đã xong với is_fee_default trên 220000
-Tìm những customer có trước khi thay đổi là thành công và is_fee_default lớn hơn 910000</t>
-  </si>
-  <si>
-    <t>Số liệu thống kê customer thuộc sở hữu sau khi cập nhật không thành công với is_fee_default trên 800000.
-Lọc customer xử lý có is_fee_default &gt; 4500000
-Danh sách các customer được đưa ra sau khi cập nhật không thành công với is_fee_default trên 800000.
-Lọc customer hết hạn có is_fee_default &gt; 940000
-Liệt kê customer thuộc sau khi cập nhật bị treo với is_fee_default trên 4050000
-Danh sách customer (sau khi cập nhật: hết hạn) có is_fee_default cao hơn 940000
-Liệt kê customer thuộc sau khi cập nhật thất bại với is_fee_default trên 800000
-Tìm những customer có sau khi cập nhật là hết hạn và is_fee_default lớn hơn 940000
-Tìm những customer có sau khi cập nhật là bị treo và is_fee_default lớn hơn 4050000
-Liệt kê customer thuộc sau khi cập nhật xử lý với is_fee_default trên 4500000</t>
-  </si>
-  <si>
-    <t>cif_no, số cif, mã khách hàng, customer information file, số cif mã định danh duy nhất khách hàng ngân hàng, số mã khách hàng, mã định danh khách hàng, số khách hàng</t>
-  </si>
-  <si>
-    <t>id định danh khách hàng trong nội bộ, mã khách hàng, id định danh khách hàng trong hệ thống nội bộ, customer_id, số khách hàng</t>
-  </si>
-  <si>
-    <t>customer_no, mã số khách hàng, số khách hàng, có thể khác với cif tùy theo cấu trúc hệ thống</t>
-  </si>
-  <si>
-    <t>tên khách hàng, customer_name, họ và tên đầy đủ của khách hàng, họ và tên đầy đủ khách hàng</t>
-  </si>
-  <si>
-    <t>chi nhánh nơi mở/quản lý mã cif này, quản lý mã cif, chi nhánh nơi mở, mã khách hàng chi nhánh, khách hàng chi nhánh, cif_branch</t>
-  </si>
-  <si>
-    <t>loại cif, cá nhân, loại mã khách hàng, doanh nghiệp, cif_type, loại khách hàng, khách hàng ưu tiên...</t>
-  </si>
-  <si>
-    <t>số nhà, address line, address_line, dòng địa chỉ, tên đường, số tài khoản trạng thái, dòng địa chỉ chi tiết</t>
-  </si>
-  <si>
-    <t>số chi nhánh, mã chi nhánh, mã chi nhánh quản lý trực tiếp khách hàng, branch_code</t>
-  </si>
-  <si>
-    <t>trạng thái hiện khách hàng, trạng thái hiện tại của khách hàng, active, inactive, closed..., customer_status, khách hàng trạng thái, trạng thái khách hàng</t>
-  </si>
-  <si>
-    <t>ngày cấp giấy tờ định danh, ngày trạng thái trạng thái, ngày of issue, cmnd/cccd/hộ chiếu, date_of_issue</t>
-  </si>
-  <si>
-    <t>ngày khởi tạo khách hàng trên, ngày khởi tạo thông tin khách hàng trên hệ thống, ngày trạng thái, ngày init, init_date</t>
-  </si>
-  <si>
-    <t>trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
-  </si>
-  <si>
-    <t>nơi cấp giấy tờ định danh, place of issue, place_of_issue, nội dung trạng thái trạng thái, ca tp. hà nội</t>
-  </si>
-  <si>
-    <t>unique value, unique_value, giá trị đặc trưng dùng để định danh duy nhất khách hàng, trạng thái số tiền, giá trị đặc trưng định danh duy nhất khách hàng</t>
-  </si>
-  <si>
-    <t>trạng thái, trạng thái bản ghi, 0-hết hiệu lực, status, 1-hiệu lực</t>
-  </si>
-  <si>
-    <t>ngày tháng năm sinh, ngày of birth, ngày trạng thái trạng thái, date_of_birth</t>
-  </si>
-  <si>
-    <t>trạng thái cũ khách hàng, trạng thái cũ của khách hàng, old_customer_status, người thụ hưởng khách hàng trạng thái, trước khi thay đổi, trạng thái old khách hàng</t>
-  </si>
-  <si>
-    <t>new_customer_status, sau khi cập nhật, trạng thái new khách hàng, trạng thái mới của khách hàng, trạng thái mới khách hàng, nội dung khách hàng trạng thái</t>
-  </si>
-  <si>
-    <t>trạng thái nội dung trạng thái, đường dẫn ảnh mặt trước giấy tờ định danh, unique_image_front, cmnd/cccd, unique image front</t>
-  </si>
-  <si>
-    <t>trạng thái nội dung trạng thái, đường dẫn ảnh mặt sau giấy tờ định danh, unique_image_back, unique image back</t>
-  </si>
-  <si>
-    <t>trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay không, so sánh</t>
+Xem 10 customer có is_fee_default thấp nhất</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu các giao dịch mua sắm theo tên người dùng muốn mua sắm hoặc mua sắm.
+Danh sách customer (customer_name: Duyên Trần) có is_fee_default cao hơn 150000
+Tìm những customer có customer_name là Quý cô Chi Mai và is_fee_default lớn hơn 4450000
+Liệt kê customer thuộc customer_name Quý cô Chi Mai với is_fee_default trên 4450000
+Lọc customer Quý cô Chi Mai có is_fee_default &gt; 4450000
+Liệt kê customer thuộc customer_name Duyên Trần với is_fee_default trên 150000
+Tìm những customer có customer_name là Quang Hoàng và is_fee_default lớn hơn 2300000
+Liệt kê customer thuộc customer_name Quang Hoàng với is_fee_default trên 2300000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số lượng người dùng muốn xem.
+Lọc customer Duyên Trần có is_fee_default &gt; 150000</t>
+  </si>
+  <si>
+    <t>Liệt kê customer thuộc cá nhân nạp thẻ với is_fee_default trên 30000
+Tìm những customer có cá nhân là napas 247 và is_fee_default lớn hơn 71000000
+Người dùng muốn tra cứu các giao dịch mua sắm theo số lượng người dùng muốn mua hoặc bán sản phẩm.
+Lọc customer nạp thẻ có is_fee_default &gt; 490000
+Danh sách customer (cá nhân: nạp thẻ) có is_fee_default cao hơn 490000
+Liệt kê customer thuộc cá nhân nạp thẻ với is_fee_default trên 490000
+Người dùng muốn tra cứu danh sách các giao dịch nạp hoặc rút tiền theo số tài khoản nguồn.
+Lọc customer hóa đơn nước có is_fee_default &gt; 14000000
+Danh sách customer (cá nhân: hóa đơn nước) có is_fee_default cao hơn 14000000
+Danh sách customer (cá nhân: napas 247) có is_fee_default cao hơn 71000000</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Liệt kê customer thuộc số nhà 411 với is_fee_default trên 4850000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Lọc customer 319 có is_fee_default &gt; 560000
+Lọc customer 680 có is_fee_default &gt; 52000000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nhận tiền.
+Tìm những customer có số nhà là 680 và is_fee_default lớn hơn 52000000
+Tìm những customer có số nhà là 319 và is_fee_default lớn hơn 560000
+Danh sách customer (số nhà: 411) có is_fee_default cao hơn 4850000
+Lọc customer 411 có is_fee_default &gt; 4850000</t>
+  </si>
+  <si>
+    <t>Tìm những customer có quận/huyện là 408 và is_fee_default lớn hơn 4650000
+Lọc customer 367 có is_fee_default &gt; 580000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã truy cập hoặc mã tham chiếu.
+Người dùng muốn tra cứu các giao dịch mua sắm theo số lượng giao dịch hoặc hình thức mua sắm.
+Tìm những customer có quận/huyện là 825 và is_fee_default lớn hơn 450000
+Tìm những customer có quận/huyện là 294 và is_fee_default lớn hơn 7700000
+Người dùng muốn tra cứu các giao dịch mua sắm theo số lượng người dùng muốn tra cứu hoặc kết quả giao dịch.
+Danh sách customer (quận/huyện: 367) có is_fee_default cao hơn 580000
+Lọc customer 294 có is_fee_default &gt; 7700000</t>
+  </si>
+  <si>
+    <t>Lọc customer 829 có is_fee_default &gt; 440000
+Lọc customer 946 có is_fee_default &gt; 7100000
+Danh sách customer (bạc: 829) có is_fee_default cao hơn 440000
+Liệt kê customer thuộc bạc 829 với is_fee_default trên 440000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Liệt kê customer thuộc bạc 794 với is_fee_default trên 530000
+Danh sách customer (bạc: 800) có is_fee_default cao hơn 29000000
+Người dùng muốn tra cứu các giao dịch mua sắm theo số tiền.
+Liệt kê customer thuộc bạc 946 với is_fee_default trên 7100000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tiền.</t>
+  </si>
+  <si>
+    <t>Tìm những customer có active là hết hạn và is_fee_default lớn hơn 7100000
+Liệt kê customer thuộc active hết hạn với is_fee_default trên 82000000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số lượng giao dịch hoặc mã tham chiếu.
+Danh sách customer (active: hết hạn) có is_fee_default cao hơn 82000000
+Danh sách customer (active: treo) có is_fee_default cao hơn 4000000
+Danh sách customer (active: hết hạn) có is_fee_default cao hơn 7100000
+Liệt kê customer thuộc active hết hạn với is_fee_default trên 7100000
+Danh sách customer (active: thành công) có is_fee_default cao hơn 31000000
+Người dùng muốn tra cứu các giao dịch mua sắm theo số lượng giao dịch hoặc mã tham chiếu.</t>
+  </si>
+  <si>
+    <t>Danh sách customer (email: 376389) có is_fee_default cao hơn 73000000
+Danh sách customer (email: 544580) có is_fee_default cao hơn 840000
+Danh sách customer (email: 364901) có is_fee_default cao hơn 900000
+Tìm những customer có email là 544580 và is_fee_default lớn hơn 840000
+Người dùng muốn tra cứu các giao dịch nạp hoặc rút tiền theo số tài khoản nhận email hoặc tài khoản đích.
+Liệt kê customer thuộc email 983636 với is_fee_default trên 7200000
+Liệt kê customer thuộc email 376389 với is_fee_default trên 73000000
+Lọc customer 983636 có is_fee_default &gt; 7200000
+Lọc customer 364901 có is_fee_default &gt; 900000
+Lọc customer 544580 có is_fee_default &gt; 840000</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã truy cập hoặc mã tham chiếu.
+Tìm những customer có home_phone là 212 và is_fee_default lớn hơn 950000
+Liệt kê customer thuộc home_phone 212 với is_fee_default trên 950000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số điện thoại hoặc điện thoại.
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Tìm những customer có home_phone là 154 và is_fee_default lớn hơn 4500000
+Danh sách customer (home_phone: 390) có is_fee_default cao hơn 80000
+Liệt kê customer thuộc home_phone 154 với is_fee_default trên 4500000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nhận tiền.
+Tìm những customer có home_phone là 555 và is_fee_default lớn hơn 690000</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu các giao dịch mua sắm theo số đo hoặc số lượng giao dịch.
+Người dùng muốn tra cứu danh sách các cá nhân theo trạng thái xử lý hoặc kết quả giao dịch.
+Tìm những customer có vĩ độ là 560 và is_fee_default lớn hơn 38000000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số lượng giao dịch hoặc mã tham chiếu.
+Liệt kê customer thuộc vĩ độ 560 với is_fee_default trên 38000000
+Danh sách customer (vĩ độ: 950) có is_fee_default cao hơn 6600000
+Liệt kê customer thuộc vĩ độ 950 với is_fee_default trên 6600000
+Lọc customer 684 có is_fee_default &gt; 410000
+Lọc customer 560 có is_fee_default &gt; 38000000
+Danh sách customer (vĩ độ: 560) có is_fee_default cao hơn 38000000</t>
+  </si>
+  <si>
+    <t>Danh sách customer (kinh độ: 798) có is_fee_default cao hơn 35000000
+Liệt kê customer thuộc kinh độ 798 với is_fee_default trên 35000000
+Tìm những customer có kinh độ là 228 và is_fee_default lớn hơn 4700000
+Lọc customer 747 có is_fee_default &gt; 2900000
+Người dùng muốn tra cứu các giao dịch mua sắm theo số tiền.
+Tìm những customer có kinh độ là 747 và is_fee_default lớn hơn 2900000
+Lọc customer 236 có is_fee_default &gt; 140000
+Liệt kê customer thuộc kinh độ 236 với is_fee_default trên 140000
+Liệt kê customer thuộc kinh độ 228 với is_fee_default trên 4700000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.</t>
+  </si>
+  <si>
+    <t>Liệt kê customer thuộc mobile phone 136 với is_fee_default trên 30000
+Danh sách customer (mobile phone: 372) có is_fee_default cao hơn 9200000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Liệt kê customer thuộc mobile phone 372 với is_fee_default trên 9200000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số điện thoại hoặc điện thoại.
+Tìm những customer có mobile phone là 136 và is_fee_default lớn hơn 30000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã truy cập hoặc mã tham chiếu.
+Lọc customer 136 có is_fee_default &gt; 30000
+Tìm những customer có mobile phone là 238 và is_fee_default lớn hơn 2550000
+Lọc customer 372 có is_fee_default &gt; 9200000</t>
+  </si>
+  <si>
+    <t>Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nguồn.
+Lọc customer đã xong có is_fee_default &gt; 2000000
+Danh sách customer (status: thất bại) có is_fee_default cao hơn 91000000
+Danh sách customer (status: đã xong) có is_fee_default cao hơn 2000000
+Người dùng muốn tra cứu một giao dịch mua sắm cụ thể dựa trên mã truy cập hoặc mã tham chiếu.
+Lọc customer treo có is_fee_default &gt; 7300000
+Lọc customer thất bại có is_fee_default &gt; 600000
+Tìm những customer có status là đã xong và is_fee_default lớn hơn 2000000
+Liệt kê customer thuộc status thất bại với is_fee_default trên 600000
+Liệt kê customer thuộc status treo với is_fee_default trên 7300000</t>
+  </si>
+  <si>
+    <t>Lọc customer 176 có is_fee_default &gt; 3550000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số tài khoản nhận tiền hoặc tài khoản đích.
+Liệt kê customer thuộc sign 1 941 với is_fee_default trên 230000
+Tìm những customer có sign 1 là 176 và is_fee_default lớn hơn 3550000
+Liệt kê customer thuộc sign 1 572 với is_fee_default trên 49000000
+Lọc customer 941 có is_fee_default &gt; 230000
+Tìm những customer có sign 1 là 572 và is_fee_default lớn hơn 49000000
+Người dùng muốn tra cứu các giao dịch mua sắm theo số tài khoản nhận tiền hoặc tài khoản đích.
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã truy cập hoặc mã tham chiếu.
+Lọc customer 741 có is_fee_default &gt; 4000000</t>
+  </si>
+  <si>
+    <t>Tìm những customer có sign_2 là 695 và is_fee_default lớn hơn 610000
+Lọc customer 780 có is_fee_default &gt; 2900000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.
+Người dùng muốn tra cứu các giao dịch mua sắm theo số lượng giao dịch hoặc mã tham chiếu.
+Lọc customer 728 có is_fee_default &gt; 850000
+Lọc customer 404 có is_fee_default &gt; 2000000
+Liệt kê customer thuộc sign_2 780 với is_fee_default trên 2900000
+Tìm những customer có sign_2 là 404 và is_fee_default lớn hơn 2000000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã truy cập hoặc mã tham chiếu.
+Danh sách customer (sign_2: 404) có is_fee_default cao hơn 2000000</t>
+  </si>
+  <si>
+    <t>Danh sách customer (sex: 863) có is_fee_default cao hơn 550000
+Người dùng muốn tra cứu các giao dịch ngoại tuyến theo số tài khoản nhận dạng hoặc mã tham chiếu.
+Liệt kê customer thuộc sex 588 với is_fee_default trên 600000
+Tìm những customer có sex là 103 và is_fee_default lớn hơn 3500000
+Danh sách customer (sex: 103) có is_fee_default cao hơn 3500000
+Liệt kê customer thuộc sex 103 với is_fee_default trên 3500000
+Người dùng muốn tra cứu các giao dịch ngoại tuyến theo số lượng người dùng muốn tra cứu hoặc kết quả giao dịch.
+Lọc customer 103 có is_fee_default &gt; 3500000
+Lọc customer 588 có is_fee_default &gt; 600000
+Tìm những customer có sex là 863 và is_fee_default lớn hơn 550000</t>
+  </si>
+  <si>
+    <t>Tìm những customer có trước khi thay đổi là quá giờ và is_fee_default lớn hơn 3400000
+Lọc customer hết hạn có is_fee_default &gt; 56000000
+Lọc customer thành công có is_fee_default &gt; 970000
+Liệt kê customer thuộc trước khi thay đổi thành công với is_fee_default trên 970000
+Danh sách customer (trước khi thay đổi: treo) có is_fee_default cao hơn 2250000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo trạng thái xử lý hoặc kết quả giao dịch.
+Danh sách customer (trước khi thay đổi: thành công) có is_fee_default cao hơn 970000
+Người dùng muốn tra cứu các giao dịch mua sắm theo trạng thái xử lý hoặc kết quả giao dịch.
+Tìm những customer có trước khi thay đổi là thành công và is_fee_default lớn hơn 970000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã truy cập hoặc mã tham chiếu.</t>
+  </si>
+  <si>
+    <t>Lọc customer hoàn tất có is_fee_default &gt; 75000000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số lượng người dùng muốn tra cứu hoặc kết quả giao dịch.
+Lọc customer thành công có is_fee_default &gt; 1000000
+Danh sách customer (sau khi cập nhật: quá giờ) có is_fee_default cao hơn 6200000
+Lọc customer quá giờ có is_fee_default &gt; 6200000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã người dùng muốn tra cứu hoặc mã tham chiếu.
+Danh sách customer (sau khi cập nhật: đang chờ) có is_fee_default cao hơn 5400000
+Người dùng muốn tra cứu danh sách các giao dịch mua sắm theo số lượng giao dịch hoặc mã tham chiếu.
+Tìm những customer có sau khi cập nhật là thành công và is_fee_default lớn hơn 1000000
+Người dùng muốn tra cứu một giao dịch nạp hoặc rút tiền cụ thể dựa trên mã giao dịch hoặc mã tham chiếu.</t>
+  </si>
+  <si>
+    <t>cif_no, số cif mã định danh duy nhất khách hàng ngân hàng, customer information file, mã định danh khách hàng, số khách hàng, số cif, số mã khách hàng, mã khách hàng</t>
+  </si>
+  <si>
+    <t>id định danh khách hàng trong nội bộ, id định danh khách hàng trong hệ thống nội bộ, customer_id, số khách hàng, mã khách hàng</t>
+  </si>
+  <si>
+    <t>có thể khác với cif tùy theo cấu trúc hệ thống, số khách hàng, customer_no, mã số khách hàng</t>
+  </si>
+  <si>
+    <t>customer_name, họ và tên đầy đủ của khách hàng, họ và tên đầy đủ khách hàng, tên khách hàng</t>
+  </si>
+  <si>
+    <t>chi nhánh nơi mở, chi nhánh nơi mở/quản lý mã cif này, mã khách hàng chi nhánh, quản lý mã cif, cif_branch, khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>khách hàng ưu tiên..., cif_type, loại khách hàng, cá nhân, loại cif, doanh nghiệp, loại mã khách hàng</t>
+  </si>
+  <si>
+    <t>số tài khoản trạng thái, số nhà, address_line, dòng địa chỉ, dòng địa chỉ chi tiết, tên đường, address line</t>
+  </si>
+  <si>
+    <t>mã chi nhánh quản lý trực tiếp khách hàng, số chi nhánh, branch_code, mã chi nhánh</t>
+  </si>
+  <si>
+    <t>trạng thái khách hàng, khách hàng trạng thái, active, trạng thái hiện tại của khách hàng, trạng thái hiện khách hàng, customer_status, closed..., inactive</t>
+  </si>
+  <si>
+    <t>ngày trạng thái trạng thái, ngày of issue, ngày cấp giấy tờ định danh, cmnd/cccd/hộ chiếu, date_of_issue</t>
+  </si>
+  <si>
+    <t>ngày init, ngày trạng thái, ngày khởi tạo thông tin khách hàng trên hệ thống, init_date, ngày khởi tạo khách hàng trên</t>
+  </si>
+  <si>
+    <t>is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay không</t>
+  </si>
+  <si>
+    <t>nội dung trạng thái trạng thái, nơi cấp giấy tờ định danh, place_of_issue, ca tp. hà nội, place of issue</t>
+  </si>
+  <si>
+    <t>unique value, giá trị đặc trưng dùng để định danh duy nhất khách hàng, unique_value, trạng thái số tiền, giá trị đặc trưng định danh duy nhất khách hàng</t>
+  </si>
+  <si>
+    <t>trạng thái, 1-hiệu lực, trạng thái bản ghi, 0-hết hiệu lực, status</t>
+  </si>
+  <si>
+    <t>ngày of birth, date_of_birth, ngày trạng thái trạng thái, ngày tháng năm sinh</t>
+  </si>
+  <si>
+    <t>trước khi thay đổi, trạng thái cũ khách hàng, người thụ hưởng khách hàng trạng thái, old_customer_status, trạng thái old khách hàng, trạng thái cũ của khách hàng</t>
+  </si>
+  <si>
+    <t>new_customer_status, trạng thái new khách hàng, trạng thái mới khách hàng, nội dung khách hàng trạng thái, sau khi cập nhật, trạng thái mới của khách hàng</t>
+  </si>
+  <si>
+    <t>unique image front, cmnd/cccd, trạng thái nội dung trạng thái, unique_image_front, đường dẫn ảnh mặt trước giấy tờ định danh</t>
+  </si>
+  <si>
+    <t>unique_image_back, unique image back, đường dẫn ảnh mặt sau giấy tờ định danh, trạng thái nội dung trạng thái</t>
+  </si>
+  <si>
+    <t>is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay không, so sánh</t>
   </si>
   <si>
     <t>xếp hạng</t>
   </si>
   <si>
-    <t>tên khách hàng, customer_name, họ và tên đầy đủ của khách hàng, họ và tên đầy đủ khách hàng, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtên khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>loại cif, cá nhân, loại mã khách hàng, doanh nghiệp, cif_type, loại khách hàng, khách hàng ưu tiên..., trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngloại mã khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>số nhà, address line, address_line, dòng địa chỉ, tên đường, số tài khoản trạng thái, dòng địa chỉ chi tiết, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngdòng địa chỉ và is phí default</t>
-  </si>
-  <si>
-    <t>địa chỉ đầy đủ, full_address, bao gồm xã/phường, quận/huyện, full address, tỉnh/thành, nội dung số tài khoản, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngđịa chỉ đầy đủ và is phí default</t>
-  </si>
-  <si>
-    <t>customer_class, bạc, vàng, đồng, kim cương, loại khách hàng, phân hạng khách hàng, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngphân hạng khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>trạng thái hiện khách hàng, trạng thái hiện tại của khách hàng, active, inactive, closed..., customer_status, khách hàng trạng thái, trạng thái khách hàng, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái hiện khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>email, địa chỉ thư điện tử khách hàng, địa chỉ thư điện tử của khách hàng, nội dung, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngemail và is phí default</t>
-  </si>
-  <si>
-    <t>home_phone, số điện thoại bàn, điện thoại cố định, nội dung phone, home phone, số điện thoại bàn/điện thoại cố định, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khônghome phone và is phí default</t>
-  </si>
-  <si>
-    <t>trạng thái, latitude, tọa độ vị trí nhà ở hoặc nơi đăng ký, vĩ độ, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khônglatitude và is phí default</t>
-  </si>
-  <si>
-    <t>tọa độ vị trí, kinh độ, longitude, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngkinh độ và is phí default</t>
-  </si>
-  <si>
-    <t>mobile_phone, mobile phone, số điện thoại di động chính, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngmobile phone và is phí default</t>
-  </si>
-  <si>
-    <t>trạng thái, trạng thái bản ghi, 0-hết hiệu lực, status, 1-hiệu lực, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái bản ghi và is phí default</t>
-  </si>
-  <si>
-    <t>sign_1, đường dẫn hoặc chữ ký mẫu số khách hàng, sign 1, trạng thái trạng thái, đường dẫn hoặc dữ liệu chữ ký mẫu số 1 của khách hàng, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsign 1 và is phí default</t>
-  </si>
-  <si>
-    <t>sign 2, sign_2, đường dẫn hoặc chữ ký mẫu số, trạng thái trạng thái, đường dẫn hoặc dữ liệu chữ ký mẫu số 2, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsign 2 và is phí default</t>
-  </si>
-  <si>
-    <t>sex, female, male, nội dung, unknown, giới tính, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsex và is phí default</t>
-  </si>
-  <si>
-    <t>trạng thái cũ khách hàng, trạng thái cũ của khách hàng, old_customer_status, người thụ hưởng khách hàng trạng thái, trước khi thay đổi, trạng thái old khách hàng, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái cũ khách hàng và is phí default</t>
-  </si>
-  <si>
-    <t>new_customer_status, sau khi cập nhật, trạng thái new khách hàng, trạng thái mới của khách hàng, trạng thái mới khách hàng, nội dung khách hàng trạng thái, trạng thái phí trạng thái, is_fee_default, is phí default, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái mới khách hàng và is phí default</t>
+    <t>customer_name, họ và tên đầy đủ của khách hàng, họ và tên đầy đủ khách hàng, tên khách hàng, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khônghọ và tên đầy đủ khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>khách hàng ưu tiên..., cif_type, loại khách hàng, cá nhân, loại cif, doanh nghiệp, loại mã khách hàng, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngloại cif và is phí default</t>
+  </si>
+  <si>
+    <t>số tài khoản trạng thái, số nhà, address_line, dòng địa chỉ, dòng địa chỉ chi tiết, tên đường, address line, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngdòng địa chỉ và is phí default</t>
+  </si>
+  <si>
+    <t>quận/huyện, nội dung số tài khoản, tỉnh/thành, full address, full_address, bao gồm xã/phường, địa chỉ đầy đủ, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngđịa chỉ đầy đủ và is phí default</t>
+  </si>
+  <si>
+    <t>đồng, loại khách hàng, vàng, kim cương, bạc, customer_class, phân hạng khách hàng, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngphân hạng khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>trạng thái khách hàng, khách hàng trạng thái, active, trạng thái hiện tại của khách hàng, trạng thái hiện khách hàng, customer_status, closed..., inactive, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>địa chỉ thư điện tử khách hàng, nội dung, địa chỉ thư điện tử của khách hàng, email, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngđịa chỉ thư điện tử khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>nội dung phone, home_phone, số điện thoại bàn, điện thoại cố định, số điện thoại bàn/điện thoại cố định, home phone, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khônghome phone và is phí default</t>
+  </si>
+  <si>
+    <t>latitude, trạng thái, tọa độ vị trí nhà ở hoặc nơi đăng ký, vĩ độ, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khônglatitude và is phí default</t>
+  </si>
+  <si>
+    <t>longitude, kinh độ, tọa độ vị trí, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khônglongitude và is phí default</t>
+  </si>
+  <si>
+    <t>số điện thoại di động chính, mobile phone, mobile_phone, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsố điện thoại di động chính và is phí default</t>
+  </si>
+  <si>
+    <t>trạng thái, 1-hiệu lực, trạng thái bản ghi, 0-hết hiệu lực, status, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái bản ghi và is phí default</t>
+  </si>
+  <si>
+    <t>đường dẫn hoặc chữ ký mẫu số khách hàng, sign 1, đường dẫn hoặc dữ liệu chữ ký mẫu số 1 của khách hàng, trạng thái trạng thái, sign_1, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsign 1 và is phí default</t>
+  </si>
+  <si>
+    <t>sign_2, đường dẫn hoặc dữ liệu chữ ký mẫu số 2, sign 2, đường dẫn hoặc chữ ký mẫu số, trạng thái trạng thái, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsign 2 và is phí default</t>
+  </si>
+  <si>
+    <t>female, nội dung, unknown, sex, male, giới tính, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngsex và is phí default</t>
+  </si>
+  <si>
+    <t>trước khi thay đổi, trạng thái cũ khách hàng, người thụ hưởng khách hàng trạng thái, old_customer_status, trạng thái old khách hàng, trạng thái cũ của khách hàng, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái cũ khách hàng và is phí default</t>
+  </si>
+  <si>
+    <t>new_customer_status, trạng thái new khách hàng, trạng thái mới khách hàng, nội dung khách hàng trạng thái, sau khi cập nhật, trạng thái mới của khách hàng, is_fee_default, is phí default, trạng thái phí trạng thái, đánh dấu khách hàng có thuộc diện mặc định thu phí hay khôngtrạng thái new khách hàng và is phí default</t>
   </si>
   <si>
     <t>{"raw_text": "SELECT * FROM customer WHERE cif_no = '{{cif_no}}'"}</t>
@@ -970,8 +976,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1023,10 +1029,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1034,13 +1043,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1078,7 +1095,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1112,6 +1129,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1146,9 +1164,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1321,11 +1340,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="5" width="46.921875" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1342,666 +1364,666 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" ht="233.15" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5" ht="204" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
+    <row r="11" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+    <row r="12" spans="1:5" ht="306" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
+    <row r="13" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
+    <row r="14" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
+    <row r="15" spans="1:5" ht="233.15" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
+    <row r="16" spans="1:5" ht="204" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
+    <row r="17" spans="1:5" ht="291.45" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
+    <row r="18" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
+    <row r="19" spans="1:5" ht="189.45" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
+    <row r="20" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
+    <row r="21" spans="1:5" ht="276.89999999999998" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
+    <row r="22" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
+    <row r="23" spans="1:5" ht="189.45" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
+    <row r="24" spans="1:5" ht="276.89999999999998" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
+    <row r="25" spans="1:5" ht="276.89999999999998" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
+    <row r="26" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
+    <row r="27" spans="1:5" ht="276.89999999999998" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
+    <row r="28" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
+    <row r="29" spans="1:5" ht="291.45" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
+    <row r="30" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
+    <row r="31" spans="1:5" ht="291.45" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
+    <row r="32" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
+    <row r="33" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
+    <row r="34" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
+    <row r="35" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
+    <row r="36" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
+    <row r="37" spans="1:5" ht="247.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
+    <row r="38" spans="1:5" ht="276.89999999999998" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
+    <row r="39" spans="1:5" ht="262.3" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
+    <row r="40" spans="1:5" ht="276.89999999999998" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="2" t="s">
         <v>199</v>
       </c>
     </row>
